--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -790,7 +790,7 @@
         <v>2.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="G3" t="n">
         <v>4.8</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>4.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1560,7 +1560,7 @@
         <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
         <v>1.96</v>
@@ -1656,7 +1656,7 @@
         <v>18.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
         <v>9.199999999999999</v>
@@ -1692,11 +1692,11 @@
         <v>40</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2151,10 +2151,10 @@
         <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
         <v>1.61</v>
@@ -2187,7 +2187,7 @@
         <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE9" t="n">
         <v>48</v>
@@ -2205,13 +2205,13 @@
         <v>48</v>
       </c>
       <c r="AJ9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
         <v>65</v>
@@ -2274,11 +2274,11 @@
         <v>8.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
         <v>25</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
         <v>21</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>3.65</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J11" t="n">
         <v>3.9</v>
@@ -2551,13 +2551,13 @@
         <v>2.64</v>
       </c>
       <c r="V11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W11" t="n">
         <v>1.37</v>
       </c>
       <c r="X11" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
         <v>13.5</v>
@@ -2593,13 +2593,13 @@
         <v>32</v>
       </c>
       <c r="AJ11" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
         <v>60</v>
@@ -2611,7 +2611,7 @@
         <v>10</v>
       </c>
       <c r="AP11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>12.5</v>
@@ -2620,7 +2620,7 @@
         <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AT11" t="n">
         <v>16.5</v>
@@ -2635,7 +2635,7 @@
         <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AY11" t="n">
         <v>13.5</v>
@@ -2647,7 +2647,7 @@
         <v>23</v>
       </c>
       <c r="BB11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC11" t="n">
         <v>30</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G12" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H12" t="n">
         <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>2.96</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -2900,10 +2900,10 @@
         <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
@@ -2924,7 +2924,7 @@
         <v>1.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -3294,7 +3294,7 @@
         <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
@@ -3551,7 +3551,7 @@
         <v>70</v>
       </c>
       <c r="AF16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG16" t="n">
         <v>15.5</v>
@@ -3581,16 +3581,16 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AR16" t="n">
         <v>2.42</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AT16" t="n">
         <v>2.14</v>
@@ -3614,29 +3614,29 @@
         <v>15.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BB16" t="n">
         <v>2.42</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G17" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H17" t="n">
-        <v>1.05</v>
+        <v>7.2</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
         <v>3.7</v>
@@ -3691,13 +3691,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 00:24:14</t>
+          <t>2026-03-09 02:33:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="G2" t="n">
         <v>22</v>
@@ -766,7 +766,7 @@
         <v>1.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="J2" t="n">
         <v>7.4</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -963,7 +963,7 @@
         <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
@@ -984,7 +984,7 @@
         <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="H5" t="n">
-        <v>1.96</v>
+        <v>3.45</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J6" t="n">
         <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.33</v>
@@ -1557,16 +1557,16 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
@@ -1575,25 +1575,25 @@
         <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
         <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>15.5</v>
@@ -1611,7 +1611,7 @@
         <v>16.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG6" t="n">
         <v>27</v>
@@ -1629,13 +1629,13 @@
         <v>110</v>
       </c>
       <c r="AL6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM6" t="n">
         <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AO6" t="n">
         <v>9.199999999999999</v>
@@ -1644,7 +1644,7 @@
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR6" t="n">
         <v>8.199999999999999</v>
@@ -1668,10 +1668,10 @@
         <v>44</v>
       </c>
       <c r="AY6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA6" t="n">
         <v>30</v>
@@ -1692,11 +1692,11 @@
         <v>40</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="n">
         <v>1.88</v>
       </c>
       <c r="I7" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
         <v>3.65</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
         <v>2.52</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,7 +2139,7 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
@@ -2163,22 +2163,22 @@
         <v>2.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
         <v>21</v>
       </c>
       <c r="Z9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA9" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AB9" t="n">
         <v>13</v>
@@ -2190,7 +2190,7 @@
         <v>16.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF9" t="n">
         <v>14.5</v>
@@ -2202,7 +2202,7 @@
         <v>15.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
         <v>23</v>
@@ -2211,13 +2211,13 @@
         <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AM9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
         <v>32</v>
@@ -2229,13 +2229,13 @@
         <v>18.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AS9" t="n">
         <v>60</v>
       </c>
       <c r="AT9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU9" t="n">
         <v>8.800000000000001</v>
@@ -2271,14 +2271,14 @@
         <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG9" t="n">
         <v>28</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J10" t="n">
         <v>3.8</v>
@@ -2333,7 +2333,7 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
@@ -2351,22 +2351,22 @@
         <v>2.54</v>
       </c>
       <c r="T10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U10" t="n">
         <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
         <v>21</v>
@@ -2384,13 +2384,13 @@
         <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
@@ -2402,7 +2402,7 @@
         <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
         <v>32</v>
@@ -2411,16 +2411,16 @@
         <v>60</v>
       </c>
       <c r="AN10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO10" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>16</v>
       </c>
       <c r="AP10" t="n">
         <v>20</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
         <v>18</v>
@@ -2438,10 +2438,10 @@
         <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY10" t="n">
         <v>11</v>
@@ -2450,10 +2450,10 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BB10" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BC10" t="n">
         <v>21</v>
@@ -2462,17 +2462,17 @@
         <v>26</v>
       </c>
       <c r="BE10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BF10" t="n">
         <v>13.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>3.65</v>
       </c>
       <c r="G11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
         <v>2.08</v>
@@ -2527,22 +2527,22 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
         <v>1.58</v>
@@ -2581,7 +2581,7 @@
         <v>19.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AG11" t="n">
         <v>15.5</v>
@@ -2596,7 +2596,7 @@
         <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL11" t="n">
         <v>38</v>
@@ -2605,7 +2605,7 @@
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO11" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
         <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AT11" t="n">
         <v>16.5</v>
@@ -2644,16 +2644,16 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC11" t="n">
         <v>30</v>
       </c>
       <c r="BD11" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BE11" t="n">
         <v>29</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
         <v>2.96</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>2.18</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H13" t="n">
         <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3476,49 +3476,49 @@
         <v>2.14</v>
       </c>
       <c r="G16" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.6</v>
       </c>
-      <c r="I16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.03</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.31</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,116 +3527,116 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL16" t="n">
         <v>40</v>
       </c>
-      <c r="AA16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ16" t="n">
+      <c r="AM16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW16" t="n">
         <v>40</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AX16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG16" t="n">
         <v>34</v>
       </c>
-      <c r="AL16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4055,52 +4055,52 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="R19" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,116 +4109,116 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -963,7 +963,7 @@
         <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I6" t="n">
         <v>1.62</v>
@@ -1557,7 +1557,7 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
@@ -1572,7 +1572,7 @@
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
@@ -1593,7 +1593,7 @@
         <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
         <v>15.5</v>
@@ -1602,7 +1602,7 @@
         <v>21</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>9.800000000000001</v>
@@ -1614,22 +1614,22 @@
         <v>55</v>
       </c>
       <c r="AG6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AK6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AM6" t="n">
         <v>140</v>
@@ -1647,25 +1647,25 @@
         <v>7.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS6" t="n">
         <v>13.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AU6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
         <v>15</v>
       </c>
       <c r="AX6" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AY6" t="n">
         <v>21</v>
@@ -1674,13 +1674,13 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB6" t="n">
         <v>46</v>
       </c>
       <c r="BC6" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BD6" t="n">
         <v>38</v>
@@ -1689,14 +1689,14 @@
         <v>42</v>
       </c>
       <c r="BF6" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I7" t="n">
         <v>2.12</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.98</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -2133,7 +2133,7 @@
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2151,7 +2151,7 @@
         <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
         <v>2.56</v>
@@ -2184,7 +2184,7 @@
         <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>16.5</v>
@@ -2211,13 +2211,13 @@
         <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM9" t="n">
         <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO9" t="n">
         <v>32</v>
@@ -2241,10 +2241,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AX9" t="n">
         <v>13</v>
@@ -2253,7 +2253,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
         <v>38</v>
@@ -2262,7 +2262,7 @@
         <v>20</v>
       </c>
       <c r="BC9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD9" t="n">
         <v>24</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I10" t="n">
         <v>2.72</v>
@@ -2342,13 +2342,13 @@
         <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
         <v>1.56</v>
@@ -2390,7 +2390,7 @@
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
@@ -2411,7 +2411,7 @@
         <v>60</v>
       </c>
       <c r="AN10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO10" t="n">
         <v>15.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H11" t="n">
         <v>2.08</v>
@@ -2521,25 +2521,25 @@
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
         <v>2.56</v>
@@ -2548,16 +2548,16 @@
         <v>1.58</v>
       </c>
       <c r="U11" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
         <v>13.5</v>
@@ -2566,7 +2566,7 @@
         <v>16</v>
       </c>
       <c r="AA11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB11" t="n">
         <v>18.5</v>
@@ -2587,10 +2587,10 @@
         <v>15.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AJ11" t="n">
         <v>65</v>
@@ -2605,7 +2605,7 @@
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
         <v>10</v>
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR11" t="n">
         <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT11" t="n">
         <v>16.5</v>
@@ -2635,7 +2635,7 @@
         <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY11" t="n">
         <v>13.5</v>
@@ -2653,7 +2653,7 @@
         <v>30</v>
       </c>
       <c r="BD11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE11" t="n">
         <v>29</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>2.22</v>
       </c>
       <c r="H16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
         <v>3.8</v>
@@ -3503,7 +3503,7 @@
         <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
         <v>2</v>
@@ -3518,7 +3518,7 @@
         <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3533,10 +3533,10 @@
         <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AB16" t="n">
         <v>9.4</v>
@@ -3548,7 +3548,7 @@
         <v>16</v>
       </c>
       <c r="AE16" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF16" t="n">
         <v>13.5</v>
@@ -3560,7 +3560,7 @@
         <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
         <v>28</v>
@@ -3590,7 +3590,7 @@
         <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AT16" t="n">
         <v>8.4</v>
@@ -3605,7 +3605,7 @@
         <v>40</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY16" t="n">
         <v>9.800000000000001</v>
@@ -3614,7 +3614,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.5</v>
+        <v>48</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -3626,17 +3626,17 @@
         <v>32</v>
       </c>
       <c r="BE16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF16" t="n">
         <v>12</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>12.5</v>
       </c>
       <c r="BG16" t="n">
         <v>34</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>2.64</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
         <v>5.8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
         <v>4.2</v>
@@ -4085,7 +4085,7 @@
         <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
         <v>1.89</v>
@@ -4097,10 +4097,10 @@
         <v>3.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4112,7 +4112,7 @@
         <v>16.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z19" t="n">
         <v>42</v>
@@ -4172,7 +4172,7 @@
         <v>7.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -4193,10 +4193,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB19" t="n">
         <v>16</v>
@@ -4205,20 +4205,20 @@
         <v>16</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE19" t="n">
         <v>8.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BG19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -769,22 +769,22 @@
         <v>1.25</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="K2" t="n">
         <v>9.6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
         <v>2.84</v>
@@ -793,134 +793,134 @@
         <v>1.44</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G3" t="n">
         <v>4.8</v>
@@ -969,152 +969,152 @@
         <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.58</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G4" t="n">
         <v>7.2</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
         <v>1.9</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G6" t="n">
         <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I6" t="n">
         <v>1.62</v>
@@ -1563,7 +1563,7 @@
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
         <v>1.94</v>
@@ -1572,7 +1572,7 @@
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
@@ -1590,10 +1590,10 @@
         <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>15.5</v>
@@ -1629,7 +1629,7 @@
         <v>100</v>
       </c>
       <c r="AL6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM6" t="n">
         <v>140</v>
@@ -1638,13 +1638,13 @@
         <v>150</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR6" t="n">
         <v>8.4</v>
@@ -1659,13 +1659,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AY6" t="n">
         <v>21</v>
@@ -1680,23 +1680,23 @@
         <v>46</v>
       </c>
       <c r="BC6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BD6" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BE6" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="I7" t="n">
         <v>2.12</v>
@@ -1742,7 +1742,7 @@
         <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.54</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q8" t="n">
         <v>2.8</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
@@ -2154,13 +2154,13 @@
         <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
         <v>1.61</v>
       </c>
       <c r="U9" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
         <v>1.32</v>
@@ -2199,10 +2199,10 @@
         <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
         <v>23</v>
@@ -2238,7 +2238,7 @@
         <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV9" t="n">
         <v>14.5</v>
@@ -2259,7 +2259,7 @@
         <v>38</v>
       </c>
       <c r="BB9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC9" t="n">
         <v>16.5</v>
@@ -2268,7 +2268,7 @@
         <v>24</v>
       </c>
       <c r="BE9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BF9" t="n">
         <v>8.6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I10" t="n">
         <v>2.72</v>
@@ -2327,7 +2327,7 @@
         <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
@@ -2348,7 +2348,7 @@
         <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="T10" t="n">
         <v>1.56</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2512,28 +2512,28 @@
         <v>2.08</v>
       </c>
       <c r="I11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q11" t="n">
         <v>1.65</v>
@@ -2653,7 +2653,7 @@
         <v>30</v>
       </c>
       <c r="BD11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
         <v>29</v>
@@ -2662,11 +2662,11 @@
         <v>18</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H12" t="n">
         <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>2.96</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>2.18</v>
       </c>
       <c r="G13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
         <v>4.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -3294,7 +3294,7 @@
         <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="n">
         <v>3.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
         <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
         <v>3.55</v>
@@ -3518,7 +3518,7 @@
         <v>1.8</v>
       </c>
       <c r="U16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3536,10 +3536,10 @@
         <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
         <v>8</v>
@@ -3551,7 +3551,7 @@
         <v>60</v>
       </c>
       <c r="AF16" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
@@ -3560,22 +3560,22 @@
         <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AK16" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AL16" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM16" t="n">
         <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
         <v>55</v>
@@ -3590,19 +3590,19 @@
         <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU16" t="n">
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>40</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
         <v>11.5</v>
@@ -3614,7 +3614,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>48</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -3626,7 +3626,7 @@
         <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BF16" t="n">
         <v>12</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G17" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="H17" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>2.34</v>
       </c>
       <c r="O17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P17" t="n">
         <v>1.44</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G19" t="n">
         <v>1.87</v>
@@ -4070,7 +4070,7 @@
         <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4079,28 +4079,28 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R19" t="n">
         <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4121,7 +4121,7 @@
         <v>140</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC19" t="n">
         <v>9.4</v>
@@ -4160,7 +4160,7 @@
         <v>12</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP19" t="n">
         <v>13</v>
@@ -4169,13 +4169,13 @@
         <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU19" t="n">
         <v>7.8</v>
@@ -4184,7 +4184,7 @@
         <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX19" t="n">
         <v>9.4</v>
@@ -4196,7 +4196,7 @@
         <v>6.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB19" t="n">
         <v>16</v>
@@ -4205,20 +4205,20 @@
         <v>16</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>21</v>
@@ -769,7 +769,7 @@
         <v>1.25</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="K2" t="n">
         <v>9.6</v>
@@ -781,7 +781,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.15</v>
@@ -796,16 +796,16 @@
         <v>1.74</v>
       </c>
       <c r="S2" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
         <v>1.05</v>
@@ -835,13 +835,13 @@
         <v>14.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AG2" t="n">
         <v>75</v>
       </c>
       <c r="AH2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
@@ -850,77 +850,77 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AL2" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AM2" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN2" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AO2" t="n">
         <v>3.55</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.68</v>
+        <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BC2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD2" t="n">
         <v>2.7</v>
       </c>
-      <c r="BD2" t="n">
-        <v>2.68</v>
-      </c>
       <c r="BE2" t="n">
-        <v>2.68</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -975,16 +975,16 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
         <v>1.53</v>
@@ -993,10 +993,10 @@
         <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>2.36</v>
       </c>
       <c r="V3" t="n">
         <v>1.9</v>
@@ -1005,116 +1005,116 @@
         <v>1.26</v>
       </c>
       <c r="X3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI3" t="n">
         <v>34</v>
       </c>
-      <c r="Y3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>40</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AK3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.97</v>
+        <v>3.35</v>
       </c>
       <c r="AR3" t="n">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.04</v>
+        <v>3.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.04</v>
+        <v>3.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.08</v>
+        <v>3.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.16</v>
+        <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.12</v>
+        <v>3.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.12</v>
+        <v>3.95</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="H4" t="n">
         <v>1.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
@@ -1163,152 +1163,152 @@
         <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
         <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="G6" t="n">
         <v>6.8</v>
@@ -1542,7 +1542,7 @@
         <v>1.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="J6" t="n">
         <v>4.4</v>
@@ -1563,16 +1563,16 @@
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
@@ -1581,19 +1581,19 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
         <v>15.5</v>
@@ -1617,7 +1617,7 @@
         <v>25</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
         <v>38</v>
@@ -1629,7 +1629,7 @@
         <v>100</v>
       </c>
       <c r="AL6" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AM6" t="n">
         <v>140</v>
@@ -1653,10 +1653,10 @@
         <v>13.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
         <v>9.199999999999999</v>
@@ -1665,10 +1665,10 @@
         <v>15.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
         <v>21</v>
@@ -1692,11 +1692,11 @@
         <v>40</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>1.89</v>
       </c>
       <c r="I7" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
         <v>3.15</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>2.52</v>
       </c>
       <c r="G8" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
         <v>2.86</v>
@@ -1933,10 +1933,10 @@
         <v>4.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.98</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -2133,13 +2133,13 @@
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
@@ -2151,10 +2151,10 @@
         <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
         <v>1.61</v>
@@ -2259,13 +2259,13 @@
         <v>38</v>
       </c>
       <c r="BB9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE9" t="n">
         <v>44</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
@@ -2342,7 +2342,7 @@
         <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R10" t="n">
         <v>1.6</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>3.7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.08</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.1</v>
       </c>
       <c r="J11" t="n">
         <v>3.95</v>
@@ -2533,13 +2533,13 @@
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
         <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
         <v>2.56</v>
@@ -2560,16 +2560,16 @@
         <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA11" t="n">
         <v>26</v>
       </c>
       <c r="AB11" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC11" t="n">
         <v>9.4</v>
@@ -2578,13 +2578,13 @@
         <v>10.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
         <v>15.5</v>
@@ -2596,10 +2596,10 @@
         <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM11" t="n">
         <v>60</v>
@@ -2623,19 +2623,19 @@
         <v>22</v>
       </c>
       <c r="AT11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW11" t="n">
         <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AY11" t="n">
         <v>13.5</v>
@@ -2650,23 +2650,23 @@
         <v>50</v>
       </c>
       <c r="BC11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE11" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BF11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H12" t="n">
         <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
         <v>2.96</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H13" t="n">
         <v>4.3</v>
@@ -2903,10 +2903,10 @@
         <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>3.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J16" t="n">
         <v>3.4</v>
@@ -3503,22 +3503,22 @@
         <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
         <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
         <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
         <v>60</v>
@@ -3581,7 +3581,7 @@
         <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
         <v>12</v>
@@ -3590,7 +3590,7 @@
         <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT16" t="n">
         <v>8.6</v>
@@ -3614,7 +3614,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BB16" t="n">
         <v>21</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H17" t="n">
         <v>6.8</v>
       </c>
       <c r="I17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O17" t="n">
         <v>1.63</v>
@@ -3700,7 +3700,7 @@
         <v>1.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>1.75</v>
       </c>
       <c r="G19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
         <v>5.8</v>
@@ -4079,13 +4079,13 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
         <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q19" t="n">
         <v>1.91</v>
@@ -4100,7 +4100,7 @@
         <v>1.83</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4148,7 +4148,7 @@
         <v>19.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL19" t="n">
         <v>38</v>
@@ -4172,7 +4172,7 @@
         <v>32</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
         <v>7.8</v>
@@ -4184,7 +4184,7 @@
         <v>17</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX19" t="n">
         <v>9.4</v>
@@ -4193,7 +4193,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA19" t="n">
         <v>8.4</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 09:03:27</t>
+          <t>2026-03-09 11:13:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="J2" t="n">
         <v>6.6</v>
       </c>
       <c r="K2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,7 +781,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.15</v>
@@ -796,131 +796,131 @@
         <v>1.74</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AC2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AG2" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AH2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AL2" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AM2" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN2" t="n">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.74</v>
+        <v>5.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -963,7 +963,7 @@
         <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
@@ -984,13 +984,13 @@
         <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="R3" t="n">
         <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="T3" t="n">
         <v>1.58</v>
@@ -1002,7 +1002,7 @@
         <v>1.9</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
         <v>28</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.92</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY4" t="n">
         <v>3.7</v>
       </c>
-      <c r="T4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>1.82</v>
+        <v>3.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.93</v>
+        <v>3.95</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.93</v>
+        <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.93</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.93</v>
+        <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.93</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.93</v>
+        <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.93</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
         <v>1.93</v>
@@ -1581,13 +1581,13 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
         <v>8</v>
@@ -1626,7 +1626,7 @@
         <v>230</v>
       </c>
       <c r="AK6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL6" t="n">
         <v>95</v>
@@ -1638,13 +1638,13 @@
         <v>150</v>
       </c>
       <c r="AO6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR6" t="n">
         <v>8.4</v>
@@ -1653,19 +1653,19 @@
         <v>13.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
         <v>15.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1692,11 +1692,11 @@
         <v>40</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="I7" t="n">
         <v>2.08</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G8" t="n">
         <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I8" t="n">
         <v>4.3</v>
@@ -1936,7 +1936,7 @@
         <v>2.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.98</v>
+        <v>2.68</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>2.72</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,146 +2139,146 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="R9" t="n">
         <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z9" t="n">
         <v>21</v>
       </c>
-      <c r="Z9" t="n">
-        <v>34</v>
-      </c>
       <c r="AA9" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AC9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AF9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>15</v>
-      </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AL9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AM9" t="n">
         <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AP9" t="n">
         <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AT9" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG9" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>28</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="H10" t="n">
-        <v>2.68</v>
+        <v>3.95</v>
       </c>
       <c r="I10" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.6</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.56</v>
-      </c>
       <c r="U10" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
         <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AJ10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM10" t="n">
         <v>60</v>
       </c>
       <c r="AN10" t="n">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>14</v>
       </c>
-      <c r="AR10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA10" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BB10" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BE10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF10" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="BG10" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>3.8</v>
+        <v>500</v>
       </c>
       <c r="H11" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>500</v>
       </c>
       <c r="J11" t="n">
-        <v>3.95</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>1.37</v>
       </c>
       <c r="T11" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,184 +2683,184 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.34</v>
+        <v>3.55</v>
       </c>
       <c r="G12" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>2.12</v>
       </c>
       <c r="I12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K12" t="n">
         <v>4.1</v>
       </c>
-      <c r="J12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>2.44</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.58</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="G13" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K13" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,32 +3076,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.1</v>
       </c>
-      <c r="G14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1000</v>
-      </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,66 +3265,66 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.01</v>
       </c>
-      <c r="N15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.37</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3333,116 +3333,116 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -3464,61 +3464,61 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="G16" t="n">
-        <v>2.34</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="O16" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="T16" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,123 +3527,123 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="G17" t="n">
-        <v>1.81</v>
+        <v>2.34</v>
       </c>
       <c r="H17" t="n">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="I17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
         <v>8</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>2.64</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,201 +4024,783 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 11:13:21</t>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19:45:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:23:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19:45:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Atletico FC Cali</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Orsomarso</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K20" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:23:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Brazilian Serie A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Bahia</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>EC Vitoria Salvador</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F21" t="n">
         <v>1.75</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G21" t="n">
         <v>1.86</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H21" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I21" t="n">
         <v>5.8</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>3.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K21" t="n">
         <v>4.1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1.06</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N21" t="n">
         <v>3.75</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O21" t="n">
         <v>1.3</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="P21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.37</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S21" t="n">
         <v>3.3</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>1.83</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U21" t="n">
         <v>2</v>
       </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y21" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z21" t="n">
         <v>42</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA21" t="n">
         <v>140</v>
       </c>
-      <c r="AB19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AB21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC21" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AD21" t="n">
         <v>21</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH19" t="n">
+      <c r="AG21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH21" t="n">
         <v>21</v>
       </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>19.5</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AK21" t="n">
         <v>19.5</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AL21" t="n">
         <v>38</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AM21" t="n">
         <v>120</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AN21" t="n">
         <v>12</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AO21" t="n">
         <v>100</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AP21" t="n">
         <v>13</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AQ21" t="n">
         <v>15</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AR21" t="n">
         <v>32</v>
       </c>
-      <c r="AS19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT19" t="n">
+      <c r="AS21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT21" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AU21" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AV21" t="n">
         <v>17</v>
       </c>
-      <c r="AW19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX19" t="n">
+      <c r="AW21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX21" t="n">
         <v>9.4</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="AY21" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="AZ21" t="n">
         <v>17.5</v>
       </c>
-      <c r="BA19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB19" t="n">
+      <c r="BA21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB21" t="n">
         <v>16</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BC21" t="n">
         <v>16</v>
       </c>
-      <c r="BD19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF19" t="n">
+      <c r="BD21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF21" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BG19" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-03-09 11:13:21</t>
+      <c r="BG21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:23:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Independiente Yumbo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>500</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>500</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K22" t="n">
+        <v>950</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:23:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -772,7 +772,7 @@
         <v>6.6</v>
       </c>
       <c r="K2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -790,7 +790,7 @@
         <v>2.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R2" t="n">
         <v>1.74</v>
@@ -874,7 +874,7 @@
         <v>6.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>5.1</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G4" t="n">
         <v>7.4</v>
@@ -1193,7 +1193,7 @@
         <v>1.86</v>
       </c>
       <c r="V4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="W4" t="n">
         <v>1.15</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>3.45</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J5" t="n">
         <v>3.95</v>
@@ -1357,152 +1357,152 @@
         <v>5.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
         <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -1551,13 +1551,13 @@
         <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
@@ -1581,28 +1581,28 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB6" t="n">
         <v>21</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>9.800000000000001</v>
@@ -1623,10 +1623,10 @@
         <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AK6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL6" t="n">
         <v>95</v>
@@ -1635,7 +1635,7 @@
         <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO6" t="n">
         <v>9.199999999999999</v>
@@ -1653,7 +1653,7 @@
         <v>13.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AU6" t="n">
         <v>8.800000000000001</v>
@@ -1665,10 +1665,10 @@
         <v>15.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
         <v>21</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="I7" t="n">
         <v>2.08</v>
@@ -1760,7 +1760,7 @@
         <v>1.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="G8" t="n">
         <v>3.6</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.72</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.72</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,146 +2139,146 @@
         <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.61</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.55</v>
-      </c>
       <c r="U9" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="X9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD9" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE9" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM9" t="n">
         <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>14</v>
       </c>
-      <c r="AR9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC9" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG9" t="n">
         <v>28</v>
       </c>
-      <c r="BF9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>2.04</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>3.95</v>
+        <v>2.68</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,146 +2333,146 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U10" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AM10" t="n">
         <v>60</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.6</v>
+        <v>15.5</v>
       </c>
       <c r="AO10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS10" t="n">
         <v>32</v>
       </c>
-      <c r="AP10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AT10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX10" t="n">
         <v>18</v>
       </c>
-      <c r="AR10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="AY10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>28</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -2530,19 +2530,19 @@
         <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
         <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="R11" t="n">
         <v>1.13</v>
       </c>
       <c r="S11" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>3.55</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I12" t="n">
         <v>2.12</v>
       </c>
-      <c r="I12" t="n">
-        <v>2.14</v>
-      </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
@@ -2727,7 +2727,7 @@
         <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
         <v>1.66</v>
@@ -2742,13 +2742,13 @@
         <v>1.59</v>
       </c>
       <c r="U12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
         <v>22</v>
@@ -2757,7 +2757,7 @@
         <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA12" t="n">
         <v>26</v>
@@ -2781,7 +2781,7 @@
         <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
         <v>28</v>
@@ -2817,10 +2817,10 @@
         <v>23</v>
       </c>
       <c r="AT12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV12" t="n">
         <v>9.800000000000001</v>
@@ -2829,7 +2829,7 @@
         <v>17.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY12" t="n">
         <v>13.5</v>
@@ -2841,7 +2841,7 @@
         <v>25</v>
       </c>
       <c r="BB12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC12" t="n">
         <v>32</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>2.34</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H13" t="n">
         <v>3.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
@@ -3464,61 +3464,61 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.4</v>
+        <v>2.28</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J16" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.6</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.03</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,123 +3527,123 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,61 +3658,61 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.34</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.87</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,123 +3721,123 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3885,16 +3885,16 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.02</v>
+        <v>2.96</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.81</v>
+        <v>5.5</v>
       </c>
       <c r="H19" t="n">
-        <v>6.8</v>
+        <v>2.28</v>
       </c>
       <c r="I19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K19" t="n">
         <v>8</v>
       </c>
-      <c r="J19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
@@ -4079,16 +4079,16 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,66 +4235,66 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="G20" t="n">
-        <v>5.5</v>
+        <v>1.86</v>
       </c>
       <c r="H20" t="n">
-        <v>2.28</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
-        <v>2.64</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,123 +4303,123 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,373 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1.86</v>
+        <v>500</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>5.8</v>
+        <v>500</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>1.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 13:23:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Independiente Yumbo</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Barranquilla</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G22" t="n">
-        <v>500</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I22" t="n">
-        <v>500</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K22" t="n">
-        <v>950</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>2026-03-09 13:23:49</t>
+          <t>2026-03-09 15:32:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -775,7 +775,7 @@
         <v>9.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -787,22 +787,22 @@
         <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S2" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V2" t="n">
         <v>5.1</v>
@@ -811,22 +811,22 @@
         <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y2" t="n">
         <v>13</v>
       </c>
       <c r="Z2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>10.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="AC2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD2" t="n">
         <v>14.5</v>
@@ -838,7 +838,7 @@
         <v>210</v>
       </c>
       <c r="AG2" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AH2" t="n">
         <v>44</v>
@@ -862,25 +862,25 @@
         <v>450</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS2" t="n">
         <v>7.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV2" t="n">
         <v>9.6</v>
@@ -892,35 +892,35 @@
         <v>5.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ2" t="n">
         <v>4.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC2" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
         <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
         <v>1.87</v>
@@ -963,7 +963,7 @@
         <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
         <v>4.6</v>
@@ -978,7 +978,7 @@
         <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
         <v>2.32</v>
@@ -990,7 +990,7 @@
         <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T3" t="n">
         <v>1.58</v>
@@ -999,7 +999,7 @@
         <v>2.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W3" t="n">
         <v>1.3</v>
@@ -1011,7 +1011,7 @@
         <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
         <v>28</v>
@@ -1059,46 +1059,46 @@
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.7</v>
+        <v>18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.35</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.7</v>
+        <v>16.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="AX3" t="n">
         <v>3.85</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.8</v>
+        <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BD3" t="n">
         <v>3.95</v>
@@ -1107,14 +1107,14 @@
         <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -1199,37 +1199,37 @@
         <v>1.15</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Y4" t="n">
         <v>9.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AA4" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AB4" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE4" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="AF4" t="n">
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="AH4" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1253,31 +1253,31 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
         <v>3.7</v>
@@ -1298,17 +1298,17 @@
         <v>4.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -1339,28 +1339,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G5" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
         <v>4.9</v>
@@ -1369,34 +1369,34 @@
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="Q5" t="n">
         <v>1.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V5" t="n">
         <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X5" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="Y5" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
@@ -1405,104 +1405,104 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="AC5" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>28</v>
+        <v>980</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.88</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.87</v>
+        <v>4.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.79</v>
+        <v>3.85</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.75</v>
+        <v>3.65</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.84</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.98</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.75</v>
+        <v>3.65</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.98</v>
+        <v>4.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.98</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.98</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -1542,10 +1542,10 @@
         <v>1.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
         <v>4.5</v>
@@ -1557,22 +1557,22 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
         <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
@@ -1581,7 +1581,7 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
@@ -1593,7 +1593,7 @@
         <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
         <v>15</v>
@@ -1647,16 +1647,16 @@
         <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
         <v>19.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
         <v>9.4</v>
@@ -1680,7 +1680,7 @@
         <v>46</v>
       </c>
       <c r="BC6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BD6" t="n">
         <v>80</v>
@@ -1689,14 +1689,14 @@
         <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -1733,164 +1733,164 @@
         <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P7" t="n">
         <v>1.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -1924,167 +1924,167 @@
         <v>2.62</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P8" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -2121,19 +2121,19 @@
         <v>2.02</v>
       </c>
       <c r="H9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I9" t="n">
         <v>4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.1</v>
       </c>
       <c r="J9" t="n">
         <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2157,13 +2157,13 @@
         <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
         <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
         <v>1.98</v>
@@ -2184,16 +2184,16 @@
         <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE9" t="n">
         <v>40</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
         <v>10.5</v>
@@ -2211,7 +2211,7 @@
         <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM9" t="n">
         <v>60</v>
@@ -2220,31 +2220,31 @@
         <v>9.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP9" t="n">
         <v>19.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR9" t="n">
         <v>29</v>
       </c>
       <c r="AS9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
         <v>14.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX9" t="n">
         <v>13.5</v>
@@ -2253,19 +2253,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA9" t="n">
         <v>38</v>
       </c>
       <c r="BB9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC9" t="n">
         <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE9" t="n">
         <v>50</v>
@@ -2274,11 +2274,11 @@
         <v>9</v>
       </c>
       <c r="BG9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
         <v>2.68</v>
@@ -2321,13 +2321,13 @@
         <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
         <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
@@ -2363,7 +2363,7 @@
         <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
         <v>16</v>
@@ -2381,16 +2381,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>14.5</v>
@@ -2420,16 +2420,16 @@
         <v>20</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
         <v>8.4</v>
@@ -2438,10 +2438,10 @@
         <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY10" t="n">
         <v>11</v>
@@ -2450,7 +2450,7 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BB10" t="n">
         <v>32</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>500</v>
+        <v>2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>500</v>
+        <v>5.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
         <v>1.41</v>
@@ -2542,7 +2542,7 @@
         <v>1.13</v>
       </c>
       <c r="S11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,122 +2551,122 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>3.55</v>
       </c>
       <c r="G12" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -2715,7 +2715,7 @@
         <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -2751,40 +2751,40 @@
         <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB12" t="n">
         <v>18</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
         <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ12" t="n">
         <v>65</v>
@@ -2793,13 +2793,13 @@
         <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
         <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO12" t="n">
         <v>10.5</v>
@@ -2808,59 +2808,59 @@
         <v>19.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY12" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
         <v>25</v>
       </c>
       <c r="BB12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD12" t="n">
         <v>34</v>
       </c>
       <c r="BE12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G13" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H13" t="n">
         <v>3.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.16</v>
       </c>
       <c r="G14" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H14" t="n">
         <v>4.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
         <v>3.65</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
         <v>3.65</v>
@@ -3518,7 +3518,7 @@
         <v>1.79</v>
       </c>
       <c r="U16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA16" t="n">
         <v>65</v>
@@ -3548,7 +3548,7 @@
         <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
         <v>16.5</v>
@@ -3575,13 +3575,13 @@
         <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>11.5</v>
@@ -3590,7 +3590,7 @@
         <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
         <v>8.800000000000001</v>
@@ -3602,7 +3602,7 @@
         <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX16" t="n">
         <v>12.5</v>
@@ -3614,7 +3614,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
         <v>23</v>
@@ -3626,7 +3626,7 @@
         <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF16" t="n">
         <v>16.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.68</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -4273,16 +4273,16 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
         <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
         <v>1.37</v>
@@ -4318,7 +4318,7 @@
         <v>8.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
         <v>21</v>
@@ -4354,7 +4354,7 @@
         <v>12</v>
       </c>
       <c r="AO20" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
         <v>13</v>
@@ -4366,7 +4366,7 @@
         <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
@@ -4378,7 +4378,7 @@
         <v>17</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
@@ -4390,7 +4390,7 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
         <v>16</v>
@@ -4399,20 +4399,20 @@
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>
@@ -4470,19 +4470,19 @@
         <v>1.03</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
         <v>1.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R21" t="n">
         <v>1.08</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 15:32:54</t>
+          <t>2026-03-09 17:40:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -760,7 +760,7 @@
         <v>16.5</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -787,22 +787,22 @@
         <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q2" t="n">
         <v>1.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="T2" t="n">
         <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V2" t="n">
         <v>5.1</v>
@@ -823,7 +823,7 @@
         <v>10.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AC2" t="n">
         <v>21</v>
@@ -838,7 +838,7 @@
         <v>210</v>
       </c>
       <c r="AG2" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AH2" t="n">
         <v>44</v>
@@ -853,34 +853,34 @@
         <v>340</v>
       </c>
       <c r="AL2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AM2" t="n">
         <v>230</v>
       </c>
       <c r="AN2" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AO2" t="n">
         <v>3.95</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AR2" t="n">
         <v>7.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
         <v>5.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AV2" t="n">
         <v>9.6</v>
@@ -889,38 +889,38 @@
         <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.6</v>
       </c>
-      <c r="BC2" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J3" t="n">
         <v>3.85</v>
@@ -978,31 +978,31 @@
         <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q3" t="n">
         <v>1.59</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U3" t="n">
         <v>2.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
         <v>28</v>
@@ -1011,7 +1011,7 @@
         <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA3" t="n">
         <v>28</v>
@@ -1059,28 +1059,28 @@
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT3" t="n">
         <v>16.5</v>
       </c>
-      <c r="AT3" t="n">
-        <v>14</v>
-      </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX3" t="n">
         <v>3.85</v>
@@ -1089,16 +1089,16 @@
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
         <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD3" t="n">
         <v>3.95</v>
@@ -1107,14 +1107,14 @@
         <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG3" t="n">
         <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
         <v>2.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
         <v>980</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>1.89</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -1465,7 +1465,7 @@
         <v>3.65</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW5" t="n">
         <v>4.5</v>
@@ -1477,7 +1477,7 @@
         <v>3.65</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
         <v>4.5</v>
@@ -1486,7 +1486,7 @@
         <v>4</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
         <v>4.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -1539,40 +1539,40 @@
         <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I6" t="n">
         <v>1.62</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
         <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
@@ -1590,7 +1590,7 @@
         <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
         <v>9</v>
@@ -1605,7 +1605,7 @@
         <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE6" t="n">
         <v>16.5</v>
@@ -1626,7 +1626,7 @@
         <v>200</v>
       </c>
       <c r="AK6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL6" t="n">
         <v>95</v>
@@ -1635,7 +1635,7 @@
         <v>140</v>
       </c>
       <c r="AN6" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO6" t="n">
         <v>9.199999999999999</v>
@@ -1680,7 +1680,7 @@
         <v>46</v>
       </c>
       <c r="BC6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BD6" t="n">
         <v>80</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>1.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.15</v>
@@ -1772,7 +1772,7 @@
         <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
         <v>1.96</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AW7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AY7" t="n">
         <v>2.06</v>
       </c>
-      <c r="AX7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G8" t="n">
         <v>3.05</v>
@@ -1966,7 +1966,7 @@
         <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V8" t="n">
         <v>1.37</v>
@@ -2032,31 +2032,31 @@
         <v>2.16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AR8" t="n">
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AT8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AU8" t="n">
         <v>1.77</v>
       </c>
-      <c r="AU8" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AV8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AZ8" t="n">
         <v>2.04</v>
@@ -2065,10 +2065,10 @@
         <v>2.16</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BD8" t="n">
         <v>2.16</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -2118,10 +2118,10 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I9" t="n">
         <v>4</v>
@@ -2166,7 +2166,7 @@
         <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X9" t="n">
         <v>21</v>
@@ -2184,13 +2184,13 @@
         <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
         <v>15.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF9" t="n">
         <v>14.5</v>
@@ -2220,7 +2220,7 @@
         <v>9.6</v>
       </c>
       <c r="AO9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
         <v>19.5</v>
@@ -2232,7 +2232,7 @@
         <v>29</v>
       </c>
       <c r="AS9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT9" t="n">
         <v>12</v>
@@ -2247,7 +2247,7 @@
         <v>36</v>
       </c>
       <c r="AX9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
         <v>9.800000000000001</v>
@@ -2259,7 +2259,7 @@
         <v>38</v>
       </c>
       <c r="BB9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC9" t="n">
         <v>16.5</v>
@@ -2271,14 +2271,14 @@
         <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG9" t="n">
         <v>26</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
         <v>2.68</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
         <v>3.9</v>
@@ -2384,7 +2384,7 @@
         <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
@@ -2393,10 +2393,10 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ10" t="n">
         <v>38</v>
@@ -2405,7 +2405,7 @@
         <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
         <v>60</v>
@@ -2414,7 +2414,7 @@
         <v>15.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP10" t="n">
         <v>20</v>
@@ -2432,7 +2432,7 @@
         <v>15</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV10" t="n">
         <v>11</v>
@@ -2441,13 +2441,13 @@
         <v>22</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY10" t="n">
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
         <v>27</v>
@@ -2465,14 +2465,14 @@
         <v>44</v>
       </c>
       <c r="BF10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG10" t="n">
         <v>14</v>
       </c>
-      <c r="BG10" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="H11" t="n">
         <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2536,13 +2536,13 @@
         <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="R11" t="n">
         <v>1.13</v>
       </c>
       <c r="S11" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,88 +2551,88 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="X11" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Y11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z11" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AB11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AC11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI11" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="n">
         <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AN11" t="n">
         <v>46</v>
       </c>
       <c r="AO11" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.8</v>
+        <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AX11" t="n">
         <v>9.6</v>
@@ -2641,32 +2641,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -2703,10 +2703,10 @@
         <v>3.6</v>
       </c>
       <c r="H12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I12" t="n">
         <v>2.12</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.14</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -2724,7 +2724,7 @@
         <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P12" t="n">
         <v>2.46</v>
@@ -2748,25 +2748,25 @@
         <v>1.89</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
         <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
         <v>15.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB12" t="n">
         <v>18</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>10.5</v>
@@ -2775,7 +2775,7 @@
         <v>19</v>
       </c>
       <c r="AF12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
         <v>14.5</v>
@@ -2823,10 +2823,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX12" t="n">
         <v>26</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
         <v>3.6</v>
@@ -2903,22 +2903,22 @@
         <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K13" t="n">
         <v>3.35</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P13" t="n">
         <v>1.51</v>
@@ -2927,134 +2927,134 @@
         <v>2.58</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>2.84</v>
@@ -3103,152 +3103,152 @@
         <v>3.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P14" t="n">
         <v>1.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I16" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -3503,7 +3503,7 @@
         <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
         <v>2</v>
@@ -3518,43 +3518,43 @@
         <v>1.79</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y16" t="n">
         <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF16" t="n">
         <v>15</v>
       </c>
-      <c r="AE16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>18</v>
@@ -3563,22 +3563,22 @@
         <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK16" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP16" t="n">
         <v>12.5</v>
@@ -3587,56 +3587,56 @@
         <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU16" t="n">
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BB16" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BC16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BD16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG16" t="n">
         <v>32</v>
       </c>
-      <c r="BE16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>34</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
         <v>1.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G20" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
         <v>5.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
         <v>4.1</v>
@@ -4288,13 +4288,13 @@
         <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T20" t="n">
         <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4366,7 +4366,7 @@
         <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
@@ -4378,19 +4378,19 @@
         <v>17</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB20" t="n">
         <v>16</v>
@@ -4399,20 +4399,20 @@
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 17:40:48</t>
+          <t>2026-03-09 19:47:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="J2" t="n">
         <v>6.6</v>
       </c>
       <c r="K2" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.21</v>
@@ -793,10 +793,10 @@
         <v>1.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="T2" t="n">
         <v>2.14</v>
@@ -805,34 +805,34 @@
         <v>1.73</v>
       </c>
       <c r="V2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="Y2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AB2" t="n">
         <v>950</v>
       </c>
       <c r="AC2" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE2" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>16.5</v>
       </c>
       <c r="AF2" t="n">
         <v>210</v>
@@ -841,10 +841,10 @@
         <v>950</v>
       </c>
       <c r="AH2" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>440</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>9.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS2" t="n">
         <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
         <v>15.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>11</v>
       </c>
-      <c r="AX2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H3" t="n">
         <v>1.88</v>
@@ -963,10 +963,10 @@
         <v>2.08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.25</v>
@@ -984,7 +984,7 @@
         <v>2.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R3" t="n">
         <v>1.54</v>
@@ -999,122 +999,122 @@
         <v>2.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="W3" t="n">
         <v>1.26</v>
       </c>
       <c r="X3" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE3" t="n">
         <v>28</v>
       </c>
-      <c r="Y3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AF3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG3" t="n">
         <v>24</v>
       </c>
-      <c r="AC3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>23</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>40</v>
       </c>
-      <c r="AG3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>34</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AO3" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>19</v>
+        <v>2.56</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>2.44</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>2.56</v>
       </c>
       <c r="AT3" t="n">
-        <v>16.5</v>
+        <v>2.52</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="AW3" t="n">
-        <v>15.5</v>
+        <v>2.52</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>2.48</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>2.46</v>
       </c>
       <c r="BA3" t="n">
-        <v>20</v>
+        <v>2.58</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.95</v>
+        <v>2.64</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.95</v>
+        <v>2.64</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.85</v>
+        <v>18.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>1.88</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>4.7</v>
@@ -1178,22 +1178,22 @@
         <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
         <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="W4" t="n">
         <v>1.18</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -1339,28 +1339,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="H5" t="n">
         <v>3.85</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
         <v>4.9</v>
@@ -1369,10 +1369,10 @@
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
         <v>1.61</v>
@@ -1390,13 +1390,13 @@
         <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
@@ -1405,43 +1405,43 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1450,59 +1450,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
         <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -1641,7 +1641,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>7.6</v>
@@ -1665,10 +1665,10 @@
         <v>15.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AY6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
         <v>21</v>
@@ -1689,14 +1689,14 @@
         <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BG6" t="n">
         <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -1736,10 +1736,10 @@
         <v>1.85</v>
       </c>
       <c r="I7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
@@ -1748,149 +1748,149 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>1.54</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
         <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W7" t="n">
         <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AR7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AS7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX7" t="n">
         <v>32</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AY7" t="n">
         <v>18.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>2.08</v>
+        <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.16</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.2</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -1942,19 +1942,19 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="O8" t="n">
         <v>1.13</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
@@ -1963,19 +1963,19 @@
         <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U8" t="n">
         <v>1.47</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
         <v>11.5</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.82</v>
+        <v>2.38</v>
       </c>
       <c r="AR8" t="n">
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.12</v>
+        <v>2.92</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.98</v>
+        <v>2.66</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.12</v>
+        <v>2.92</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.04</v>
+        <v>2.76</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
         <v>3.95</v>
@@ -2130,10 +2130,10 @@
         <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2148,13 +2148,13 @@
         <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R9" t="n">
         <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
         <v>1.6</v>
@@ -2166,7 +2166,7 @@
         <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X9" t="n">
         <v>21</v>
@@ -2190,7 +2190,7 @@
         <v>15.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
         <v>14.5</v>
@@ -2205,7 +2205,7 @@
         <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
@@ -2217,13 +2217,13 @@
         <v>60</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
         <v>18.5</v>
@@ -2232,7 +2232,7 @@
         <v>29</v>
       </c>
       <c r="AS9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT9" t="n">
         <v>12</v>
@@ -2241,13 +2241,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
         <v>36</v>
       </c>
       <c r="AX9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY9" t="n">
         <v>9.800000000000001</v>
@@ -2259,10 +2259,10 @@
         <v>38</v>
       </c>
       <c r="BB9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
         <v>25</v>
@@ -2271,14 +2271,14 @@
         <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G10" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.72</v>
       </c>
       <c r="H10" t="n">
         <v>2.68</v>
@@ -2327,7 +2327,7 @@
         <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
@@ -2342,13 +2342,13 @@
         <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R10" t="n">
         <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="T10" t="n">
         <v>1.55</v>
@@ -2366,7 +2366,7 @@
         <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
         <v>21</v>
@@ -2375,7 +2375,7 @@
         <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
@@ -2396,25 +2396,25 @@
         <v>14</v>
       </c>
       <c r="AI10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ10" t="n">
         <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
         <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN10" t="n">
         <v>15.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP10" t="n">
         <v>20</v>
@@ -2426,31 +2426,31 @@
         <v>19</v>
       </c>
       <c r="AS10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV10" t="n">
         <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY10" t="n">
         <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB10" t="n">
         <v>32</v>
@@ -2459,20 +2459,20 @@
         <v>22</v>
       </c>
       <c r="BD10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE10" t="n">
         <v>44</v>
       </c>
       <c r="BF10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG10" t="n">
         <v>14</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -2509,13 +2509,13 @@
         <v>2.48</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="K11" t="n">
         <v>3.35</v>
@@ -2524,31 +2524,31 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>1.45</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="V11" t="n">
         <v>1.31</v>
@@ -2557,116 +2557,116 @@
         <v>1.67</v>
       </c>
       <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
         <v>34</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>38</v>
       </c>
       <c r="AL11" t="n">
         <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>260</v>
+        <v>410</v>
       </c>
       <c r="AN11" t="n">
         <v>46</v>
       </c>
       <c r="AO11" t="n">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.02</v>
+        <v>4.9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.04</v>
+        <v>9.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.96</v>
+        <v>4.6</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB11" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BC11" t="n">
-        <v>2.04</v>
+        <v>3.75</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.14</v>
+        <v>4.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I12" t="n">
         <v>2.1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.12</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -2715,19 +2715,19 @@
         <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
         <v>1.66</v>
@@ -2736,7 +2736,7 @@
         <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
         <v>1.59</v>
@@ -2745,10 +2745,10 @@
         <v>2.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
         <v>21</v>
@@ -2763,7 +2763,7 @@
         <v>26</v>
       </c>
       <c r="AB12" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC12" t="n">
         <v>9.199999999999999</v>
@@ -2772,13 +2772,13 @@
         <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF12" t="n">
         <v>29</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
@@ -2805,7 +2805,7 @@
         <v>10.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ12" t="n">
         <v>12</v>
@@ -2820,7 +2820,7 @@
         <v>17</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV12" t="n">
         <v>9.800000000000001</v>
@@ -2844,7 +2844,7 @@
         <v>50</v>
       </c>
       <c r="BC12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD12" t="n">
         <v>34</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
         <v>2.96</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
         <v>1.55</v>
@@ -2915,37 +2915,37 @@
         <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>1.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S13" t="n">
         <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
         <v>15</v>
@@ -3002,59 +3002,59 @@
         <v>2.12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="AR13" t="n">
         <v>17</v>
       </c>
       <c r="AS13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT13" t="n">
         <v>2.12</v>
       </c>
-      <c r="AT13" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AU13" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.92</v>
+        <v>2.34</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.04</v>
+        <v>2.54</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
         <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P14" t="n">
         <v>1.47</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.46</v>
-      </c>
       <c r="Q14" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="R14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S14" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
         <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ14" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK14" t="n">
         <v>38</v>
       </c>
       <c r="AL14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>21</v>
+        <v>5.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.04</v>
+        <v>5.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.08</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.36</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.58</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.82</v>
+        <v>6.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.62</v>
+        <v>5.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>24</v>
+        <v>5.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.72</v>
+        <v>5.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.82</v>
+        <v>6.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="G15" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="I15" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,22 +3303,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="P15" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="R15" t="n">
         <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3327,10 +3327,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>2.26</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H16" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
         <v>3.55</v>
@@ -3488,7 +3488,7 @@
         <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
         <v>1.4</v>
@@ -3503,7 +3503,7 @@
         <v>1.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
         <v>2</v>
@@ -3524,7 +3524,7 @@
         <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X16" t="n">
         <v>13.5</v>
@@ -3533,25 +3533,25 @@
         <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
         <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3563,19 +3563,19 @@
         <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK16" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM16" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>42</v>
@@ -3590,7 +3590,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT16" t="n">
         <v>9</v>
@@ -3602,10 +3602,10 @@
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
         <v>27</v>
@@ -3626,17 +3626,17 @@
         <v>34</v>
       </c>
       <c r="BE16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BF16" t="n">
         <v>17</v>
       </c>
       <c r="BG16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="G17" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I17" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
         <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,40 +3691,40 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3733,10 +3733,10 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -3745,10 +3745,10 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
         <v>1000</v>
@@ -3757,7 +3757,7 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>2.82</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>3.05</v>
       </c>
       <c r="AR17" t="n">
-        <v>28</v>
+        <v>3.45</v>
       </c>
       <c r="AS17" t="n">
-        <v>50</v>
+        <v>3.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>5.7</v>
+        <v>2.44</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>2.66</v>
       </c>
       <c r="AV17" t="n">
-        <v>18.5</v>
+        <v>3.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>50</v>
+        <v>3.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>2.82</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19.5</v>
+        <v>3.25</v>
       </c>
       <c r="BA17" t="n">
-        <v>50</v>
+        <v>3.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>3.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>17.5</v>
+        <v>3.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>34</v>
+        <v>3.45</v>
       </c>
       <c r="BE17" t="n">
-        <v>50</v>
+        <v>3.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -3879,16 +3879,16 @@
         <v>3.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.32</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="P18" t="n">
         <v>1.43</v>
@@ -3897,134 +3897,134 @@
         <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="G19" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G20" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H20" t="n">
         <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J20" t="n">
         <v>3.75</v>
@@ -4267,28 +4267,28 @@
         <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
         <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
         <v>1.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
         <v>1.83</v>
@@ -4297,22 +4297,22 @@
         <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X20" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB20" t="n">
         <v>8.6</v>
@@ -4321,13 +4321,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG20" t="n">
         <v>10.5</v>
@@ -4339,19 +4339,19 @@
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
         <v>19.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
@@ -4360,13 +4360,13 @@
         <v>13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
@@ -4375,10 +4375,10 @@
         <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW20" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
@@ -4390,29 +4390,29 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC20" t="n">
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="G21" t="n">
-        <v>500</v>
+        <v>1.81</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I21" t="n">
-        <v>500</v>
+        <v>8.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.08</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.34</v>
+        <v>1.99</v>
       </c>
       <c r="R21" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>1.34</v>
+        <v>3.35</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 19:47:56</t>
+          <t>2026-03-09 21:54:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -760,7 +760,7 @@
         <v>14.5</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
         <v>1.88</v>
@@ -1002,28 +1002,28 @@
         <v>1.92</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y3" t="n">
         <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
         <v>28</v>
@@ -1044,67 +1044,67 @@
         <v>100</v>
       </c>
       <c r="AK3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL3" t="n">
         <v>980</v>
       </c>
-      <c r="AL3" t="n">
-        <v>65</v>
-      </c>
       <c r="AM3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AO3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.44</v>
+        <v>2.86</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.52</v>
+        <v>15.5</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.52</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.46</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="BF3" t="n">
         <v>18.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J4" t="n">
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.35</v>
@@ -1187,16 +1187,16 @@
         <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X4" t="n">
         <v>980</v>
@@ -1256,59 +1256,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="AX4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE4" t="n">
         <v>4</v>
       </c>
-      <c r="AY4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BF4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG4" t="n">
         <v>3.95</v>
       </c>
-      <c r="BB4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="H5" t="n">
         <v>3.85</v>
@@ -1387,7 +1387,7 @@
         <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="G6" t="n">
         <v>6.8</v>
       </c>
       <c r="H6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.61</v>
       </c>
-      <c r="I6" t="n">
-        <v>1.62</v>
-      </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
         <v>4.5</v>
@@ -1581,7 +1581,7 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
@@ -1602,7 +1602,7 @@
         <v>21</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>9.6</v>
@@ -1626,7 +1626,7 @@
         <v>200</v>
       </c>
       <c r="AK6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL6" t="n">
         <v>95</v>
@@ -1650,7 +1650,7 @@
         <v>8.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT6" t="n">
         <v>19.5</v>
@@ -1689,14 +1689,14 @@
         <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BG6" t="n">
         <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
         <v>2.66</v>
@@ -1769,7 +1769,7 @@
         <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
         <v>1.72</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -1942,13 +1942,13 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N8" t="n">
         <v>1.31</v>
       </c>
       <c r="O8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P8" t="n">
         <v>1.3</v>
@@ -1963,10 +1963,10 @@
         <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
         <v>1.34</v>
@@ -1975,7 +1975,7 @@
         <v>1.42</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
         <v>11.5</v>
@@ -2032,59 +2032,59 @@
         <v>2.18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AR8" t="n">
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.92</v>
+        <v>2.14</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.28</v>
+        <v>1.78</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.92</v>
+        <v>2.14</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.76</v>
+        <v>2.04</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="BD8" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="BE8" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="BF8" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="BG8" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I10" t="n">
         <v>2.72</v>
@@ -2468,11 +2468,11 @@
         <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G11" t="n">
         <v>2.48</v>
@@ -2542,7 +2542,7 @@
         <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
         <v>1.98</v>
@@ -2611,7 +2611,7 @@
         <v>400</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>5.4</v>
@@ -2641,7 +2641,7 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
         <v>4.1</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>3.6</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I12" t="n">
         <v>2.1</v>
@@ -2751,7 +2751,7 @@
         <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
         <v>13</v>
@@ -2841,7 +2841,7 @@
         <v>25</v>
       </c>
       <c r="BB12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC12" t="n">
         <v>32</v>
@@ -2856,11 +2856,11 @@
         <v>23</v>
       </c>
       <c r="BG12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
         <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
         <v>2.48</v>
@@ -2933,10 +2933,10 @@
         <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
         <v>1.3</v>
@@ -2945,7 +2945,7 @@
         <v>1.61</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
         <v>15</v>
@@ -3002,59 +3002,59 @@
         <v>2.12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="AR13" t="n">
         <v>17</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="AT13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA13" t="n">
         <v>2.12</v>
       </c>
-      <c r="AU13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BB13" t="n">
-        <v>2.54</v>
+        <v>2.04</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G14" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H14" t="n">
         <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K14" t="n">
         <v>3.15</v>
@@ -3124,7 +3124,7 @@
         <v>1.17</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T14" t="n">
         <v>2.26</v>
@@ -3136,13 +3136,13 @@
         <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X14" t="n">
         <v>7.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
         <v>34</v>
@@ -3199,13 +3199,13 @@
         <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
@@ -3214,7 +3214,7 @@
         <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3229,26 +3229,26 @@
         <v>6.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF14" t="n">
         <v>5.5</v>
       </c>
-      <c r="BD14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I15" t="n">
         <v>2.04</v>
@@ -3306,7 +3306,7 @@
         <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P15" t="n">
         <v>1.59</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
         <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF16" t="n">
         <v>14.5</v>
@@ -3578,7 +3578,7 @@
         <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP16" t="n">
         <v>12.5</v>
@@ -3590,7 +3590,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT16" t="n">
         <v>9</v>
@@ -3614,7 +3614,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BB16" t="n">
         <v>27</v>
@@ -3626,7 +3626,7 @@
         <v>34</v>
       </c>
       <c r="BE16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BF16" t="n">
         <v>17</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>1.86</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
         <v>7.4</v>
@@ -3691,28 +3691,28 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U17" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="V17" t="n">
         <v>1.15</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G18" t="n">
         <v>1.81</v>
@@ -3912,13 +3912,13 @@
         <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,104 +3927,104 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
         <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -4076,37 +4076,37 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="P19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" t="n">
         <v>2.34</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S19" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
         <v>3.75</v>
@@ -4282,7 +4282,7 @@
         <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="R20" t="n">
         <v>1.34</v>
@@ -4306,7 +4306,7 @@
         <v>17.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -4324,7 +4324,7 @@
         <v>23</v>
       </c>
       <c r="AE20" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
@@ -4378,13 +4378,13 @@
         <v>18</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
         <v>17.5</v>
@@ -4402,7 +4402,7 @@
         <v>7.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
         <v>9.199999999999999</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>
@@ -4443,100 +4443,100 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="G21" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="H21" t="n">
-        <v>1.09</v>
+        <v>5.9</v>
       </c>
       <c r="I21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.75</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="X21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Z21" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG21" t="n">
         <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
         <v>55</v>
@@ -4545,68 +4545,68 @@
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AQ21" t="n">
         <v>4.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AV21" t="n">
         <v>4.7</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY21" t="n">
         <v>3.65</v>
       </c>
-      <c r="AY21" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AZ21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC21" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC21" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD21" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF21" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 21:54:39</t>
+          <t>2026-03-10 00:01:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,7 +781,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.15</v>
@@ -793,7 +793,7 @@
         <v>1.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S2" t="n">
         <v>2.14</v>
@@ -802,7 +802,7 @@
         <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V2" t="n">
         <v>5</v>
@@ -835,7 +835,7 @@
         <v>14.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AG2" t="n">
         <v>950</v>
@@ -850,22 +850,22 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AL2" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AM2" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN2" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AO2" t="n">
         <v>3.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
         <v>9.6</v>
@@ -889,7 +889,7 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>3.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
         <v>1.88</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>1.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
         <v>2.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
         <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.4</v>
@@ -1581,7 +1581,7 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
@@ -1593,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AA6" t="n">
         <v>15</v>
@@ -1638,7 +1638,7 @@
         <v>130</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AP6" t="n">
         <v>13.5</v>
@@ -1647,10 +1647,10 @@
         <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
         <v>19.5</v>
@@ -1689,14 +1689,14 @@
         <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BG6" t="n">
         <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>2.02</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
@@ -1751,7 +1751,7 @@
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O7" t="n">
         <v>1.5</v>
@@ -1769,7 +1769,7 @@
         <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
         <v>1.72</v>
@@ -1823,7 +1823,7 @@
         <v>120</v>
       </c>
       <c r="AL7" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM7" t="n">
         <v>240</v>
@@ -1835,7 +1835,7 @@
         <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
         <v>5.8</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J8" t="n">
         <v>2.6</v>
@@ -1966,7 +1966,7 @@
         <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V8" t="n">
         <v>1.34</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2.48</v>
       </c>
       <c r="H9" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="I9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>410</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>400</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS9" t="n">
         <v>4</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X9" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>60</v>
-      </c>
       <c r="AT9" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>36</v>
+        <v>4.3</v>
       </c>
       <c r="AX9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AY9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>22</v>
-      </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>3.75</v>
       </c>
       <c r="BD9" t="n">
-        <v>25</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>50</v>
+        <v>4.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="I10" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.31</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.58</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.7</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
         <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB10" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AJ10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL10" t="n">
         <v>38</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>30</v>
       </c>
       <c r="AM10" t="n">
         <v>55</v>
       </c>
       <c r="AN10" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AP10" t="n">
         <v>20</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AS10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC10" t="n">
         <v>32</v>
       </c>
-      <c r="AT10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW10" t="n">
+      <c r="BD10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF10" t="n">
         <v>23</v>
       </c>
-      <c r="AX10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>14</v>
-      </c>
       <c r="BG10" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>3.35</v>
+        <v>2.66</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>2.68</v>
       </c>
       <c r="J11" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="U11" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="W11" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>40</v>
+        <v>16.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="AF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
         <v>14</v>
       </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>42</v>
-      </c>
       <c r="AI11" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS11" t="n">
         <v>34</v>
       </c>
-      <c r="AL11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>410</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>400</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4</v>
-      </c>
       <c r="AT11" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF11" t="n">
         <v>14</v>
       </c>
-      <c r="AW11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -2688,28 +2688,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>3.65</v>
+        <v>2.02</v>
       </c>
       <c r="H12" t="n">
-        <v>2.08</v>
+        <v>3.95</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
@@ -2718,156 +2718,156 @@
         <v>1.31</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
         <v>5.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.98</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB12" t="n">
         <v>13</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>18.5</v>
       </c>
       <c r="AC12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="AF12" t="n">
-        <v>29</v>
+        <v>14.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
       </c>
       <c r="AI12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL12" t="n">
         <v>27</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>38</v>
       </c>
       <c r="AM12" t="n">
         <v>60</v>
       </c>
       <c r="AN12" t="n">
-        <v>26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO12" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT12" t="n">
         <v>12</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AU12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="BA12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC12" t="n">
         <v>17</v>
       </c>
-      <c r="AU12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA12" t="n">
+      <c r="BD12" t="n">
         <v>25</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>55</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>34</v>
       </c>
       <c r="BE12" t="n">
         <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.6</v>
+        <v>27</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,112 +2882,112 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.34</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.9</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>2.34</v>
       </c>
       <c r="T13" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="W13" t="n">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         <v>2.92</v>
       </c>
       <c r="K14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.62</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.2</v>
+        <v>2.34</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>2.64</v>
       </c>
       <c r="H15" t="n">
-        <v>1.83</v>
+        <v>3.55</v>
       </c>
       <c r="I15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB15" t="n">
         <v>2.04</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.4</v>
@@ -3572,7 +3572,7 @@
         <v>40</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
         <v>19</v>
@@ -3626,7 +3626,7 @@
         <v>34</v>
       </c>
       <c r="BE16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BF16" t="n">
         <v>17</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G17" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I17" t="n">
         <v>7.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,13 +3691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
         <v>1.43</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q17" t="n">
         <v>2.28</v>
@@ -3709,7 +3709,7 @@
         <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U17" t="n">
         <v>1.59</v>
@@ -3718,7 +3718,7 @@
         <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="X17" t="n">
         <v>12.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -3876,19 +3876,19 @@
         <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.61</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>2.32</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P18" t="n">
         <v>1.43</v>
@@ -3912,10 +3912,10 @@
         <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y18" t="n">
         <v>18</v>
@@ -3930,16 +3930,16 @@
         <v>6.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE18" t="n">
         <v>240</v>
       </c>
       <c r="AF18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG18" t="n">
         <v>14.5</v>
@@ -3954,7 +3954,7 @@
         <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL18" t="n">
         <v>110</v>
@@ -3975,10 +3975,10 @@
         <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AT18" t="n">
         <v>4.7</v>
@@ -3987,10 +3987,10 @@
         <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX18" t="n">
         <v>7.2</v>
@@ -3999,32 +3999,32 @@
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB18" t="n">
         <v>4.1</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BC18" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4</v>
-      </c>
       <c r="BD18" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF18" t="n">
         <v>16.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 00:01:01</t>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G21" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="H21" t="n">
-        <v>5.9</v>
+        <v>1.09</v>
       </c>
       <c r="I21" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
         <v>4.5</v>
@@ -4476,7 +4476,7 @@
         <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R21" t="n">
         <v>1.28</v>
@@ -4512,7 +4512,7 @@
         <v>7.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD21" t="n">
         <v>36</v>
@@ -4524,7 +4524,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
         <v>32</v>
@@ -4551,62 +4551,1226 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:15:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Lobos UPNFM</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K22" t="n">
+        <v>950</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J24" t="n">
         <v>3.95</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="K24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Atl Tucuman</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S25" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS21" t="n">
+      <c r="T25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Boyaca Patriotas</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Quindio</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K27" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-03-10 00:01:01</t>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-10 02:08:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -760,7 +760,7 @@
         <v>14.5</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -865,10 +865,10 @@
         <v>3.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
         <v>7.6</v>
@@ -895,16 +895,16 @@
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC2" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>11</v>
@@ -913,14 +913,14 @@
         <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
         <v>2.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>2.08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
         <v>4.5</v>
@@ -999,122 +999,122 @@
         <v>2.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W3" t="n">
         <v>1.3</v>
       </c>
       <c r="X3" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI3" t="n">
         <v>29</v>
       </c>
-      <c r="Y3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AJ3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA3" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G4" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="H4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I4" t="n">
         <v>1.89</v>
@@ -1163,7 +1163,7 @@
         <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1184,7 +1184,7 @@
         <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="T4" t="n">
         <v>1.93</v>
@@ -1196,13 +1196,13 @@
         <v>2.12</v>
       </c>
       <c r="W4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>980</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.4</v>
+        <v>980</v>
       </c>
       <c r="Z4" t="n">
         <v>980</v>
@@ -1256,59 +1256,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU4" t="n">
         <v>4.1</v>
       </c>
-      <c r="AU4" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AV4" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BG4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AY4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1339,28 +1339,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="G5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H5" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
         <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
         <v>4.9</v>
@@ -1369,10 +1369,10 @@
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
         <v>1.62</v>
@@ -1387,10 +1387,10 @@
         <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1450,59 +1450,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1539,28 +1539,28 @@
         <v>6.8</v>
       </c>
       <c r="H6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.61</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.62</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
         <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -1581,7 +1581,7 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
@@ -1590,7 +1590,7 @@
         <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
         <v>8.6</v>
@@ -1602,13 +1602,13 @@
         <v>21</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>9.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
         <v>55</v>
@@ -1641,7 +1641,7 @@
         <v>9.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
         <v>7.6</v>
@@ -1662,41 +1662,41 @@
         <v>9.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AY6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>22</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>21</v>
-      </c>
       <c r="BA6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB6" t="n">
         <v>46</v>
       </c>
       <c r="BC6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BD6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BE6" t="n">
         <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="BG6" t="n">
         <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1733,25 +1733,25 @@
         <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I7" t="n">
         <v>2.02</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="O7" t="n">
         <v>1.5</v>
@@ -1769,7 +1769,7 @@
         <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
         <v>1.72</v>
@@ -1778,7 +1778,7 @@
         <v>1.98</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
         <v>9.6</v>
@@ -1811,13 +1811,13 @@
         <v>24</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AK7" t="n">
         <v>120</v>
@@ -1835,7 +1835,7 @@
         <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ7" t="n">
         <v>5.8</v>
@@ -1877,10 +1877,10 @@
         <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
         <v>7.8</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -1921,106 +1921,106 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N8" t="n">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z8" t="n">
         <v>980</v>
       </c>
       <c r="AA8" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AB8" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
         <v>980</v>
       </c>
       <c r="AE8" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AF8" t="n">
         <v>980</v>
       </c>
       <c r="AG8" t="n">
-        <v>20</v>
+        <v>980</v>
       </c>
       <c r="AH8" t="n">
         <v>980</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.18</v>
+        <v>6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.84</v>
+        <v>7.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.14</v>
+        <v>7.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.78</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.14</v>
+        <v>7.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.98</v>
+        <v>12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.18</v>
+        <v>7.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.18</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.18</v>
+        <v>7.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.18</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.18</v>
+        <v>7.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>3.35</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
         <v>2.98</v>
@@ -2178,10 +2178,10 @@
         <v>27</v>
       </c>
       <c r="AA9" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
         <v>7.4</v>
@@ -2190,7 +2190,7 @@
         <v>36</v>
       </c>
       <c r="AE9" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
         <v>14</v>
@@ -2256,13 +2256,13 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
         <v>13.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BD9" t="n">
         <v>4.1</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="G10" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2345,7 +2345,7 @@
         <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
         <v>2.62</v>
@@ -2357,10 +2357,10 @@
         <v>2.58</v>
       </c>
       <c r="V10" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="W10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
         <v>22</v>
@@ -2375,7 +2375,7 @@
         <v>26</v>
       </c>
       <c r="AB10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC10" t="n">
         <v>9.199999999999999</v>
@@ -2387,7 +2387,7 @@
         <v>18.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG10" t="n">
         <v>15</v>
@@ -2402,16 +2402,16 @@
         <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO10" t="n">
         <v>10.5</v>
@@ -2426,7 +2426,7 @@
         <v>14.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT10" t="n">
         <v>17</v>
@@ -2441,10 +2441,10 @@
         <v>17.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
@@ -2459,20 +2459,20 @@
         <v>32</v>
       </c>
       <c r="BD10" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG10" t="n">
         <v>9.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H11" t="n">
         <v>2.66</v>
@@ -2554,13 +2554,13 @@
         <v>1.59</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
         <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z11" t="n">
         <v>21</v>
@@ -2614,7 +2614,7 @@
         <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
         <v>19</v>
@@ -2626,7 +2626,7 @@
         <v>15</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV11" t="n">
         <v>11</v>
@@ -2635,7 +2635,7 @@
         <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
@@ -2647,7 +2647,7 @@
         <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC11" t="n">
         <v>22</v>
@@ -2656,7 +2656,7 @@
         <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF11" t="n">
         <v>14</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I12" t="n">
         <v>3.95</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.95</v>
       </c>
       <c r="K12" t="n">
         <v>4.1</v>
@@ -2739,7 +2739,7 @@
         <v>2.64</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
         <v>2.56</v>
@@ -2748,13 +2748,13 @@
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X12" t="n">
         <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z12" t="n">
         <v>32</v>
@@ -2766,10 +2766,10 @@
         <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
         <v>40</v>
@@ -2787,7 +2787,7 @@
         <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK12" t="n">
         <v>18</v>
@@ -2796,16 +2796,16 @@
         <v>27</v>
       </c>
       <c r="AM12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AO12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ12" t="n">
         <v>18.5</v>
@@ -2814,10 +2814,10 @@
         <v>29</v>
       </c>
       <c r="AS12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU12" t="n">
         <v>8.800000000000001</v>
@@ -2832,7 +2832,7 @@
         <v>13.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>14.5</v>
@@ -2841,10 +2841,10 @@
         <v>38</v>
       </c>
       <c r="BB12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD12" t="n">
         <v>25</v>
@@ -2853,14 +2853,14 @@
         <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
         <v>27</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G13" t="n">
         <v>6.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="I13" t="n">
         <v>2.04</v>
@@ -2909,46 +2909,46 @@
         <v>3.65</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>2.72</v>
       </c>
       <c r="O13" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="P13" t="n">
         <v>1.59</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S13" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V13" t="n">
         <v>1.96</v>
       </c>
       <c r="W13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
         <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V14" t="n">
         <v>1.25</v>
@@ -3178,13 +3178,13 @@
         <v>32</v>
       </c>
       <c r="AK14" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL14" t="n">
         <v>70</v>
       </c>
       <c r="AM14" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN14" t="n">
         <v>34</v>
@@ -3199,7 +3199,7 @@
         <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS14" t="n">
         <v>6.4</v>
@@ -3211,10 +3211,10 @@
         <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3226,29 +3226,29 @@
         <v>22</v>
       </c>
       <c r="BA14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD14" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>6</v>
-      </c>
       <c r="BE14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG14" t="n">
         <v>6.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="G15" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="H15" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
         <v>2.96</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="O15" t="n">
         <v>1.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.9</v>
+        <v>2.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>36</v>
       </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="AK15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY15" t="n">
         <v>10</v>
       </c>
-      <c r="AD15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>2</v>
+        <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.12</v>
+        <v>7.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.04</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.04</v>
+        <v>6.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.12</v>
+        <v>8</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.12</v>
+        <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.12</v>
+        <v>7.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H16" t="n">
         <v>3.45</v>
@@ -3488,7 +3488,7 @@
         <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
         <v>1.4</v>
@@ -3497,40 +3497,40 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
         <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V16" t="n">
         <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X16" t="n">
         <v>13.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
         <v>24</v>
@@ -3539,10 +3539,10 @@
         <v>65</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>14.5</v>
@@ -3557,7 +3557,7 @@
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI16" t="n">
         <v>55</v>
@@ -3566,16 +3566,16 @@
         <v>30</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL16" t="n">
         <v>40</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO16" t="n">
         <v>40</v>
@@ -3590,7 +3590,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT16" t="n">
         <v>9</v>
@@ -3605,7 +3605,7 @@
         <v>36</v>
       </c>
       <c r="AX16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
@@ -3614,29 +3614,29 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="BB16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG16" t="n">
         <v>34</v>
       </c>
-      <c r="BE16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>36</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>1.78</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="I17" t="n">
         <v>7.4</v>
@@ -3685,34 +3685,34 @@
         <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>2.66</v>
       </c>
       <c r="O17" t="n">
         <v>1.43</v>
       </c>
       <c r="P17" t="n">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="Q17" t="n">
         <v>2.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="V17" t="n">
         <v>1.15</v>
@@ -3721,10 +3721,10 @@
         <v>2.28</v>
       </c>
       <c r="X17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3733,10 +3733,10 @@
         <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -3745,10 +3745,10 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>1000</v>
@@ -3757,10 +3757,10 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -3769,68 +3769,68 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.82</v>
+        <v>5.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.45</v>
+        <v>8.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.66</v>
+        <v>4.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.25</v>
+        <v>7.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>2.82</v>
+        <v>5.1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.25</v>
+        <v>7.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.45</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE17" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G18" t="n">
         <v>1.81</v>
@@ -3879,16 +3879,16 @@
         <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M18" t="n">
         <v>1.14</v>
       </c>
       <c r="N18" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P18" t="n">
         <v>1.43</v>
@@ -3897,25 +3897,25 @@
         <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S18" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="V18" t="n">
         <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y18" t="n">
         <v>18</v>
@@ -3927,10 +3927,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>40</v>
@@ -3951,7 +3951,7 @@
         <v>270</v>
       </c>
       <c r="AJ18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
         <v>36</v>
@@ -3963,7 +3963,7 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3972,13 +3972,13 @@
         <v>6.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT18" t="n">
         <v>4.7</v>
@@ -3987,7 +3987,7 @@
         <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.4</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>4.9</v>
@@ -4005,10 +4005,10 @@
         <v>4.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD18" t="n">
         <v>4.8</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>2.8</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="J19" t="n">
         <v>2.82</v>
@@ -4073,152 +4073,152 @@
         <v>3.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>1.4</v>
+        <v>2.28</v>
       </c>
       <c r="O19" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="Q19" t="n">
         <v>2.34</v>
       </c>
       <c r="R19" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
         <v>1.4</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
         <v>1.9</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
         <v>3.3</v>
@@ -4309,7 +4309,7 @@
         <v>19</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA20" t="n">
         <v>150</v>
@@ -4321,16 +4321,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH20" t="n">
         <v>21</v>
@@ -4348,7 +4348,7 @@
         <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN20" t="n">
         <v>12.5</v>
@@ -4363,10 +4363,10 @@
         <v>15.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
@@ -4378,7 +4378,7 @@
         <v>18</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
@@ -4390,7 +4390,7 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
         <v>15.5</v>
@@ -4399,20 +4399,20 @@
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
         <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
         <v>2.12</v>
@@ -4494,7 +4494,7 @@
         <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="X21" t="n">
         <v>15</v>
@@ -4512,7 +4512,7 @@
         <v>7.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
         <v>36</v>
@@ -4524,7 +4524,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
         <v>32</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC21" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY21" t="n">
+      <c r="BD21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF21" t="n">
         <v>3.75</v>
       </c>
-      <c r="AZ21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4</v>
-      </c>
       <c r="BG21" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -4661,13 +4661,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="O22" t="n">
         <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q22" t="n">
         <v>1.35</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.4</v>
@@ -4861,13 +4861,13 @@
         <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
         <v>2.04</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
         <v>3.65</v>
@@ -4939,16 +4939,16 @@
         <v>210</v>
       </c>
       <c r="AP23" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>20</v>
       </c>
       <c r="AR23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>14</v>
+        <v>5.8</v>
       </c>
       <c r="AT23" t="n">
         <v>6.8</v>
@@ -4960,7 +4960,7 @@
         <v>22</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX23" t="n">
         <v>7.4</v>
@@ -4969,10 +4969,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB23" t="n">
         <v>12</v>
@@ -4981,20 +4981,20 @@
         <v>14</v>
       </c>
       <c r="BD23" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BE23" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
       <c r="BF23" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>7.2</v>
       </c>
       <c r="I24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>3.95</v>
@@ -5049,7 +5049,7 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>1.4</v>
@@ -5058,13 +5058,13 @@
         <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T24" t="n">
         <v>2.2</v>
@@ -5073,7 +5073,7 @@
         <v>1.73</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W24" t="n">
         <v>2.56</v>
@@ -5088,7 +5088,7 @@
         <v>65</v>
       </c>
       <c r="AA24" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AB24" t="n">
         <v>6.8</v>
@@ -5097,10 +5097,10 @@
         <v>9.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE24" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF24" t="n">
         <v>8.6</v>
@@ -5109,10 +5109,10 @@
         <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI24" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ24" t="n">
         <v>15.5</v>
@@ -5124,7 +5124,7 @@
         <v>48</v>
       </c>
       <c r="AM24" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN24" t="n">
         <v>12</v>
@@ -5139,10 +5139,10 @@
         <v>17.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT24" t="n">
         <v>6</v>
@@ -5154,7 +5154,7 @@
         <v>21</v>
       </c>
       <c r="AW24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX24" t="n">
         <v>7.4</v>
@@ -5166,7 +5166,7 @@
         <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB24" t="n">
         <v>13</v>
@@ -5175,20 +5175,20 @@
         <v>17</v>
       </c>
       <c r="BD24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF24" t="n">
         <v>10.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -5219,61 +5219,61 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="G25" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I25" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J25" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="K25" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M25" t="n">
         <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="O25" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.52</v>
+        <v>2.52</v>
       </c>
       <c r="R25" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="S25" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="V25" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W25" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y25" t="n">
         <v>1000</v>
@@ -5282,13 +5282,13 @@
         <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD25" t="n">
         <v>1000</v>
@@ -5297,16 +5297,16 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ25" t="n">
         <v>1000</v>
@@ -5318,7 +5318,7 @@
         <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G26" t="n">
         <v>1.7</v>
@@ -5437,28 +5437,28 @@
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>1.46</v>
+        <v>2.68</v>
       </c>
       <c r="O26" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="P26" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="V26" t="n">
         <v>1.13</v>
@@ -5467,116 +5467,116 @@
         <v>2.42</v>
       </c>
       <c r="X26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y26" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU26" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AV26" t="n">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX26" t="n">
-        <v>2.22</v>
+        <v>7</v>
       </c>
       <c r="AY26" t="n">
-        <v>2.34</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.62</v>
+        <v>7.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.48</v>
+        <v>13.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.56</v>
+        <v>19.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.78</v>
+        <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.78</v>
+        <v>9</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>
@@ -5607,100 +5607,100 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="G27" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="H27" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
         <v>2.72</v>
       </c>
       <c r="K27" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>1.36</v>
+        <v>2.36</v>
       </c>
       <c r="O27" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="P27" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R27" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="S27" t="n">
-        <v>2.34</v>
+        <v>3.45</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V27" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL27" t="n">
         <v>1000</v>
@@ -5709,68 +5709,68 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 02:08:09</t>
+          <t>2026-03-10 04:15:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
         <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q5" t="n">
         <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
         <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1450,7 +1450,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="AR5" t="n">
         <v>1.61</v>
@@ -1459,50 +1459,50 @@
         <v>1.64</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="BA5" t="n">
         <v>1.62</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.65</v>
+        <v>2.44</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="BF5" t="n">
         <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1539,13 +1539,13 @@
         <v>6.8</v>
       </c>
       <c r="H6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.6</v>
       </c>
-      <c r="I6" t="n">
-        <v>1.61</v>
-      </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
         <v>4.5</v>
@@ -1581,7 +1581,7 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
@@ -1605,7 +1605,7 @@
         <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE6" t="n">
         <v>17</v>
@@ -1623,7 +1623,7 @@
         <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AK6" t="n">
         <v>100</v>
@@ -1689,14 +1689,14 @@
         <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BG6" t="n">
         <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1730,10 +1730,10 @@
         <v>4.8</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I7" t="n">
         <v>2.02</v>
@@ -1751,7 +1751,7 @@
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O7" t="n">
         <v>1.5</v>
@@ -1775,7 +1775,7 @@
         <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="W7" t="n">
         <v>1.21</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G8" t="n">
         <v>3.05</v>
@@ -1936,10 +1936,10 @@
         <v>2.66</v>
       </c>
       <c r="K8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M8" t="n">
         <v>1.16</v>
@@ -1954,7 +1954,7 @@
         <v>1.41</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>1.14</v>
@@ -2047,7 +2047,7 @@
         <v>6</v>
       </c>
       <c r="AV8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
         <v>7.2</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
         <v>240</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK9" t="n">
         <v>34</v>
@@ -2226,16 +2226,16 @@
         <v>7.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR9" t="n">
         <v>9.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AU9" t="n">
         <v>6.2</v>
@@ -2244,7 +2244,7 @@
         <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX9" t="n">
         <v>6.4</v>
@@ -2256,13 +2256,13 @@
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB9" t="n">
         <v>13.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BD9" t="n">
         <v>4.1</v>
@@ -2274,11 +2274,11 @@
         <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G10" t="n">
         <v>3.8</v>
       </c>
       <c r="H10" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2339,10 +2339,10 @@
         <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
         <v>1.58</v>
@@ -2357,10 +2357,10 @@
         <v>2.58</v>
       </c>
       <c r="V10" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
         <v>22</v>
@@ -2396,7 +2396,7 @@
         <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ10" t="n">
         <v>65</v>
@@ -2429,7 +2429,7 @@
         <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU10" t="n">
         <v>9</v>
@@ -2453,7 +2453,7 @@
         <v>23</v>
       </c>
       <c r="BB10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC10" t="n">
         <v>32</v>
@@ -2468,11 +2468,11 @@
         <v>24</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G11" t="n">
         <v>2.74</v>
@@ -2515,10 +2515,10 @@
         <v>2.68</v>
       </c>
       <c r="J11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -2635,7 +2635,7 @@
         <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
@@ -2662,11 +2662,11 @@
         <v>14</v>
       </c>
       <c r="BG11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G12" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H12" t="n">
         <v>3.9</v>
@@ -2736,19 +2736,19 @@
         <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
         <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V12" t="n">
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
         <v>21</v>
@@ -2790,7 +2790,7 @@
         <v>23</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL12" t="n">
         <v>27</v>
@@ -2799,7 +2799,7 @@
         <v>65</v>
       </c>
       <c r="AN12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO12" t="n">
         <v>30</v>
@@ -2814,10 +2814,10 @@
         <v>29</v>
       </c>
       <c r="AS12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
         <v>8.800000000000001</v>
@@ -2853,14 +2853,14 @@
         <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12" t="n">
         <v>27</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G14" t="n">
         <v>2.26</v>
@@ -3109,7 +3109,7 @@
         <v>1.14</v>
       </c>
       <c r="N14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O14" t="n">
         <v>1.61</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I15" t="n">
         <v>4.2</v>
@@ -3294,7 +3294,7 @@
         <v>2.96</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
         <v>1.56</v>
@@ -3303,25 +3303,25 @@
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="R15" t="n">
         <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U15" t="n">
         <v>1.77</v>
@@ -3330,10 +3330,10 @@
         <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X15" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Y15" t="n">
         <v>11</v>
@@ -3348,7 +3348,7 @@
         <v>7.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
         <v>17.5</v>
@@ -3357,7 +3357,7 @@
         <v>70</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG15" t="n">
         <v>12.5</v>
@@ -3369,19 +3369,19 @@
         <v>110</v>
       </c>
       <c r="AJ15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK15" t="n">
         <v>34</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
         <v>230</v>
       </c>
       <c r="AN15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO15" t="n">
         <v>120</v>
@@ -3396,7 +3396,7 @@
         <v>18.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="AT15" t="n">
         <v>6.4</v>
@@ -3405,44 +3405,44 @@
         <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX15" t="n">
         <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB15" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BC15" t="n">
-        <v>6.6</v>
+        <v>25</v>
       </c>
       <c r="BD15" t="n">
-        <v>7.4</v>
+        <v>46</v>
       </c>
       <c r="BE15" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G16" t="n">
         <v>2.32</v>
@@ -3482,7 +3482,7 @@
         <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
         <v>3.5</v>
@@ -3503,7 +3503,7 @@
         <v>1.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q16" t="n">
         <v>1.96</v>
@@ -3515,13 +3515,13 @@
         <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U16" t="n">
         <v>2.14</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
         <v>1.75</v>
@@ -3542,7 +3542,7 @@
         <v>10</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
         <v>14.5</v>
@@ -3602,7 +3602,7 @@
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>36</v>
+        <v>14.5</v>
       </c>
       <c r="AX16" t="n">
         <v>13</v>
@@ -3626,7 +3626,7 @@
         <v>13.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BF16" t="n">
         <v>16</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>2.76</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H19" t="n">
         <v>2.8</v>
@@ -4079,7 +4079,7 @@
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="O19" t="n">
         <v>1.53</v>
@@ -4094,19 +4094,19 @@
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V19" t="n">
         <v>1.44</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="X19" t="n">
         <v>10.5</v>
@@ -4136,7 +4136,7 @@
         <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
         <v>28</v>
@@ -4163,62 +4163,62 @@
         <v>70</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AY19" t="n">
         <v>3.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE19" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>1.73</v>
       </c>
       <c r="G20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H20" t="n">
         <v>5.2</v>
@@ -4300,7 +4300,7 @@
         <v>1.2</v>
       </c>
       <c r="W20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X20" t="n">
         <v>17.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G21" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="H21" t="n">
-        <v>1.09</v>
+        <v>5.9</v>
       </c>
       <c r="I21" t="n">
         <v>9.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>4.5</v>
@@ -4476,13 +4476,13 @@
         <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="R21" t="n">
         <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
         <v>2.12</v>
@@ -4524,7 +4524,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH21" t="n">
         <v>32</v>
@@ -4551,28 +4551,28 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="n">
         <v>3.4</v>
@@ -4581,32 +4581,32 @@
         <v>3.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BC21" t="n">
         <v>4.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG21" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K22" t="n">
         <v>950</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
         <v>1.33</v>
@@ -4876,7 +4876,7 @@
         <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="V23" t="n">
         <v>1.13</v>
@@ -4945,7 +4945,7 @@
         <v>20</v>
       </c>
       <c r="AR23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS23" t="n">
         <v>5.8</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
         <v>4.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
         <v>3.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
         <v>1.12</v>
@@ -5267,7 +5267,7 @@
         <v>1.71</v>
       </c>
       <c r="V25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
         <v>1.92</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G26" t="n">
         <v>1.7</v>
@@ -5431,7 +5431,7 @@
         <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M26" t="n">
         <v>1.11</v>
@@ -5443,7 +5443,7 @@
         <v>1.49</v>
       </c>
       <c r="P26" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q26" t="n">
         <v>2.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 04:15:14</t>
+          <t>2026-03-10 06:22:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -763,16 +763,16 @@
         <v>19.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.21</v>
@@ -784,28 +784,28 @@
         <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P2" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
         <v>1.75</v>
       </c>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="W2" t="n">
         <v>1.05</v>
@@ -838,7 +838,7 @@
         <v>200</v>
       </c>
       <c r="AG2" t="n">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AH2" t="n">
         <v>980</v>
@@ -865,7 +865,7 @@
         <v>3.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
         <v>9.800000000000001</v>
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
         <v>15.5</v>
@@ -889,22 +889,22 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA2" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BA2" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>11</v>
@@ -913,14 +913,14 @@
         <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>2.08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>4.5</v>
@@ -984,16 +984,16 @@
         <v>2.34</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T3" t="n">
         <v>1.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.59</v>
       </c>
       <c r="U3" t="n">
         <v>2.36</v>
@@ -1002,79 +1002,79 @@
         <v>1.93</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB3" t="n">
         <v>24</v>
       </c>
-      <c r="Y3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>21</v>
-      </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH3" t="n">
         <v>19.5</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>34</v>
       </c>
-      <c r="AG3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>29</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AK3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AN3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AO3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
         <v>19</v>
       </c>
       <c r="AT3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
         <v>9.199999999999999</v>
@@ -1083,38 +1083,38 @@
         <v>15.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1184,13 +1184,13 @@
         <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V4" t="n">
         <v>2.12</v>
@@ -1304,11 +1304,11 @@
         <v>1.84</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
         <v>4.4</v>
@@ -1351,7 +1351,7 @@
         <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K5" t="n">
         <v>5.4</v>
@@ -1363,34 +1363,34 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T5" t="n">
         <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
         <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1450,59 +1450,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.44</v>
+        <v>2.98</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BF5" t="n">
         <v>6</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1539,10 +1539,10 @@
         <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J6" t="n">
         <v>4.4</v>
@@ -1557,7 +1557,7 @@
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
@@ -1566,13 +1566,13 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
@@ -1581,19 +1581,19 @@
         <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
         <v>15</v>
@@ -1602,7 +1602,7 @@
         <v>21</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
         <v>9.800000000000001</v>
@@ -1647,7 +1647,7 @@
         <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS6" t="n">
         <v>14</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
         <v>5.7</v>
@@ -1754,10 +1754,10 @@
         <v>2.68</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q7" t="n">
         <v>2.5</v>
@@ -1769,13 +1769,13 @@
         <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
         <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="W7" t="n">
         <v>1.21</v>
@@ -1811,7 +1811,7 @@
         <v>24</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>60</v>
@@ -1868,29 +1868,29 @@
         <v>21</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC7" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC7" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BD7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF7" t="n">
         <v>8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
         <v>17</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -1948,10 +1948,10 @@
         <v>2.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="P8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" t="n">
         <v>3</v>
@@ -1960,19 +1960,19 @@
         <v>1.14</v>
       </c>
       <c r="S8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X8" t="n">
         <v>8</v>
@@ -2035,7 +2035,7 @@
         <v>7.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="AS8" t="n">
         <v>7.2</v>
@@ -2059,7 +2059,7 @@
         <v>12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
         <v>7.6</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,103 +2139,103 @@
         <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O9" t="n">
         <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
         <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
         <v>42</v>
       </c>
       <c r="AI9" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
         <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
         <v>410</v>
       </c>
       <c r="AN9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU9" t="n">
         <v>6.2</v>
@@ -2244,41 +2244,41 @@
         <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BB9" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
         <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S10" t="n">
         <v>2.62</v>
@@ -2354,13 +2354,13 @@
         <v>1.59</v>
       </c>
       <c r="U10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V10" t="n">
         <v>1.92</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
         <v>22</v>
@@ -2378,7 +2378,7 @@
         <v>19</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
         <v>10.5</v>
@@ -2444,7 +2444,7 @@
         <v>27</v>
       </c>
       <c r="AY10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I11" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.31</v>
@@ -2527,34 +2527,34 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q11" t="n">
         <v>1.63</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
         <v>2.58</v>
       </c>
       <c r="T11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U11" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.59</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.57</v>
       </c>
       <c r="X11" t="n">
         <v>22</v>
@@ -2566,7 +2566,7 @@
         <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB11" t="n">
         <v>16</v>
@@ -2581,7 +2581,7 @@
         <v>24</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
@@ -2596,7 +2596,7 @@
         <v>38</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
         <v>32</v>
@@ -2608,7 +2608,7 @@
         <v>15.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2629,7 +2629,7 @@
         <v>8.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
         <v>22</v>
@@ -2638,7 +2638,7 @@
         <v>19</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>13.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G12" t="n">
         <v>1.99</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
         <v>4</v>
@@ -2730,7 +2730,7 @@
         <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R12" t="n">
         <v>1.59</v>
@@ -2745,7 +2745,7 @@
         <v>2.58</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
         <v>2</v>
@@ -2802,7 +2802,7 @@
         <v>9.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
         <v>20</v>
@@ -2814,7 +2814,7 @@
         <v>29</v>
       </c>
       <c r="AS12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT12" t="n">
         <v>12</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -2891,64 +2891,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P13" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V13" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR13" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.3</v>
       </c>
       <c r="AS13" t="n">
         <v>5.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW13" t="n">
         <v>5.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.05</v>
+        <v>5.9</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.86</v>
+        <v>2.44</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.84</v>
+        <v>2.42</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H14" t="n">
         <v>4.5</v>
@@ -3136,13 +3136,13 @@
         <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X14" t="n">
         <v>7.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z14" t="n">
         <v>34</v>
@@ -3151,7 +3151,7 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC14" t="n">
         <v>8.199999999999999</v>
@@ -3163,10 +3163,10 @@
         <v>110</v>
       </c>
       <c r="AF14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
         <v>30</v>
@@ -3193,16 +3193,16 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
         <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
         <v>5.8</v>
@@ -3214,7 +3214,7 @@
         <v>18.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3226,29 +3226,29 @@
         <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.7</v>
+        <v>28</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3285,13 @@
         <v>2.46</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>3.25</v>
@@ -3303,13 +3303,13 @@
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O15" t="n">
         <v>1.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q15" t="n">
         <v>2.66</v>
@@ -3321,31 +3321,31 @@
         <v>5.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="X15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC15" t="n">
         <v>7.4</v>
@@ -3396,10 +3396,10 @@
         <v>18.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU15" t="n">
         <v>6.2</v>
@@ -3414,19 +3414,19 @@
         <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>55</v>
       </c>
       <c r="BB15" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BC15" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
         <v>46</v>
@@ -3438,11 +3438,11 @@
         <v>19.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G16" t="n">
         <v>2.32</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
         <v>3.65</v>
@@ -3500,13 +3500,13 @@
         <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
@@ -3518,13 +3518,13 @@
         <v>1.78</v>
       </c>
       <c r="U16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X16" t="n">
         <v>13.5</v>
@@ -3533,7 +3533,7 @@
         <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA16" t="n">
         <v>65</v>
@@ -3545,7 +3545,7 @@
         <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>48</v>
@@ -3563,7 +3563,7 @@
         <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK16" t="n">
         <v>24</v>
@@ -3575,7 +3575,7 @@
         <v>95</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
         <v>40</v>
@@ -3590,7 +3590,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT16" t="n">
         <v>9</v>
@@ -3617,7 +3617,7 @@
         <v>42</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
         <v>21</v>
@@ -3626,7 +3626,7 @@
         <v>13.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BF16" t="n">
         <v>16</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -3667,64 +3667,64 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="G17" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="H17" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.48</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O17" t="n">
         <v>1.43</v>
       </c>
       <c r="P17" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3736,7 +3736,7 @@
         <v>6.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -3757,7 +3757,7 @@
         <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK17" t="n">
         <v>23</v>
@@ -3769,68 +3769,68 @@
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AQ17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV17" t="n">
+      <c r="AW17" t="n">
         <v>7.2</v>
       </c>
-      <c r="AW17" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AX17" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AZ17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA17" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA17" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BB17" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
@@ -3876,7 +3876,7 @@
         <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L18" t="n">
         <v>1.62</v>
@@ -3885,13 +3885,13 @@
         <v>1.14</v>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="O18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q18" t="n">
         <v>3</v>
@@ -3903,22 +3903,22 @@
         <v>6.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V18" t="n">
         <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,13 +3927,13 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC18" t="n">
         <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
         <v>240</v>
@@ -3954,7 +3954,7 @@
         <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
         <v>110</v>
@@ -3963,7 +3963,7 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -3972,13 +3972,13 @@
         <v>6.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
         <v>4.7</v>
@@ -3987,10 +3987,10 @@
         <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>24</v>
+        <v>4.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX18" t="n">
         <v>7.2</v>
@@ -3999,32 +3999,32 @@
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC18" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF18" t="n">
         <v>16.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>2.8</v>
       </c>
       <c r="I19" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
         <v>2.82</v>
@@ -4097,16 +4097,16 @@
         <v>1.05</v>
       </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V19" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
         <v>10.5</v>
@@ -4118,7 +4118,7 @@
         <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB19" t="n">
         <v>10.5</v>
@@ -4130,10 +4130,10 @@
         <v>17</v>
       </c>
       <c r="AE19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
         <v>17</v>
@@ -4163,62 +4163,62 @@
         <v>70</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AS19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE19" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BF19" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G20" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H20" t="n">
         <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
         <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L20" t="n">
         <v>1.39</v>
@@ -4276,40 +4276,40 @@
         <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R20" t="n">
         <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W20" t="n">
         <v>2.2</v>
       </c>
       <c r="X20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y20" t="n">
         <v>19</v>
       </c>
       <c r="Z20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>150</v>
@@ -4318,13 +4318,13 @@
         <v>8.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD20" t="n">
         <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
@@ -4363,13 +4363,13 @@
         <v>15.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU20" t="n">
         <v>7.8</v>
@@ -4378,19 +4378,19 @@
         <v>18</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX20" t="n">
         <v>9.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB20" t="n">
         <v>15.5</v>
@@ -4399,20 +4399,20 @@
         <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG20" t="n">
         <v>9.4</v>
       </c>
-      <c r="BF20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>9</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>1.54</v>
       </c>
       <c r="G21" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="H21" t="n">
-        <v>5.9</v>
+        <v>1.09</v>
       </c>
       <c r="I21" t="n">
         <v>9.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
         <v>4.5</v>
@@ -4476,13 +4476,13 @@
         <v>1.76</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="R21" t="n">
         <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
         <v>2.12</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="O22" t="n">
         <v>1.35</v>
@@ -4676,13 +4676,13 @@
         <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I23" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>4.3</v>
@@ -4861,7 +4861,7 @@
         <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q23" t="n">
         <v>2.04</v>
@@ -4873,22 +4873,22 @@
         <v>3.65</v>
       </c>
       <c r="T23" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V23" t="n">
         <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X23" t="n">
         <v>14.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z23" t="n">
         <v>70</v>
@@ -4939,16 +4939,16 @@
         <v>210</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ23" t="n">
         <v>20</v>
       </c>
       <c r="AR23" t="n">
-        <v>16.5</v>
+        <v>44</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT23" t="n">
         <v>6.8</v>
@@ -4957,10 +4957,10 @@
         <v>9</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AW23" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX23" t="n">
         <v>7.4</v>
@@ -4969,32 +4969,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
         <v>15</v>
       </c>
       <c r="BB23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.7</v>
+        <v>15.5</v>
       </c>
       <c r="BF23" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -5058,13 +5058,13 @@
         <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R24" t="n">
         <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T24" t="n">
         <v>2.2</v>
@@ -5175,7 +5175,7 @@
         <v>17</v>
       </c>
       <c r="BD24" t="n">
-        <v>9.6</v>
+        <v>40</v>
       </c>
       <c r="BE24" t="n">
         <v>11.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G25" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H25" t="n">
         <v>4.7</v>
       </c>
       <c r="I25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="n">
         <v>3.1</v>
@@ -5249,10 +5249,10 @@
         <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="R25" t="n">
         <v>1.19</v>
@@ -5261,16 +5261,16 @@
         <v>5.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U25" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V25" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W25" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X25" t="n">
         <v>9.199999999999999</v>
@@ -5345,7 +5345,7 @@
         <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="AW25" t="n">
         <v>8.199999999999999</v>
@@ -5375,14 +5375,14 @@
         <v>8.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="BG25" t="n">
         <v>8.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G26" t="n">
         <v>1.7</v>
@@ -5425,13 +5425,13 @@
         <v>8.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
         <v>3.9</v>
       </c>
       <c r="L26" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M26" t="n">
         <v>1.11</v>
@@ -5440,10 +5440,10 @@
         <v>2.68</v>
       </c>
       <c r="O26" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P26" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q26" t="n">
         <v>2.5</v>
@@ -5515,13 +5515,13 @@
         <v>330</v>
       </c>
       <c r="AN26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
         <v>15</v>
@@ -5530,7 +5530,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26" t="n">
         <v>5.1</v>
@@ -5539,10 +5539,10 @@
         <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX26" t="n">
         <v>7</v>
@@ -5551,10 +5551,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB26" t="n">
         <v>13.5</v>
@@ -5566,17 +5566,17 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF26" t="n">
         <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>
@@ -5610,16 +5610,16 @@
         <v>1.98</v>
       </c>
       <c r="G27" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J27" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="K27" t="n">
         <v>3.4</v>
@@ -5634,7 +5634,7 @@
         <v>2.36</v>
       </c>
       <c r="O27" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P27" t="n">
         <v>1.48</v>
@@ -5649,16 +5649,16 @@
         <v>3.45</v>
       </c>
       <c r="T27" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X27" t="n">
         <v>9.800000000000001</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 06:22:21</t>
+          <t>2026-03-10 08:29:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Erbaaspor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kepez Belediyespor</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>14.5</v>
+        <v>1.53</v>
       </c>
       <c r="G2" t="n">
-        <v>19.5</v>
+        <v>1.69</v>
       </c>
       <c r="H2" t="n">
-        <v>1.21</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.24</v>
+        <v>8.6</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>2.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.75</v>
+        <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>1.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>5.1</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>2.44</v>
       </c>
       <c r="X2" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -942,179 +942,179 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Istanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.7</v>
+        <v>16.5</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>1.88</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.08</v>
+        <v>1.24</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="L3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.25</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.34</v>
-      </c>
       <c r="Q3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.61</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.53</v>
-      </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.93</v>
+        <v>4.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="Y3" t="n">
         <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AB3" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AJ3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>18.5</v>
+        <v>2.78</v>
       </c>
       <c r="AQ3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AW3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AX3" t="n">
-        <v>3.85</v>
+        <v>2.94</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>2.86</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>2.94</v>
       </c>
       <c r="BA3" t="n">
-        <v>20</v>
+        <v>2.82</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.95</v>
+        <v>2.94</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.9</v>
+        <v>2.94</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>2.52</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Umraniyespor</t>
+          <t>Istanbulspor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Erzurum BB</t>
+          <t>Amed Sportif Faaliyetler</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="I4" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP4" t="n">
         <v>2</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="AQ4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AV4" t="n">
         <v>1.87</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AW4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY4" t="n">
         <v>2.12</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>980</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>980</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>5.8</v>
+        <v>2.12</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>2.02</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.84</v>
+        <v>18.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turkish 1 Lig</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,72 +1325,72 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Keciorengucu</t>
+          <t>Adana 1954 FK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Ankaraspor</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>1.07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>1.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,69 +1447,69 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>07:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>Erzincanspor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Beykoz Anadolu Spor</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.6</v>
+        <v>1.54</v>
       </c>
       <c r="G6" t="n">
-        <v>6.8</v>
+        <v>1.99</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.61</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
         <v>1.07</v>
       </c>
-      <c r="N6" t="n">
-        <v>4</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>2.64</v>
+        <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>2.28</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Fk Siauliai</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>1.56</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>1.97</v>
       </c>
       <c r="H7" t="n">
-        <v>1.87</v>
+        <v>3.85</v>
       </c>
       <c r="I7" t="n">
-        <v>2.02</v>
+        <v>6.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.68</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>2.54</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.98</v>
+        <v>1.09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.95</v>
       </c>
       <c r="X7" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>Ankaragucu</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Kastamonuspor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>2.66</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.24</v>
+        <v>2.98</v>
       </c>
       <c r="O8" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="S8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="Z8" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY8" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD8" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>980</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>980</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>980</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR8" t="n">
+      <c r="AZ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC8" t="n">
         <v>13.5</v>
       </c>
-      <c r="AS8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7</v>
-      </c>
       <c r="BD8" t="n">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,90 +2101,90 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Umraniyespor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Erzurum BB</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="G9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
         <v>2.4</v>
       </c>
-      <c r="H9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.11</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>2.12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,28 +2193,28 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
         <v>1000</v>
@@ -2223,69 +2223,69 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Turkish 1 Lig</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Keciorengucu</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.66</v>
+        <v>1.69</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="H11" t="n">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6</v>
+        <v>2.36</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.63</v>
+        <v>1.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>2.58</v>
+        <v>1.49</v>
       </c>
       <c r="T11" t="n">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>2.68</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>1.59</v>
+        <v>2.26</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15</v>
+        <v>1.24</v>
       </c>
       <c r="AR11" t="n">
-        <v>19</v>
+        <v>1.24</v>
       </c>
       <c r="AS11" t="n">
-        <v>34</v>
+        <v>1.24</v>
       </c>
       <c r="AT11" t="n">
-        <v>15</v>
+        <v>1.24</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.6</v>
+        <v>1.24</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>1.24</v>
       </c>
       <c r="AW11" t="n">
-        <v>22</v>
+        <v>1.24</v>
       </c>
       <c r="AX11" t="n">
-        <v>19</v>
+        <v>1.16</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>1.24</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>1.18</v>
       </c>
       <c r="BA11" t="n">
-        <v>28</v>
+        <v>1.24</v>
       </c>
       <c r="BB11" t="n">
-        <v>34</v>
+        <v>1.18</v>
       </c>
       <c r="BC11" t="n">
-        <v>22</v>
+        <v>1.17</v>
       </c>
       <c r="BD11" t="n">
-        <v>28</v>
+        <v>1.24</v>
       </c>
       <c r="BE11" t="n">
-        <v>50</v>
+        <v>1.24</v>
       </c>
       <c r="BF11" t="n">
-        <v>14</v>
+        <v>1.24</v>
       </c>
       <c r="BG11" t="n">
-        <v>14.5</v>
+        <v>1.24</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paris St-G</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.97</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>1.99</v>
+        <v>5.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>2.22</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>1.62</v>
       </c>
       <c r="O12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.21</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV12" t="n">
         <v>9</v>
       </c>
-      <c r="AD12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AW12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY12" t="n">
         <v>15</v>
       </c>
-      <c r="AI12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AZ12" t="n">
         <v>17.5</v>
       </c>
-      <c r="AL12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BA12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="BC12" t="n">
-        <v>16.5</v>
+        <v>46</v>
       </c>
       <c r="BD12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="BE12" t="n">
         <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="H13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.56</v>
-      </c>
       <c r="Q13" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>1.05</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.83</v>
+        <v>2.64</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.5</v>
+        <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.9</v>
+        <v>46</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.3</v>
+        <v>23</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.38</v>
+        <v>34</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.44</v>
+        <v>48</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.4</v>
+        <v>85</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.42</v>
+        <v>85</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.44</v>
+        <v>120</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.02</v>
+        <v>95</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.12</v>
+        <v>4.3</v>
       </c>
       <c r="G14" t="n">
-        <v>2.24</v>
+        <v>6.4</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>1.82</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>2.16</v>
       </c>
       <c r="J14" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.46</v>
+        <v>1.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="P14" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.86</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.17</v>
       </c>
-      <c r="S14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="X14" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="G15" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.12</v>
       </c>
-      <c r="N15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.19</v>
-      </c>
       <c r="S15" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="X15" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.33</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.39</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="X16" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB16" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AC16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX16" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="AY16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD16" t="n">
         <v>24</v>
       </c>
-      <c r="AL16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT16" t="n">
+      <c r="BE16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF16" t="n">
         <v>9</v>
       </c>
-      <c r="AU16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>16</v>
-      </c>
       <c r="BG16" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.58</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.42</v>
-      </c>
       <c r="X17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD17" t="n">
         <v>12</v>
       </c>
-      <c r="Y17" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO17" t="n">
         <v>17</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AP17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW17" t="n">
         <v>23</v>
       </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AX17" t="n">
-        <v>4.1</v>
+        <v>18.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.2</v>
+        <v>34</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>48</v>
       </c>
       <c r="BF17" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="H18" t="n">
-        <v>6.8</v>
+        <v>2.96</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BD18" t="n">
         <v>3.25</v>
       </c>
-      <c r="K18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="X18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>270</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5</v>
-      </c>
       <c r="BE18" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="BF18" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>2.08</v>
       </c>
       <c r="J19" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>2.42</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>1.51</v>
+        <v>2.52</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.34</v>
+        <v>1.64</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="S19" t="n">
-        <v>1.05</v>
+        <v>2.58</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>1.56</v>
       </c>
       <c r="U19" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.92</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X19" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD19" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AE19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO19" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AP19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS19" t="n">
         <v>23</v>
       </c>
-      <c r="AA19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH19" t="n">
+      <c r="AT19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX19" t="n">
         <v>28</v>
       </c>
-      <c r="AI19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AY19" t="n">
-        <v>3.45</v>
+        <v>14.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.75</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.1</v>
+        <v>23</v>
       </c>
       <c r="BB19" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="BC19" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.1</v>
+        <v>34</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.2</v>
+        <v>50</v>
       </c>
       <c r="BF19" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="BG19" t="n">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,90 +4235,90 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.74</v>
+        <v>2.28</v>
       </c>
       <c r="G20" t="n">
-        <v>1.82</v>
+        <v>2.46</v>
       </c>
       <c r="H20" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="J20" t="n">
-        <v>3.75</v>
+        <v>2.92</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="O20" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.92</v>
+        <v>2.66</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>8.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA20" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AD20" t="n">
         <v>22</v>
@@ -4327,99 +4327,99 @@
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY20" t="n">
         <v>11</v>
       </c>
-      <c r="AG20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH20" t="n">
+      <c r="AZ20" t="n">
         <v>21</v>
       </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK20" t="n">
+      <c r="BA20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF20" t="n">
         <v>19.5</v>
       </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BG20" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.54</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>1.71</v>
+        <v>2.24</v>
       </c>
       <c r="H21" t="n">
-        <v>1.09</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>2.86</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>1.49</v>
       </c>
       <c r="O21" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>1.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>2.56</v>
+        <v>1.8</v>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,78 +4623,78 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="O22" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="P22" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S22" t="n">
-        <v>1.34</v>
+        <v>2.58</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4706,7 +4706,7 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>2.24</v>
       </c>
       <c r="G23" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="H23" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="I23" t="n">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="L23" t="n">
         <v>1.4</v>
@@ -4855,153 +4855,153 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>1.96</v>
       </c>
       <c r="O23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="U23" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="W23" t="n">
-        <v>2.84</v>
+        <v>1.76</v>
       </c>
       <c r="X23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>980</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>980</v>
+      </c>
+      <c r="AD23" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y23" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>350</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>980</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY23" t="n">
         <v>10</v>
       </c>
-      <c r="AD23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AW23" t="n">
+      <c r="AZ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BF23" t="n">
         <v>15.5</v>
       </c>
-      <c r="AX23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG23" t="n">
-        <v>5.8</v>
+        <v>2.34</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>1.57</v>
       </c>
       <c r="G24" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="H24" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="I24" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.95</v>
+        <v>1.09</v>
       </c>
       <c r="K24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P24" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V24" t="n">
         <v>1.14</v>
       </c>
       <c r="W24" t="n">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="X24" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,75 +5205,75 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Atl Tucuman</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.89</v>
+        <v>2.64</v>
       </c>
       <c r="G25" t="n">
-        <v>2.12</v>
+        <v>3.65</v>
       </c>
       <c r="H25" t="n">
-        <v>4.7</v>
+        <v>2.66</v>
       </c>
       <c r="I25" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="O25" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="R25" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="S25" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="W25" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="X25" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
         <v>1000</v>
@@ -5282,13 +5282,13 @@
         <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
         <v>1000</v>
@@ -5297,16 +5297,16 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
         <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
         <v>1000</v>
@@ -5318,7 +5318,7 @@
         <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
@@ -5399,378 +5399,1736 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H26" t="n">
-        <v>7.2</v>
+        <v>1.43</v>
       </c>
       <c r="I26" t="n">
-        <v>8.6</v>
+        <v>240</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K26" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="M26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T26" t="n">
         <v>1.11</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S26" t="n">
-        <v>5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.36</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W26" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="X26" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 08:29:50</t>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>EC Vitoria Salvador</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:37:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Independiente Yumbo</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>11</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:37:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20:15:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Lobos UPNFM</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K29" t="n">
+        <v>950</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:37:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>980</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>980</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:37:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:37:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:37:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Atl Tucuman</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G33" t="n">
+        <v>110</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I33" t="n">
+        <v>990</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:37:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Boyaca Patriotas</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Quindio</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="F34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H34" t="n">
         <v>4</v>
       </c>
-      <c r="I27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="I34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T34" t="n">
         <v>1.11</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="X27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-03-10 08:29:50</t>
+      <c r="U34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-10 10:37:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="G2" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP2" t="n">
         <v>3.6</v>
       </c>
-      <c r="K2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -951,52 +951,52 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="I3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="J3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V3" t="n">
         <v>4.7</v>
@@ -1005,116 +1005,116 @@
         <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AC3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AG3" t="n">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI3" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.78</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.48</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.34</v>
+        <v>6.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.84</v>
+        <v>5.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.64</v>
+        <v>4.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.54</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.86</v>
+        <v>5.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.94</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.82</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.94</v>
+        <v>6.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.94</v>
+        <v>6.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="I4" t="n">
         <v>2.08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
         <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W4" t="n">
         <v>1.3</v>
       </c>
       <c r="X4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD4" t="n">
         <v>32</v>
       </c>
-      <c r="Y4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.06</v>
-      </c>
       <c r="BE4" t="n">
-        <v>2.12</v>
+        <v>4.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.07</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1.07</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="R5" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1423,16 +1423,16 @@
         <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -1533,52 +1533,52 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.07</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.07</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V6" t="n">
         <v>1.15</v>
@@ -1587,116 +1587,116 @@
         <v>2.28</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="H7" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>2.86</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.07</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R8" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>980</v>
       </c>
       <c r="Y8" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="Z8" t="n">
         <v>60</v>
@@ -1993,98 +1993,98 @@
         <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE8" t="n">
         <v>110</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI8" t="n">
         <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AL8" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AM8" t="n">
         <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>3.65</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>6</v>
+        <v>2.98</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.4</v>
+        <v>3.15</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>13.5</v>
+        <v>3.65</v>
       </c>
       <c r="BD8" t="n">
-        <v>27</v>
+        <v>3.95</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -2115,91 +2115,91 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.2</v>
       </c>
-      <c r="G9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.35</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AF9" t="n">
         <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2226,59 +2226,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -2512,46 +2512,46 @@
         <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
         <v>5.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>1.49</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>2.44</v>
       </c>
       <c r="V11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
         <v>2.26</v>
@@ -2614,59 +2614,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.24</v>
+        <v>5.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.24</v>
+        <v>5.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.24</v>
+        <v>3.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.16</v>
+        <v>5.7</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.24</v>
+        <v>5.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.18</v>
+        <v>4.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.18</v>
+        <v>3.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.17</v>
+        <v>3.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.24</v>
+        <v>4.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -2700,157 +2700,157 @@
         <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I12" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
         <v>1.01</v>
       </c>
-      <c r="M12" t="n">
+      <c r="AQ12" t="n">
         <v>1.01</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="AR12" t="n">
         <v>1.01</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AS12" t="n">
         <v>1.01</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AT12" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>6.8</v>
       </c>
       <c r="H13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I13" t="n">
         <v>1.61</v>
@@ -2909,7 +2909,7 @@
         <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -2921,10 +2921,10 @@
         <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
         <v>1.39</v>
@@ -2933,7 +2933,7 @@
         <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
         <v>1.94</v>
@@ -2945,19 +2945,19 @@
         <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y13" t="n">
         <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>15</v>
       </c>
       <c r="AB13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC13" t="n">
         <v>9.6</v>
@@ -2978,16 +2978,16 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>340</v>
+        <v>240</v>
       </c>
       <c r="AK13" t="n">
         <v>100</v>
       </c>
       <c r="AL13" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AM13" t="n">
         <v>140</v>
@@ -2996,7 +2996,7 @@
         <v>130</v>
       </c>
       <c r="AO13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP13" t="n">
         <v>14.5</v>
@@ -3005,7 +3005,7 @@
         <v>7.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS13" t="n">
         <v>14</v>
@@ -3023,7 +3023,7 @@
         <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AY13" t="n">
         <v>23</v>
@@ -3041,20 +3041,20 @@
         <v>85</v>
       </c>
       <c r="BD13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BE13" t="n">
         <v>120</v>
       </c>
       <c r="BF13" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="BG13" t="n">
         <v>8.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="I14" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
@@ -3109,146 +3109,146 @@
         <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="O14" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P14" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="R14" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN14" t="n">
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -3282,103 +3282,103 @@
         <v>2.72</v>
       </c>
       <c r="G15" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="O15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.64</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.11</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AN15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
         <v>3.9</v>
@@ -3497,13 +3497,13 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q16" t="n">
         <v>1.62</v>
@@ -3512,7 +3512,7 @@
         <v>1.61</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T16" t="n">
         <v>1.6</v>
@@ -3524,16 +3524,16 @@
         <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X16" t="n">
         <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA16" t="n">
         <v>70</v>
@@ -3542,7 +3542,7 @@
         <v>13.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
         <v>16</v>
@@ -3575,7 +3575,7 @@
         <v>60</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO16" t="n">
         <v>30</v>
@@ -3590,13 +3590,13 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT16" t="n">
         <v>12.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV16" t="n">
         <v>15</v>
@@ -3605,7 +3605,7 @@
         <v>34</v>
       </c>
       <c r="AX16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
         <v>9.800000000000001</v>
@@ -3614,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB16" t="n">
         <v>22</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H17" t="n">
         <v>2.66</v>
@@ -3685,25 +3685,25 @@
         <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S17" t="n">
         <v>2.74</v>
@@ -3721,16 +3721,16 @@
         <v>1.58</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB17" t="n">
         <v>15</v>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
@@ -3757,25 +3757,25 @@
         <v>32</v>
       </c>
       <c r="AJ17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK17" t="n">
         <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
         <v>17</v>
       </c>
       <c r="AP17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3790,7 +3790,7 @@
         <v>14</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
         <v>11.5</v>
@@ -3820,17 +3820,17 @@
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="P18" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="R18" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>2.52</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
         <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG18" t="n">
         <v>12</v>
       </c>
-      <c r="Y18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z18" t="n">
+      <c r="AH18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
         <v>32</v>
       </c>
-      <c r="AA18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AL18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>450</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX18" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.1</v>
+        <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G19" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I19" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -4073,40 +4073,40 @@
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O19" t="n">
         <v>1.21</v>
       </c>
       <c r="P19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.52</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.58</v>
-      </c>
       <c r="T19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U19" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V19" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="W19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
@@ -4115,10 +4115,10 @@
         <v>13.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB19" t="n">
         <v>19.5</v>
@@ -4145,25 +4145,25 @@
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
         <v>34</v>
       </c>
       <c r="AL19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM19" t="n">
         <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>10.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ19" t="n">
         <v>12.5</v>
@@ -4172,10 +4172,10 @@
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU19" t="n">
         <v>9</v>
@@ -4187,10 +4187,10 @@
         <v>17.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
         <v>14</v>
@@ -4199,26 +4199,26 @@
         <v>23</v>
       </c>
       <c r="BB19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BC19" t="n">
         <v>32</v>
       </c>
       <c r="BD19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE19" t="n">
         <v>50</v>
       </c>
       <c r="BF19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G20" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="H20" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J20" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>3.25</v>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
@@ -4279,7 +4279,7 @@
         <v>1.55</v>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q20" t="n">
         <v>2.66</v>
@@ -4288,118 +4288,118 @@
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>2.66</v>
+        <v>5.5</v>
       </c>
       <c r="T20" t="n">
         <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W20" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="X20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AC20" t="n">
         <v>7.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ20" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR20" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT20" t="n">
         <v>6.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW20" t="n">
         <v>42</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BB20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC20" t="n">
         <v>25</v>
       </c>
-      <c r="BC20" t="n">
-        <v>21</v>
-      </c>
       <c r="BD20" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BE20" t="n">
         <v>48</v>
@@ -4408,11 +4408,11 @@
         <v>19.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -4449,46 +4449,46 @@
         <v>2.24</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="K21" t="n">
         <v>3.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="M21" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="O21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.61</v>
+        <v>2.82</v>
       </c>
       <c r="R21" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V21" t="n">
         <v>1.25</v>
@@ -4497,116 +4497,116 @@
         <v>1.8</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -4637,64 +4637,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="J22" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N22" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="O22" t="n">
-        <v>1.09</v>
+        <v>1.48</v>
       </c>
       <c r="P22" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="R22" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>2.58</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.78</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.69</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AT22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU22" t="n">
         <v>3.8</v>
       </c>
-      <c r="AU22" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AV22" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.9</v>
+        <v>2.98</v>
       </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.1</v>
+        <v>2.46</v>
       </c>
       <c r="BF22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -4831,43 +4831,43 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="G23" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I23" t="n">
         <v>3.5</v>
       </c>
-      <c r="I23" t="n">
-        <v>3.55</v>
-      </c>
       <c r="J23" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.96</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P23" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
         <v>3.55</v>
@@ -4879,34 +4879,34 @@
         <v>2.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="X23" t="n">
         <v>13.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>980</v>
+        <v>16</v>
       </c>
       <c r="Z23" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AA23" t="n">
         <v>65</v>
       </c>
       <c r="AB23" t="n">
-        <v>980</v>
+        <v>10</v>
       </c>
       <c r="AC23" t="n">
-        <v>980</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
         <v>14.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
         <v>14.5</v>
@@ -4915,40 +4915,40 @@
         <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>980</v>
       </c>
       <c r="AJ23" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AK23" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AL23" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AM23" t="n">
         <v>95</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT23" t="n">
         <v>9</v>
@@ -4957,13 +4957,13 @@
         <v>7.2</v>
       </c>
       <c r="AV23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX23" t="n">
         <v>13</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>3.45</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
@@ -4972,29 +4972,29 @@
         <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.2</v>
+        <v>42</v>
       </c>
       <c r="BB23" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="BC23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.34</v>
+        <v>34</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.42</v>
+        <v>15.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.34</v>
+        <v>32</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -5025,64 +5025,64 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G24" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H24" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="I24" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
         <v>4.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1</v>
+        <v>2.86</v>
       </c>
       <c r="O24" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="R24" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V24" t="n">
         <v>1.14</v>
       </c>
       <c r="W24" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -5091,10 +5091,10 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD24" t="n">
         <v>1000</v>
@@ -5103,10 +5103,10 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
         <v>1000</v>
@@ -5115,10 +5115,10 @@
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL24" t="n">
         <v>1000</v>
@@ -5127,68 +5127,68 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="G25" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="H25" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="J25" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="O25" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="R25" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V25" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W25" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK25" t="n">
         <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -5416,49 +5416,49 @@
         <v>1.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H26" t="n">
-        <v>1.43</v>
+        <v>6.8</v>
       </c>
       <c r="I26" t="n">
-        <v>240</v>
+        <v>7.8</v>
       </c>
       <c r="J26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M26" t="n">
         <v>1.14</v>
       </c>
       <c r="N26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
         <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S26" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>2.64</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="V26" t="n">
         <v>1.14</v>
@@ -5467,40 +5467,40 @@
         <v>2.26</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH26" t="n">
         <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AJ26" t="n">
         <v>1000</v>
@@ -5509,10 +5509,10 @@
         <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AN26" t="n">
         <v>1000</v>
@@ -5521,62 +5521,62 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -5607,170 +5607,170 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="G27" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I27" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K27" t="n">
         <v>3.85</v>
       </c>
       <c r="L27" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T27" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.78</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="V27" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG27" t="n">
         <v>10</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="n">
         <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.13</v>
+        <v>15.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.13</v>
+        <v>34</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.13</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.13</v>
+        <v>7.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.13</v>
+        <v>7.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.13</v>
+        <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.13</v>
+        <v>9</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.13</v>
+        <v>18.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.13</v>
+        <v>8.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.13</v>
+        <v>15.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.13</v>
+        <v>16</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.13</v>
+        <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.13</v>
+        <v>9</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -5801,170 +5801,170 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="G28" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="H28" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="I28" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="J28" t="n">
-        <v>2.76</v>
+        <v>3.85</v>
       </c>
       <c r="K28" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="L28" t="n">
         <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>1.28</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
         <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.36</v>
+        <v>2.06</v>
       </c>
       <c r="R28" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="T28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V28" t="n">
         <v>1.11</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W28" t="n">
-        <v>1.73</v>
+        <v>2.56</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -6195,43 +6195,43 @@
         <v>1.55</v>
       </c>
       <c r="H30" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I30" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="J30" t="n">
         <v>4.3</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M30" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>1.33</v>
       </c>
       <c r="P30" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
         <v>2.02</v>
       </c>
       <c r="R30" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T30" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
         <v>1.83</v>
@@ -6246,34 +6246,34 @@
         <v>14.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="Z30" t="n">
         <v>70</v>
       </c>
       <c r="AA30" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD30" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AE30" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AG30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
         <v>150</v>
@@ -6285,74 +6285,74 @@
         <v>17</v>
       </c>
       <c r="AL30" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AM30" t="n">
         <v>200</v>
       </c>
       <c r="AN30" t="n">
-        <v>980</v>
+        <v>9</v>
       </c>
       <c r="AO30" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AP30" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
         <v>18.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT30" t="n">
         <v>6.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AV30" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="AW30" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AX30" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="BB30" t="n">
         <v>12</v>
       </c>
       <c r="BC30" t="n">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="BF30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -6383,170 +6383,170 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G31" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="H31" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
         <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L31" t="n">
         <v>1.46</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="V31" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W31" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX31" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AY31" t="n">
-        <v>1.17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.17</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.17</v>
+        <v>6.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.17</v>
+        <v>13.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.17</v>
+        <v>17</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.17</v>
+        <v>6</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.17</v>
+        <v>10.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -6577,170 +6577,170 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G32" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H32" t="n">
-        <v>1.37</v>
+        <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J32" t="n">
-        <v>1.15</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
         <v>3.9</v>
       </c>
       <c r="L32" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
         <v>1.11</v>
       </c>
       <c r="N32" t="n">
-        <v>1.54</v>
+        <v>2.68</v>
       </c>
       <c r="O32" t="n">
         <v>1.51</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.51</v>
+        <v>2.52</v>
       </c>
       <c r="R32" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S32" t="n">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="U32" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V32" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W32" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -6771,19 +6771,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="G33" t="n">
-        <v>110</v>
+        <v>2.22</v>
       </c>
       <c r="H33" t="n">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="I33" t="n">
-        <v>990</v>
+        <v>6.4</v>
       </c>
       <c r="J33" t="n">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="K33" t="n">
         <v>3.55</v>
@@ -6795,34 +6795,34 @@
         <v>1.12</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O33" t="n">
         <v>1.12</v>
       </c>
       <c r="P33" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="R33" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S33" t="n">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W33" t="n">
-        <v>1.23</v>
+        <v>1.81</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>
@@ -6965,170 +6965,170 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="G34" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I34" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="J34" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="L34" t="n">
         <v>1.49</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>1.97</v>
+        <v>2.44</v>
       </c>
       <c r="O34" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="P34" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="R34" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="S34" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U34" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W34" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-10 10:37:33</t>
+          <t>2026-03-10 12:45:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -757,31 +757,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="O2" t="n">
         <v>1.28</v>
@@ -790,49 +790,49 @@
         <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
         <v>2.26</v>
       </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA2" t="n">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
         <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF2" t="n">
         <v>11.5</v>
@@ -841,10 +841,10 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
         <v>18.5</v>
@@ -853,74 +853,74 @@
         <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
         <v>11</v>
       </c>
       <c r="AO2" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.85</v>
+        <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
         <v>5.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
         <v>2.6</v>
@@ -1092,7 +1092,7 @@
         <v>5.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
         <v>6.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
         <v>34</v>
@@ -1277,7 +1277,7 @@
         <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
         <v>14</v>
@@ -1292,13 +1292,13 @@
         <v>4.6</v>
       </c>
       <c r="BC4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD4" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD4" t="n">
-        <v>32</v>
-      </c>
       <c r="BE4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF4" t="n">
         <v>22</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
         <v>2.42</v>
@@ -1348,13 +1348,13 @@
         <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.38</v>
@@ -1363,7 +1363,7 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>1.33</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>1.78</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>7.4</v>
@@ -1551,19 +1551,19 @@
         <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
         <v>1.84</v>
@@ -1572,13 +1572,13 @@
         <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V6" t="n">
         <v>1.15</v>
@@ -1641,10 +1641,10 @@
         <v>140</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AR6" t="n">
         <v>4.7</v>
@@ -1653,13 +1653,13 @@
         <v>5.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.3</v>
+        <v>19.5</v>
       </c>
       <c r="AW6" t="n">
         <v>5</v>
@@ -1668,19 +1668,19 @@
         <v>3.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.3</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
         <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
         <v>4.7</v>
@@ -1689,14 +1689,14 @@
         <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.7</v>
+        <v>9.6</v>
       </c>
       <c r="BG6" t="n">
         <v>5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="G7" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="T7" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
         <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="X7" t="n">
         <v>23</v>
@@ -1787,7 +1787,7 @@
         <v>26</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
@@ -1802,10 +1802,10 @@
         <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
@@ -1817,80 +1817,80 @@
         <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC7" t="n">
         <v>14</v>
       </c>
-      <c r="BC7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
         <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="I8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
         <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
         <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X8" t="n">
         <v>980</v>
@@ -1987,7 +1987,7 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
         <v>11</v>
@@ -2002,7 +2002,7 @@
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>980</v>
+        <v>950</v>
       </c>
       <c r="AH8" t="n">
         <v>980</v>
@@ -2026,7 +2026,7 @@
         <v>980</v>
       </c>
       <c r="AO8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP8" t="n">
         <v>3.5</v>
@@ -2038,10 +2038,10 @@
         <v>4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AU8" t="n">
         <v>3.1</v>
@@ -2050,19 +2050,19 @@
         <v>3.75</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.7</v>
+        <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
         <v>3.6</v>
@@ -2071,20 +2071,20 @@
         <v>3.65</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
         <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
         <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -2271,14 +2271,14 @@
         <v>4.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BG9" t="n">
         <v>4.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
@@ -2351,22 +2351,22 @@
         <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
         <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="X10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="Z10" t="n">
         <v>27</v>
@@ -2375,7 +2375,7 @@
         <v>65</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
         <v>8.800000000000001</v>
@@ -2387,7 +2387,7 @@
         <v>42</v>
       </c>
       <c r="AF10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
         <v>13</v>
@@ -2399,13 +2399,13 @@
         <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM10" t="n">
         <v>95</v>
@@ -2414,7 +2414,7 @@
         <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
         <v>12</v>
@@ -2426,7 +2426,7 @@
         <v>17.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
         <v>8.6</v>
@@ -2438,7 +2438,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2450,29 +2450,29 @@
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BC10" t="n">
         <v>19</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
         <v>5.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
         <v>5.3</v>
@@ -2530,22 +2530,22 @@
         <v>5.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S11" t="n">
         <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
         <v>2.44</v>
@@ -2614,59 +2614,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY11" t="n">
         <v>5.3</v>
       </c>
-      <c r="AV11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.6</v>
+        <v>2.42</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="BF11" t="n">
         <v>4.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -2697,94 +2697,94 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="G12" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="I12" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.84</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ12" t="n">
         <v>1000</v>
@@ -2799,68 +2799,68 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="I13" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.39</v>
@@ -2918,19 +2918,19 @@
         <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
         <v>2.02</v>
@@ -2939,10 +2939,10 @@
         <v>1.94</v>
       </c>
       <c r="V13" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
         <v>15</v>
@@ -2951,16 +2951,16 @@
         <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
         <v>9.800000000000001</v>
@@ -2969,10 +2969,10 @@
         <v>17</v>
       </c>
       <c r="AF13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH13" t="n">
         <v>24</v>
@@ -2981,13 +2981,13 @@
         <v>38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AK13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL13" t="n">
         <v>100</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>95</v>
       </c>
       <c r="AM13" t="n">
         <v>140</v>
@@ -2996,7 +2996,7 @@
         <v>130</v>
       </c>
       <c r="AO13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AP13" t="n">
         <v>14.5</v>
@@ -3005,43 +3005,43 @@
         <v>7.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT13" t="n">
         <v>19.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AV13" t="n">
         <v>9.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AY13" t="n">
         <v>23</v>
       </c>
       <c r="AZ13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA13" t="n">
         <v>34</v>
       </c>
       <c r="BB13" t="n">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="BC13" t="n">
+        <v>95</v>
+      </c>
+      <c r="BD13" t="n">
         <v>85</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>80</v>
       </c>
       <c r="BE13" t="n">
         <v>120</v>
@@ -3050,11 +3050,11 @@
         <v>110</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>5.7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="I14" t="n">
         <v>2.02</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -3285,10 +3285,10 @@
         <v>3.05</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>2.68</v>
@@ -3303,7 +3303,7 @@
         <v>1.16</v>
       </c>
       <c r="N15" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O15" t="n">
         <v>1.66</v>
@@ -3312,7 +3312,7 @@
         <v>1.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
         <v>1.14</v>
@@ -3330,10 +3330,10 @@
         <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="Y15" t="n">
         <v>9.6</v>
@@ -3396,7 +3396,7 @@
         <v>13.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT15" t="n">
         <v>6.4</v>
@@ -3408,7 +3408,7 @@
         <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX15" t="n">
         <v>12</v>
@@ -3417,32 +3417,32 @@
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BA15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC15" t="n">
         <v>5.3</v>
       </c>
-      <c r="BB15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD15" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF15" t="n">
         <v>5.5</v>
       </c>
-      <c r="BF15" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG15" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -3509,13 +3509,13 @@
         <v>1.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U16" t="n">
         <v>2.6</v>
@@ -3527,7 +3527,7 @@
         <v>1.98</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="n">
         <v>20</v>
@@ -3554,7 +3554,7 @@
         <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH16" t="n">
         <v>15</v>
@@ -3590,7 +3590,7 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT16" t="n">
         <v>12.5</v>
@@ -3629,14 +3629,14 @@
         <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G17" t="n">
         <v>2.7</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I17" t="n">
         <v>2.72</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.68</v>
       </c>
       <c r="J17" t="n">
         <v>3.85</v>
@@ -3694,7 +3694,7 @@
         <v>5.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P17" t="n">
         <v>2.36</v>
@@ -3712,10 +3712,10 @@
         <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
         <v>1.58</v>
@@ -3727,7 +3727,7 @@
         <v>14.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA17" t="n">
         <v>40</v>
@@ -3748,7 +3748,7 @@
         <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
         <v>14.5</v>
@@ -3757,7 +3757,7 @@
         <v>32</v>
       </c>
       <c r="AJ17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
         <v>25</v>
@@ -3769,13 +3769,13 @@
         <v>65</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3802,16 +3802,16 @@
         <v>18.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC17" t="n">
         <v>23</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -3861,94 +3861,94 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="O18" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="R18" t="n">
         <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V18" t="n">
         <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>70</v>
       </c>
       <c r="AF18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
         <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AJ18" t="n">
         <v>1000</v>
@@ -3957,74 +3957,74 @@
         <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>450</v>
+        <v>190</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
         <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="AS18" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF18" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BG18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="G19" t="n">
         <v>3.6</v>
       </c>
-      <c r="G19" t="n">
-        <v>3.65</v>
-      </c>
       <c r="H19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I19" t="n">
         <v>2.12</v>
@@ -4082,13 +4082,13 @@
         <v>5.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R19" t="n">
         <v>1.64</v>
@@ -4097,7 +4097,7 @@
         <v>2.52</v>
       </c>
       <c r="T19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U19" t="n">
         <v>2.66</v>
@@ -4106,7 +4106,7 @@
         <v>1.89</v>
       </c>
       <c r="W19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
@@ -4124,7 +4124,7 @@
         <v>19.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>10.5</v>
@@ -4154,7 +4154,7 @@
         <v>38</v>
       </c>
       <c r="AM19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN19" t="n">
         <v>25</v>
@@ -4169,7 +4169,7 @@
         <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
         <v>24</v>
@@ -4181,7 +4181,7 @@
         <v>9</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
         <v>17.5</v>
@@ -4211,14 +4211,14 @@
         <v>50</v>
       </c>
       <c r="BF19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H20" t="n">
         <v>3.85</v>
@@ -4264,7 +4264,7 @@
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.56</v>
@@ -4285,7 +4285,7 @@
         <v>2.66</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
         <v>5.5</v>
@@ -4294,7 +4294,7 @@
         <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V20" t="n">
         <v>1.31</v>
@@ -4318,7 +4318,7 @@
         <v>7.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD20" t="n">
         <v>18</v>
@@ -4345,7 +4345,7 @@
         <v>36</v>
       </c>
       <c r="AL20" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
         <v>230</v>
@@ -4357,7 +4357,7 @@
         <v>120</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>9.199999999999999</v>
@@ -4378,7 +4378,7 @@
         <v>15.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>4.9</v>
       </c>
       <c r="J21" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K21" t="n">
         <v>3.1</v>
@@ -4467,7 +4467,7 @@
         <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.59</v>
@@ -4512,7 +4512,7 @@
         <v>6.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
         <v>21</v>
@@ -4557,10 +4557,10 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
         <v>5.9</v>
@@ -4572,7 +4572,7 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
@@ -4584,29 +4584,29 @@
         <v>22</v>
       </c>
       <c r="BA21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE21" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF21" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I22" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="J22" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
         <v>3.45</v>
       </c>
       <c r="L22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N22" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O22" t="n">
         <v>1.48</v>
@@ -4676,16 +4676,16 @@
         <v>1.2</v>
       </c>
       <c r="S22" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U22" t="n">
         <v>1.75</v>
       </c>
       <c r="V22" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="W22" t="n">
         <v>1.25</v>
@@ -4694,7 +4694,7 @@
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4706,7 +4706,7 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
         <v>3.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BA22" t="n">
-        <v>5.1</v>
+        <v>2.28</v>
       </c>
       <c r="BB22" t="n">
-        <v>2.44</v>
+        <v>1.73</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.98</v>
+        <v>2.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.46</v>
+        <v>1.74</v>
       </c>
       <c r="BF22" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>3.45</v>
       </c>
       <c r="I23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J23" t="n">
         <v>3.5</v>
@@ -4855,7 +4855,7 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.32</v>
@@ -4870,19 +4870,19 @@
         <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W23" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X23" t="n">
         <v>13.5</v>
@@ -4936,7 +4936,7 @@
         <v>18</v>
       </c>
       <c r="AO23" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="AP23" t="n">
         <v>13</v>
@@ -4948,10 +4948,10 @@
         <v>21</v>
       </c>
       <c r="AS23" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AT23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU23" t="n">
         <v>7.2</v>
@@ -4960,13 +4960,13 @@
         <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AX23" t="n">
         <v>13</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ23" t="n">
         <v>16</v>
@@ -4984,7 +4984,7 @@
         <v>34</v>
       </c>
       <c r="BE23" t="n">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="BF23" t="n">
         <v>16</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
         <v>1.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R24" t="n">
         <v>1.23</v>
@@ -5091,7 +5091,7 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC24" t="n">
         <v>9.4</v>
@@ -5118,7 +5118,7 @@
         <v>17.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
         <v>1000</v>
@@ -5136,13 +5136,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AR24" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT24" t="n">
         <v>5.4</v>
@@ -5151,10 +5151,10 @@
         <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX24" t="n">
         <v>7.4</v>
@@ -5163,10 +5163,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB24" t="n">
         <v>14</v>
@@ -5178,17 +5178,17 @@
         <v>42</v>
       </c>
       <c r="BE24" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF24" t="n">
         <v>11</v>
       </c>
       <c r="BG24" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H25" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I25" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>2.82</v>
@@ -5267,10 +5267,10 @@
         <v>1.77</v>
       </c>
       <c r="V25" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X25" t="n">
         <v>8.800000000000001</v>
@@ -5285,7 +5285,7 @@
         <v>60</v>
       </c>
       <c r="AB25" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
         <v>7.4</v>
@@ -5309,7 +5309,7 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK25" t="n">
         <v>1000</v>
@@ -5321,22 +5321,22 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP25" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR25" t="n">
         <v>15.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT25" t="n">
         <v>7.4</v>
@@ -5348,7 +5348,7 @@
         <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
         <v>15</v>
@@ -5360,29 +5360,29 @@
         <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BC25" t="n">
         <v>36</v>
       </c>
       <c r="BD25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF25" t="n">
         <v>38</v>
       </c>
       <c r="BG25" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G26" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="H26" t="n">
         <v>6.8</v>
@@ -5464,13 +5464,13 @@
         <v>1.14</v>
       </c>
       <c r="W26" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X26" t="n">
         <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
@@ -5479,19 +5479,19 @@
         <v>410</v>
       </c>
       <c r="AB26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
         <v>250</v>
       </c>
       <c r="AF26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
         <v>14.5</v>
@@ -5527,10 +5527,10 @@
         <v>12.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT26" t="n">
         <v>4.7</v>
@@ -5539,10 +5539,10 @@
         <v>7.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX26" t="n">
         <v>7</v>
@@ -5551,32 +5551,32 @@
         <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF26" t="n">
         <v>16</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -5622,34 +5622,34 @@
         <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
         <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U27" t="n">
         <v>1.97</v>
@@ -5664,7 +5664,7 @@
         <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z27" t="n">
         <v>44</v>
@@ -5676,7 +5676,7 @@
         <v>8.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
         <v>23</v>
@@ -5694,7 +5694,7 @@
         <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
         <v>19</v>
@@ -5721,22 +5721,22 @@
         <v>15.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>34</v>
+        <v>8.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT27" t="n">
         <v>7.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV27" t="n">
         <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
@@ -5748,10 +5748,10 @@
         <v>18.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB27" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC27" t="n">
         <v>16</v>
@@ -5760,17 +5760,17 @@
         <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF27" t="n">
         <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G28" t="n">
         <v>1.64</v>
@@ -5810,7 +5810,7 @@
         <v>7.2</v>
       </c>
       <c r="I28" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J28" t="n">
         <v>3.85</v>
@@ -5849,7 +5849,7 @@
         <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W28" t="n">
         <v>2.56</v>
@@ -5861,7 +5861,7 @@
         <v>22</v>
       </c>
       <c r="Z28" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
@@ -5957,14 +5957,14 @@
         <v>5.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="BG28" t="n">
         <v>5.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G30" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H30" t="n">
         <v>7.8</v>
@@ -6207,7 +6207,7 @@
         <v>4.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
@@ -6219,7 +6219,7 @@
         <v>1.33</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
         <v>2.02</v>
@@ -6240,7 +6240,7 @@
         <v>1.13</v>
       </c>
       <c r="W30" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X30" t="n">
         <v>14.5</v>
@@ -6309,7 +6309,7 @@
         <v>6.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU30" t="n">
         <v>9</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6440,7 @@
         <v>12.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z31" t="n">
         <v>65</v>
@@ -6461,7 +6461,7 @@
         <v>160</v>
       </c>
       <c r="AF31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG31" t="n">
         <v>12</v>
@@ -6476,7 +6476,7 @@
         <v>17</v>
       </c>
       <c r="AK31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
         <v>60</v>
@@ -6497,7 +6497,7 @@
         <v>17</v>
       </c>
       <c r="AR31" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS31" t="n">
         <v>6.6</v>
@@ -6509,7 +6509,7 @@
         <v>8.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
         <v>6.4</v>
@@ -6536,7 +6536,7 @@
         <v>6</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF31" t="n">
         <v>10.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J32" t="n">
         <v>3.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="G33" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="H33" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I33" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J33" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L33" t="n">
         <v>1.56</v>
@@ -6795,82 +6795,82 @@
         <v>1.12</v>
       </c>
       <c r="N33" t="n">
-        <v>1.26</v>
+        <v>2.62</v>
       </c>
       <c r="O33" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="P33" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="R33" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U33" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="V33" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W33" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z33" t="n">
         <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE33" t="n">
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ33" t="n">
         <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL33" t="n">
         <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN33" t="n">
         <v>1000</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>
@@ -6965,70 +6965,70 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="G34" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="H34" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="I34" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q34" t="n">
         <v>3</v>
       </c>
-      <c r="K34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.66</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="T34" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="U34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.66</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.86</v>
-      </c>
       <c r="X34" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB34" t="n">
         <v>7.6</v>
@@ -7040,7 +7040,7 @@
         <v>23</v>
       </c>
       <c r="AE34" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AF34" t="n">
         <v>13.5</v>
@@ -7049,86 +7049,86 @@
         <v>14</v>
       </c>
       <c r="AH34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AK34" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AL34" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AR34" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU34" t="n">
         <v>6.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AW34" t="n">
         <v>5.5</v>
       </c>
       <c r="AX34" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD34" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB34" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD34" t="n">
+      <c r="BE34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF34" t="n">
         <v>5.3</v>
       </c>
-      <c r="BE34" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG34" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-10 12:45:09</t>
+          <t>2026-03-10 14:53:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G2" t="n">
         <v>1.8</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
         <v>6.6</v>
@@ -844,7 +844,7 @@
         <v>26</v>
       </c>
       <c r="AI2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ2" t="n">
         <v>18.5</v>
@@ -901,13 +901,13 @@
         <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.9</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
         <v>4.8</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
         <v>19</v>
@@ -960,7 +960,7 @@
         <v>1.22</v>
       </c>
       <c r="I3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="J3" t="n">
         <v>6.8</v>
@@ -975,16 +975,16 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
         <v>1.67</v>
@@ -993,13 +993,13 @@
         <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
         <v>1.72</v>
       </c>
       <c r="V3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
@@ -1011,13 +1011,13 @@
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AA3" t="n">
         <v>10.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AC3" t="n">
         <v>20</v>
@@ -1029,10 +1029,10 @@
         <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AG3" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
         <v>44</v>
@@ -1044,7 +1044,7 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AL3" t="n">
         <v>230</v>
@@ -1053,68 +1053,68 @@
         <v>220</v>
       </c>
       <c r="AN3" t="n">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="AO3" t="n">
         <v>3.9</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ3" t="n">
         <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA3" t="n">
         <v>5.8</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BB3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC3" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
         <v>3.15</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="G4" t="n">
         <v>4.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="I4" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
         <v>4.9</v>
@@ -1175,7 +1175,7 @@
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
         <v>1.61</v>
@@ -1190,19 +1190,19 @@
         <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W4" t="n">
         <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
         <v>15.5</v>
@@ -1211,16 +1211,16 @@
         <v>28</v>
       </c>
       <c r="AB4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>34</v>
@@ -1229,10 +1229,10 @@
         <v>20</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ4" t="n">
         <v>90</v>
@@ -1244,10 +1244,10 @@
         <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO4" t="n">
         <v>10.5</v>
@@ -1259,7 +1259,7 @@
         <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS4" t="n">
         <v>19</v>
@@ -1277,7 +1277,7 @@
         <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
         <v>14</v>
@@ -1286,29 +1286,29 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>2.42</v>
@@ -1348,7 +1348,7 @@
         <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
@@ -1387,7 +1387,7 @@
         <v>1.98</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
         <v>1.71</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -1566,19 +1566,19 @@
         <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.9</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.89</v>
       </c>
       <c r="V6" t="n">
         <v>1.15</v>
@@ -1647,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS6" t="n">
         <v>5.1</v>
@@ -1665,7 +1665,7 @@
         <v>5</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AY6" t="n">
         <v>8.6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H7" t="n">
         <v>5.8</v>
@@ -1754,13 +1754,13 @@
         <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P7" t="n">
         <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R7" t="n">
         <v>1.48</v>
@@ -1772,7 +1772,7 @@
         <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
         <v>1.16</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
         <v>26</v>
@@ -1805,22 +1805,22 @@
         <v>90</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK7" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AO7" t="n">
         <v>95</v>
@@ -1841,10 +1841,10 @@
         <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT7" t="n">
         <v>8.199999999999999</v>
@@ -1856,7 +1856,7 @@
         <v>20</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -1868,7 +1868,7 @@
         <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
         <v>13</v>
@@ -1877,20 +1877,20 @@
         <v>14</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
         <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -1921,76 +1921,76 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="G8" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="P8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.14</v>
-      </c>
       <c r="X8" t="n">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
         <v>980</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>980</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>980</v>
@@ -1999,16 +1999,16 @@
         <v>110</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="AH8" t="n">
         <v>980</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
         <v>980</v>
@@ -2020,71 +2020,71 @@
         <v>980</v>
       </c>
       <c r="AM8" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
         <v>980</v>
       </c>
       <c r="AO8" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY8" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AZ8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4</v>
       </c>
-      <c r="AS8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>8</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
         <v>1.73</v>
       </c>
       <c r="I9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
         <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2157,13 +2157,13 @@
         <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W9" t="n">
         <v>1.2</v>
@@ -2226,7 +2226,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR9" t="n">
         <v>4.4</v>
@@ -2238,7 +2238,7 @@
         <v>5.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV9" t="n">
         <v>4.4</v>
@@ -2259,26 +2259,26 @@
         <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="BC9" t="n">
         <v>3.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
         <v>4.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="G10" t="n">
         <v>2.32</v>
@@ -2324,7 +2324,7 @@
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.3</v>
@@ -2336,13 +2336,13 @@
         <v>3.85</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
         <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R10" t="n">
         <v>1.38</v>
@@ -2426,7 +2426,7 @@
         <v>17.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT10" t="n">
         <v>8.6</v>
@@ -2438,7 +2438,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2450,16 +2450,16 @@
         <v>12.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC10" t="n">
         <v>19</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BE10" t="n">
         <v>5.8</v>
@@ -2468,11 +2468,11 @@
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -2503,25 +2503,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="G11" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
         <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
@@ -2530,31 +2530,31 @@
         <v>5.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.53</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.64</v>
-      </c>
       <c r="S11" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U11" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
         <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2605,7 +2605,7 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
@@ -2614,59 +2614,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE11" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BF11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.71</v>
+        <v>2.46</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="G12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.35</v>
@@ -2721,13 +2721,13 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
         <v>1.94</v>
@@ -2739,13 +2739,13 @@
         <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="W12" t="n">
         <v>1.24</v>
@@ -2766,7 +2766,7 @@
         <v>16</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
         <v>10.5</v>
@@ -2799,7 +2799,7 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
         <v>15</v>
@@ -2841,26 +2841,26 @@
         <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
         <v>10.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -2897,10 +2897,10 @@
         <v>7.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
@@ -2936,22 +2936,22 @@
         <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V13" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="W13" t="n">
         <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
         <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>14.5</v>
@@ -2996,7 +2996,7 @@
         <v>130</v>
       </c>
       <c r="AO13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP13" t="n">
         <v>14.5</v>
@@ -3014,7 +3014,7 @@
         <v>19.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13" t="n">
         <v>9.4</v>
@@ -3026,7 +3026,7 @@
         <v>50</v>
       </c>
       <c r="AY13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ13" t="n">
         <v>23</v>
@@ -3047,14 +3047,14 @@
         <v>120</v>
       </c>
       <c r="BF13" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BG13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U14" t="n">
         <v>1.72</v>
@@ -3217,7 +3217,7 @@
         <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
         <v>18.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G15" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J15" t="n">
         <v>2.68</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L15" t="n">
         <v>1.59</v>
@@ -3303,16 +3303,16 @@
         <v>1.16</v>
       </c>
       <c r="N15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
         <v>1.14</v>
@@ -3321,22 +3321,22 @@
         <v>6.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V15" t="n">
         <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z15" t="n">
         <v>980</v>
@@ -3345,7 +3345,7 @@
         <v>85</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC15" t="n">
         <v>8</v>
@@ -3354,7 +3354,7 @@
         <v>19</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF15" t="n">
         <v>19</v>
@@ -3372,7 +3372,7 @@
         <v>60</v>
       </c>
       <c r="AK15" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AL15" t="n">
         <v>110</v>
@@ -3393,56 +3393,56 @@
         <v>7.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
         <v>6.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
         <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -3482,10 +3482,10 @@
         <v>3.9</v>
       </c>
       <c r="I16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
@@ -3497,22 +3497,22 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q16" t="n">
         <v>1.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
         <v>1.59</v>
@@ -3542,7 +3542,7 @@
         <v>13.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>16</v>
@@ -3575,22 +3575,22 @@
         <v>60</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP16" t="n">
         <v>20</v>
       </c>
       <c r="AQ16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AT16" t="n">
         <v>12.5</v>
@@ -3605,7 +3605,7 @@
         <v>34</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY16" t="n">
         <v>9.800000000000001</v>
@@ -3614,13 +3614,13 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
         <v>22</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD16" t="n">
         <v>24</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>2.7</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I17" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.9</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -3697,13 +3697,13 @@
         <v>1.22</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
         <v>2.74</v>
@@ -3712,10 +3712,10 @@
         <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W17" t="n">
         <v>1.58</v>
@@ -3724,7 +3724,7 @@
         <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z17" t="n">
         <v>19.5</v>
@@ -3739,13 +3739,13 @@
         <v>8.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
         <v>25</v>
       </c>
       <c r="AF17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
         <v>12.5</v>
@@ -3757,7 +3757,7 @@
         <v>32</v>
       </c>
       <c r="AJ17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK17" t="n">
         <v>25</v>
@@ -3769,10 +3769,10 @@
         <v>65</v>
       </c>
       <c r="AN17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP17" t="n">
         <v>19</v>
@@ -3799,7 +3799,7 @@
         <v>23</v>
       </c>
       <c r="AX17" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY17" t="n">
         <v>12</v>
@@ -3808,10 +3808,10 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC17" t="n">
         <v>23</v>
@@ -3823,14 +3823,14 @@
         <v>50</v>
       </c>
       <c r="BF17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG17" t="n">
         <v>16</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
         <v>3.65</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
         <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>6.8</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3888,7 +3888,7 @@
         <v>2.86</v>
       </c>
       <c r="O18" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="P18" t="n">
         <v>1.62</v>
@@ -3903,16 +3903,16 @@
         <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X18" t="n">
         <v>12</v>
@@ -3948,7 +3948,7 @@
         <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
         <v>1000</v>
@@ -3972,13 +3972,13 @@
         <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="AR18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
         <v>6.8</v>
@@ -3987,10 +3987,10 @@
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
@@ -4002,29 +4002,29 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
         <v>18.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I19" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
@@ -4073,58 +4073,58 @@
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="Q19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T19" t="n">
         <v>1.61</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.56</v>
-      </c>
       <c r="U19" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="V19" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X19" t="n">
         <v>22</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA19" t="n">
         <v>26</v>
       </c>
       <c r="AB19" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD19" t="n">
         <v>10.5</v>
@@ -4133,7 +4133,7 @@
         <v>18.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG19" t="n">
         <v>15</v>
@@ -4142,43 +4142,43 @@
         <v>15</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ19" t="n">
         <v>65</v>
       </c>
       <c r="AK19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT19" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
@@ -4199,26 +4199,26 @@
         <v>23</v>
       </c>
       <c r="BB19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC19" t="n">
         <v>32</v>
       </c>
       <c r="BD19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE19" t="n">
         <v>50</v>
       </c>
       <c r="BF19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
         <v>4.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K20" t="n">
         <v>3.2</v>
@@ -4294,7 +4294,7 @@
         <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V20" t="n">
         <v>1.31</v>
@@ -4342,7 +4342,7 @@
         <v>36</v>
       </c>
       <c r="AK20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4366,7 +4366,7 @@
         <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AT20" t="n">
         <v>6.6</v>
@@ -4378,7 +4378,7 @@
         <v>15.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G21" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H21" t="n">
         <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K21" t="n">
         <v>3.1</v>
@@ -4482,22 +4482,22 @@
         <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T21" t="n">
         <v>2.24</v>
       </c>
       <c r="U21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y21" t="n">
         <v>12</v>
@@ -4518,7 +4518,7 @@
         <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF21" t="n">
         <v>13</v>
@@ -4530,7 +4530,7 @@
         <v>26</v>
       </c>
       <c r="AI21" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ21" t="n">
         <v>32</v>
@@ -4542,7 +4542,7 @@
         <v>70</v>
       </c>
       <c r="AM21" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN21" t="n">
         <v>34</v>
@@ -4557,10 +4557,10 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>5.9</v>
@@ -4572,7 +4572,7 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
@@ -4584,29 +4584,29 @@
         <v>22</v>
       </c>
       <c r="BA21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG21" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>8</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="I22" t="n">
         <v>2.22</v>
@@ -4652,7 +4652,7 @@
         <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.48</v>
@@ -4682,10 +4682,10 @@
         <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V22" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W22" t="n">
         <v>1.25</v>
@@ -4706,10 +4706,10 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="AW22" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="AX22" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="AY22" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.28</v>
+        <v>5.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.74</v>
+        <v>3.15</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
         <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
         <v>1.79</v>
@@ -4888,7 +4888,7 @@
         <v>13.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z23" t="n">
         <v>24</v>
@@ -4927,13 +4927,13 @@
         <v>25</v>
       </c>
       <c r="AL23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
         <v>95</v>
       </c>
       <c r="AN23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO23" t="n">
         <v>90</v>
@@ -4957,7 +4957,7 @@
         <v>7.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW23" t="n">
         <v>23</v>
@@ -4966,13 +4966,13 @@
         <v>13</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
         <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB23" t="n">
         <v>27</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G24" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="H24" t="n">
         <v>6.6</v>
@@ -5040,7 +5040,7 @@
         <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
         <v>1.48</v>
@@ -5076,7 +5076,7 @@
         <v>1.14</v>
       </c>
       <c r="W24" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X24" t="n">
         <v>11.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
         <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
         <v>55</v>
@@ -5315,16 +5315,16 @@
         <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
         <v>7.2</v>
@@ -5363,10 +5363,10 @@
         <v>8.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC25" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BD25" t="n">
         <v>8.4</v>
@@ -5375,14 +5375,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF25" t="n">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG25" t="n">
         <v>8.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G26" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H26" t="n">
         <v>6.8</v>
@@ -5464,13 +5464,13 @@
         <v>1.14</v>
       </c>
       <c r="W26" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X26" t="n">
         <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
@@ -5479,19 +5479,19 @@
         <v>410</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE26" t="n">
         <v>250</v>
       </c>
       <c r="AF26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG26" t="n">
         <v>14.5</v>
@@ -5527,10 +5527,10 @@
         <v>12.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT26" t="n">
         <v>4.7</v>
@@ -5539,10 +5539,10 @@
         <v>7.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX26" t="n">
         <v>7</v>
@@ -5551,10 +5551,10 @@
         <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB26" t="n">
         <v>15</v>
@@ -5563,20 +5563,20 @@
         <v>21</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF26" t="n">
         <v>16</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>5.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
         <v>3.8</v>
@@ -5640,19 +5640,19 @@
         <v>1.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R27" t="n">
         <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T27" t="n">
         <v>1.93</v>
       </c>
       <c r="U27" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V27" t="n">
         <v>1.2</v>
@@ -5721,7 +5721,7 @@
         <v>15.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="AS27" t="n">
         <v>9.4</v>
@@ -5766,11 +5766,11 @@
         <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G28" t="n">
         <v>1.64</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -6022,19 +6022,19 @@
         <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
         <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="T29" t="n">
         <v>1.11</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G30" t="n">
         <v>1.54</v>
@@ -6219,22 +6219,22 @@
         <v>1.33</v>
       </c>
       <c r="P30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U30" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V30" t="n">
         <v>1.13</v>
@@ -6252,7 +6252,7 @@
         <v>70</v>
       </c>
       <c r="AA30" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AB30" t="n">
         <v>7.4</v>
@@ -6273,7 +6273,7 @@
         <v>10.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI30" t="n">
         <v>150</v>
@@ -6285,31 +6285,31 @@
         <v>17</v>
       </c>
       <c r="AL30" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AM30" t="n">
         <v>200</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AP30" t="n">
         <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR30" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU30" t="n">
         <v>9</v>
@@ -6318,7 +6318,7 @@
         <v>27</v>
       </c>
       <c r="AW30" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AX30" t="n">
         <v>7.6</v>
@@ -6330,7 +6330,7 @@
         <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BB30" t="n">
         <v>12</v>
@@ -6339,20 +6339,20 @@
         <v>15.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="BE30" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BF30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG30" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
         <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
         <v>1.46</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
         <v>1.28</v>
       </c>
       <c r="W34" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X34" t="n">
         <v>8</v>
@@ -7100,7 +7100,7 @@
         <v>9.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ34" t="n">
         <v>5</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-10 14:53:58</t>
+          <t>2026-03-10 17:02:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="H2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I2" t="n">
         <v>5.2</v>
       </c>
-      <c r="I2" t="n">
-        <v>6.6</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Z2" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AO2" t="n">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.95</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="AU2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" t="n">
         <v>16</v>
-      </c>
-      <c r="G3" t="n">
-        <v>19</v>
       </c>
       <c r="H3" t="n">
         <v>1.22</v>
@@ -963,158 +963,158 @@
         <v>1.25</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="AC3" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AH3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>220</v>
       </c>
       <c r="AN3" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AU3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY3" t="n">
         <v>11</v>
       </c>
-      <c r="AX3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>5.9</v>
+        <v>30</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -1145,118 +1145,118 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="I4" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
         <v>4.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.32</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.36</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AB4" t="n">
         <v>21</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ4" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="AK4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AO4" t="n">
         <v>10.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
         <v>12</v>
@@ -1265,50 +1265,50 @@
         <v>19</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
         <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ4" t="n">
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>40</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1402,43 +1402,43 @@
         <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH5" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
         <v>4.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -1533,127 +1533,127 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
         <v>1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
         <v>2.28</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH6" t="n">
         <v>22</v>
       </c>
-      <c r="Z6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF6" t="n">
+      <c r="AI6" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN6" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>13</v>
-      </c>
       <c r="AO6" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -1662,10 +1662,10 @@
         <v>19.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="AY6" t="n">
         <v>8.6</v>
@@ -1674,7 +1674,7 @@
         <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="BB6" t="n">
         <v>14.5</v>
@@ -1683,20 +1683,20 @@
         <v>16</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>17.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
         <v>9.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="H7" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z7" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>10.5</v>
       </c>
       <c r="AC7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS7" t="n">
         <v>11</v>
       </c>
-      <c r="AD7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV7" t="n">
         <v>17</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AW7" t="n">
         <v>34</v>
       </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>7</v>
-      </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BB7" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G8" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
         <v>1.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
         <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="Z8" t="n">
         <v>980</v>
       </c>
       <c r="AA8" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
         <v>980</v>
       </c>
       <c r="AE8" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AH8" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AJ8" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AL8" t="n">
         <v>980</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AP8" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF8" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -2115,94 +2115,94 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="I9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="T9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.9</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.87</v>
       </c>
       <c r="V9" t="n">
         <v>2.16</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>980</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AA9" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>980</v>
+        <v>15.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG9" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AH9" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ9" t="n">
         <v>1000</v>
@@ -2211,7 +2211,7 @@
         <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2220,65 +2220,65 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG9" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.9</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U10" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
         <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
         <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO10" t="n">
         <v>40</v>
       </c>
-      <c r="AM10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>44</v>
-      </c>
       <c r="AP10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>12</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AR10" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.7</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
         <v>19</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE11" t="n">
         <v>4.2</v>
       </c>
-      <c r="K11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BF11" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.46</v>
+        <v>10</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -2700,88 +2700,88 @@
         <v>4.5</v>
       </c>
       <c r="G12" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="I12" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
         <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W12" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="n">
         <v>8.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA12" t="n">
         <v>22</v>
       </c>
       <c r="AB12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>10.5</v>
       </c>
       <c r="AE12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH12" t="n">
         <v>22</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>23</v>
       </c>
       <c r="AI12" t="n">
         <v>40</v>
@@ -2790,19 +2790,19 @@
         <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
         <v>12.5</v>
@@ -2811,28 +2811,28 @@
         <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW12" t="n">
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ12" t="n">
         <v>18</v>
@@ -2841,26 +2841,26 @@
         <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD12" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -2891,73 +2891,73 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="I13" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.04</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.02</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V13" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC13" t="n">
         <v>9.800000000000001</v>
@@ -2966,22 +2966,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE13" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AF13" t="n">
         <v>60</v>
       </c>
       <c r="AG13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="AK13" t="n">
         <v>110</v>
@@ -2990,43 +2990,43 @@
         <v>100</v>
       </c>
       <c r="AM13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN13" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AO13" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AP13" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT13" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AY13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ13" t="n">
         <v>23</v>
@@ -3035,26 +3035,26 @@
         <v>34</v>
       </c>
       <c r="BB13" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="BC13" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BD13" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BE13" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BF13" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="G14" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="I14" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
@@ -3103,58 +3103,58 @@
         <v>3.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="M14" t="n">
         <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="R14" t="n">
         <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V14" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Z14" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>11</v>
-      </c>
       <c r="AA14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
         <v>11.5</v>
@@ -3166,46 +3166,46 @@
         <v>42</v>
       </c>
       <c r="AG14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>190</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AL14" t="n">
         <v>140</v>
       </c>
       <c r="AM14" t="n">
-        <v>240</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
         <v>5.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU14" t="n">
         <v>6.8</v>
@@ -3217,7 +3217,7 @@
         <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY14" t="n">
         <v>18.5</v>
@@ -3226,29 +3226,29 @@
         <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -3279,106 +3279,106 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I15" t="n">
         <v>3.2</v>
       </c>
-      <c r="I15" t="n">
-        <v>3.65</v>
-      </c>
       <c r="J15" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="K15" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="L15" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="M15" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="N15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X15" t="n">
         <v>6.4</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X15" t="n">
-        <v>7</v>
-      </c>
       <c r="Y15" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
         <v>19</v>
       </c>
       <c r="AG15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AI15" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="AK15" t="n">
         <v>980</v>
       </c>
       <c r="AL15" t="n">
-        <v>110</v>
+        <v>270</v>
       </c>
       <c r="AM15" t="n">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>7.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS15" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AT15" t="n">
         <v>6.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.9</v>
+        <v>36</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD15" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG15" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -3473,82 +3473,82 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="G16" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.54</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.6</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="X16" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF16" t="n">
         <v>15</v>
@@ -3560,83 +3560,83 @@
         <v>15</v>
       </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM16" t="n">
         <v>60</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AO16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AS16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE16" t="n">
         <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="I17" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.8</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.85</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -3700,79 +3700,79 @@
         <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S17" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T17" t="n">
         <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V17" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W17" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
         <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
         <v>14.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP17" t="n">
         <v>19</v>
@@ -3781,28 +3781,28 @@
         <v>14</v>
       </c>
       <c r="AR17" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AX17" t="n">
         <v>17.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
@@ -3814,23 +3814,23 @@
         <v>34</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE17" t="n">
         <v>50</v>
       </c>
       <c r="BF17" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="H18" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N18" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="P18" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Z18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH18" t="n">
         <v>27</v>
       </c>
-      <c r="AA18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>25</v>
-      </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AL18" t="n">
         <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN18" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.9</v>
+        <v>16.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="H19" t="n">
         <v>2.06</v>
@@ -4067,85 +4067,85 @@
         <v>2.08</v>
       </c>
       <c r="J19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K19" t="n">
         <v>4</v>
       </c>
-      <c r="K19" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R19" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="T19" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U19" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="V19" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W19" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>10.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>29</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH19" t="n">
         <v>15</v>
       </c>
       <c r="AI19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AK19" t="n">
         <v>36</v>
@@ -4157,7 +4157,7 @@
         <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO19" t="n">
         <v>11</v>
@@ -4169,56 +4169,56 @@
         <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS19" t="n">
         <v>23</v>
       </c>
       <c r="AT19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BC19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF19" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -4249,70 +4249,70 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J20" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="O20" t="n">
         <v>1.55</v>
       </c>
       <c r="P20" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="R20" t="n">
         <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T20" t="n">
         <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y20" t="n">
         <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA20" t="n">
-        <v>110</v>
+        <v>270</v>
       </c>
       <c r="AB20" t="n">
         <v>7.4</v>
@@ -4327,7 +4327,7 @@
         <v>70</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -4336,37 +4336,37 @@
         <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="AJ20" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AK20" t="n">
         <v>34</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
         <v>36</v>
       </c>
       <c r="AO20" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AT20" t="n">
         <v>6.6</v>
@@ -4378,10 +4378,10 @@
         <v>15.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AX20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY20" t="n">
         <v>10.5</v>
@@ -4390,29 +4390,29 @@
         <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BB20" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="BC20" t="n">
         <v>25</v>
       </c>
       <c r="BD20" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BE20" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BF20" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BG20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G21" t="n">
         <v>2.18</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.28</v>
-      </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
         <v>3.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O21" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="P21" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="R21" t="n">
         <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="T21" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W21" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="X21" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AJ21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK21" t="n">
         <v>32</v>
       </c>
-      <c r="AK21" t="n">
-        <v>34</v>
-      </c>
       <c r="AL21" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM21" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU21" t="n">
         <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
       </c>
       <c r="AY21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.8</v>
+        <v>48</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.4</v>
+        <v>100</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BG21" t="n">
-        <v>8.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -4637,177 +4637,177 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="G22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S22" t="n">
         <v>5</v>
       </c>
-      <c r="H22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4.8</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V22" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="W22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>85</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA22" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA22" t="n">
+      <c r="BB22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BC22" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD22" t="n">
-        <v>3.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE22" t="n">
-        <v>3.15</v>
+        <v>9.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Genesis Huracan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.32</v>
+        <v>1.05</v>
       </c>
       <c r="G23" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>3.45</v>
+        <v>1.05</v>
       </c>
       <c r="I23" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.99</v>
+        <v>1.21</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>1.21</v>
       </c>
       <c r="T23" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.74</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7</v>
+        <v>2.32</v>
       </c>
       <c r="H24" t="n">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="I24" t="n">
-        <v>8.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="J24" t="n">
         <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L24" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>2.86</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>2.42</v>
+        <v>1.76</v>
       </c>
       <c r="X24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y24" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
+      <c r="AR24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF24" t="n">
         <v>17.5</v>
       </c>
-      <c r="AK24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>11</v>
-      </c>
       <c r="BG24" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -5205,184 +5205,184 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.68</v>
+        <v>1.78</v>
       </c>
       <c r="G25" t="n">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="H25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N25" t="n">
         <v>2.9</v>
       </c>
-      <c r="I25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.52</v>
-      </c>
       <c r="O25" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="P25" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="U25" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="W25" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="X25" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>250</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY25" t="n">
         <v>9</v>
       </c>
-      <c r="Z25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BD25" t="n">
         <v>8.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -5413,109 +5413,109 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L26" t="n">
         <v>1.68</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="H26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.62</v>
-      </c>
       <c r="M26" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N26" t="n">
         <v>2.34</v>
       </c>
       <c r="O26" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="P26" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.14</v>
       </c>
       <c r="S26" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="X26" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA26" t="n">
-        <v>410</v>
+        <v>700</v>
       </c>
       <c r="AB26" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
         <v>36</v>
       </c>
       <c r="AE26" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AF26" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG26" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AI26" t="n">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL26" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="AM26" t="n">
-        <v>520</v>
+        <v>700</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -5527,63 +5527,63 @@
         <v>12.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.7</v>
+        <v>34</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.2</v>
+        <v>110</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.4</v>
+        <v>29</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.5</v>
+        <v>34</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.2</v>
+        <v>110</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BD26" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.2</v>
+        <v>110</v>
       </c>
       <c r="BF26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.2</v>
+        <v>110</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Orsomarso</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.77</v>
+        <v>2.68</v>
       </c>
       <c r="G27" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>5.3</v>
+        <v>2.94</v>
       </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>2.92</v>
       </c>
       <c r="K27" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="L27" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>2.66</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="P27" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.02</v>
+        <v>2.72</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
-        <v>2.2</v>
+        <v>1.51</v>
       </c>
       <c r="X27" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y27" t="n">
-        <v>18.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z27" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
         <v>160</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS27" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
+      <c r="AT27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>19</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>18.5</v>
       </c>
       <c r="BA27" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BB27" t="n">
-        <v>16.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD27" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,31 +5792,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="G28" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="H28" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K28" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="L28" t="n">
         <v>1.43</v>
@@ -5825,153 +5825,153 @@
         <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P28" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="V28" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="W28" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="X28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH28" t="n">
         <v>22</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AI28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA28" t="n">
         <v>70</v>
       </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
+      <c r="BB28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC28" t="n">
         <v>17</v>
       </c>
-      <c r="AK28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>16</v>
-      </c>
       <c r="BD28" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG28" t="n">
         <v>38</v>
       </c>
-      <c r="BE28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>1.64</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O29" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>1.27</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>CD Motagua</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="G30" t="n">
-        <v>1.54</v>
+        <v>3.45</v>
       </c>
       <c r="H30" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="I30" t="n">
-        <v>8.4</v>
+        <v>320</v>
       </c>
       <c r="J30" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>4.6</v>
+        <v>110</v>
       </c>
       <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.4</v>
       </c>
-      <c r="M30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.84</v>
-      </c>
       <c r="X30" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="AQ30" t="n">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="AR30" t="n">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="AS30" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="AU30" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="AV30" t="n">
-        <v>27</v>
+        <v>1.04</v>
       </c>
       <c r="AW30" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="AX30" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="AZ30" t="n">
-        <v>24</v>
+        <v>1.04</v>
       </c>
       <c r="BA30" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BB30" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BC30" t="n">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BD30" t="n">
-        <v>29</v>
+        <v>1.04</v>
       </c>
       <c r="BE30" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BF30" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>12.5</v>
+        <v>1.55</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -6374,186 +6374,186 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G31" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I31" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K31" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="U31" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="V31" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X31" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y31" t="n">
         <v>21</v>
       </c>
       <c r="Z31" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA31" t="n">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="AB31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT31" t="n">
         <v>6.8</v>
       </c>
-      <c r="AC31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>6</v>
-      </c>
       <c r="AU31" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV31" t="n">
         <v>23</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AX31" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY31" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BB31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BF31" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,184 +6563,184 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G32" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I32" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="M32" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="O32" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="V32" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W32" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="X32" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z32" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA32" t="n">
-        <v>390</v>
+        <v>240</v>
       </c>
       <c r="AB32" t="n">
         <v>6.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD32" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AE32" t="n">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="AF32" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH32" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AI32" t="n">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="AJ32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK32" t="n">
         <v>19</v>
       </c>
-      <c r="AK32" t="n">
-        <v>27</v>
-      </c>
       <c r="AL32" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AM32" t="n">
-        <v>350</v>
+        <v>190</v>
       </c>
       <c r="AN32" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP32" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.9</v>
+        <v>42</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.1</v>
+        <v>48</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AU32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX32" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>7</v>
-      </c>
       <c r="AY32" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.1</v>
+        <v>42</v>
       </c>
       <c r="BB32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC32" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.8</v>
+        <v>42</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.1</v>
+        <v>48</v>
       </c>
       <c r="BF32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.1</v>
+        <v>46</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
@@ -6762,373 +6762,567 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Atl Tucuman</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="G33" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="H33" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="K33" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L33" t="n">
         <v>1.56</v>
       </c>
       <c r="M33" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="O33" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="P33" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="R33" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T33" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="U33" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="V33" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="W33" t="n">
-        <v>1.9</v>
+        <v>2.66</v>
       </c>
       <c r="X33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>370</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG33" t="n">
         <v>11</v>
       </c>
-      <c r="Y33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG33" t="n">
+      <c r="AH33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>340</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>400</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF33" t="n">
         <v>12</v>
       </c>
-      <c r="AH33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BG33" t="n">
-        <v>5.2</v>
+        <v>95</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-10 17:02:27</t>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Atl Tucuman</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-11 04:33:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Boyaca Patriotas</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Quindio</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T35" t="n">
         <v>2.26</v>
       </c>
-      <c r="G34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="U35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>6.8</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X34" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC34" t="n">
+      <c r="BA35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD35" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD34" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ34" t="n">
+      <c r="BE35" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-03-10 17:02:27</t>
+      <c r="BF35" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-11 04:33:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="G2" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.82</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>20</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
         <v>12.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
         <v>14</v>
       </c>
       <c r="AO2" t="n">
-        <v>280</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB2" t="n">
         <v>20</v>
       </c>
-      <c r="AS2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD2" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>75</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -951,79 +951,79 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="K3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P3" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R3" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="V3" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>16.5</v>
@@ -1032,10 +1032,10 @@
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AH3" t="n">
         <v>55</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>980</v>
@@ -1050,71 +1050,71 @@
         <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AP3" t="n">
         <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
         <v>12.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB3" t="n">
         <v>11</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BC3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.5</v>
+        <v>140</v>
       </c>
       <c r="BF3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="I4" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="T4" t="n">
         <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="W4" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
         <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
         <v>16</v>
       </c>
       <c r="AI4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AO4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AP4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10</v>
-      </c>
       <c r="AR4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT4" t="n">
         <v>19</v>
       </c>
-      <c r="AT4" t="n">
-        <v>17</v>
-      </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW4" t="n">
         <v>15.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AY4" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD4" t="n">
         <v>20</v>
       </c>
-      <c r="BD4" t="n">
-        <v>40</v>
-      </c>
       <c r="BE4" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BF4" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BG4" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H5" t="n">
         <v>3.35</v>
@@ -1351,55 +1351,55 @@
         <v>3.95</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="T5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="X5" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1408,19 +1408,19 @@
         <v>18</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AG5" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
         <v>60</v>
@@ -1429,13 +1429,13 @@
         <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1444,7 +1444,7 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
         <v>5.8</v>
@@ -1453,22 +1453,22 @@
         <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1477,32 +1477,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
         <v>10</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BF5" t="n">
         <v>5.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I6" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
         <v>4.3</v>
@@ -1572,19 +1572,19 @@
         <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U6" t="n">
         <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X6" t="n">
         <v>15</v>
@@ -1593,22 +1593,22 @@
         <v>19.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AF6" t="n">
         <v>10.5</v>
@@ -1638,7 +1638,7 @@
         <v>11.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>170</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>12.5</v>
@@ -1647,10 +1647,10 @@
         <v>16</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT6" t="n">
         <v>7</v>
@@ -1662,7 +1662,7 @@
         <v>19.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX6" t="n">
         <v>8.6</v>
@@ -1674,7 +1674,7 @@
         <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
         <v>14.5</v>
@@ -1686,17 +1686,17 @@
         <v>17.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="BF6" t="n">
         <v>9.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1727,76 +1727,76 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G7" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.3</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
         <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
         <v>20</v>
@@ -1805,92 +1805,92 @@
         <v>110</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="AJ7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AL7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
         <v>24</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
         <v>30</v>
       </c>
       <c r="BB7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
         <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="G8" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I8" t="n">
         <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
         <v>1.93</v>
       </c>
       <c r="U8" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X8" t="n">
         <v>19.5</v>
@@ -1993,7 +1993,7 @@
         <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
@@ -2002,10 +2002,10 @@
         <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
@@ -2029,40 +2029,40 @@
         <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
         <v>7</v>
       </c>
       <c r="AR8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW8" t="n">
         <v>7</v>
       </c>
-      <c r="AS8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AX8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
         <v>7.6</v>
@@ -2071,20 +2071,20 @@
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -2115,67 +2115,67 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="I9" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
         <v>36</v>
@@ -2187,16 +2187,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AF9" t="n">
         <v>120</v>
       </c>
       <c r="AG9" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AH9" t="n">
         <v>42</v>
@@ -2220,65 +2220,65 @@
         <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT9" t="n">
         <v>9</v>
       </c>
-      <c r="AT9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AU9" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
         <v>5.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
         <v>21</v>
       </c>
       <c r="AY9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>11.5</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>18</v>
-      </c>
       <c r="BA9" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF9" t="n">
         <v>40</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -2312,127 +2312,127 @@
         <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
         <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
         <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
         <v>16</v>
       </c>
       <c r="AE10" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
         <v>29</v>
       </c>
       <c r="AK10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM10" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR10" t="n">
         <v>12</v>
       </c>
-      <c r="AR10" t="n">
-        <v>22</v>
-      </c>
       <c r="AS10" t="n">
-        <v>8.4</v>
+        <v>55</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
         <v>13</v>
@@ -2450,29 +2450,29 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10" t="n">
         <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF10" t="n">
         <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G11" t="n">
         <v>1.8</v>
@@ -2518,7 +2518,7 @@
         <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.32</v>
@@ -2527,43 +2527,43 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
         <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U11" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y11" t="n">
         <v>500</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2572,40 +2572,40 @@
         <v>22</v>
       </c>
       <c r="AC11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AG11" t="n">
         <v>19</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ11" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
         <v>65</v>
       </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>330</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
@@ -2620,25 +2620,25 @@
         <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX11" t="n">
         <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AZ11" t="n">
         <v>9</v>
@@ -2656,17 +2656,17 @@
         <v>13</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF11" t="n">
         <v>5.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>4.5</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H12" t="n">
         <v>1.85</v>
       </c>
       <c r="I12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="J12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
@@ -2721,28 +2721,28 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O12" t="n">
         <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V12" t="n">
         <v>2.08</v>
@@ -2790,7 +2790,7 @@
         <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AL12" t="n">
         <v>75</v>
@@ -2829,7 +2829,7 @@
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY12" t="n">
         <v>16</v>
@@ -2838,29 +2838,29 @@
         <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>30</v>
+        <v>9.6</v>
       </c>
       <c r="BB12" t="n">
         <v>9.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
         <v>11</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -2897,16 +2897,16 @@
         <v>7.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I13" t="n">
         <v>1.54</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.38</v>
@@ -2921,25 +2921,25 @@
         <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V13" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="W13" t="n">
         <v>1.15</v>
@@ -2951,16 +2951,16 @@
         <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA13" t="n">
         <v>13.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
         <v>9.800000000000001</v>
@@ -2972,10 +2972,10 @@
         <v>60</v>
       </c>
       <c r="AG13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
         <v>36</v>
@@ -2990,10 +2990,10 @@
         <v>100</v>
       </c>
       <c r="AM13" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="n">
         <v>7.4</v>
@@ -3002,7 +3002,7 @@
         <v>16</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR13" t="n">
         <v>8.199999999999999</v>
@@ -3011,10 +3011,10 @@
         <v>13</v>
       </c>
       <c r="AT13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV13" t="n">
         <v>9.6</v>
@@ -3050,11 +3050,11 @@
         <v>130</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>1.99</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
         <v>3.4</v>
@@ -3109,7 +3109,7 @@
         <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O14" t="n">
         <v>1.53</v>
@@ -3214,10 +3214,10 @@
         <v>9.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>18.5</v>
@@ -3226,13 +3226,13 @@
         <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
         <v>3.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="K15" t="n">
         <v>2.78</v>
@@ -3303,16 +3303,16 @@
         <v>1.19</v>
       </c>
       <c r="N15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O15" t="n">
         <v>1.74</v>
       </c>
       <c r="P15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
         <v>1.13</v>
@@ -3321,7 +3321,7 @@
         <v>7.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
         <v>1.62</v>
@@ -3330,7 +3330,7 @@
         <v>1.45</v>
       </c>
       <c r="W15" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
         <v>6.4</v>
@@ -3357,10 +3357,10 @@
         <v>500</v>
       </c>
       <c r="AF15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH15" t="n">
         <v>65</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR15" t="n">
         <v>17</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT15" t="n">
         <v>6.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>36</v>
+        <v>9.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BE15" t="n">
         <v>10.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -3479,19 +3479,19 @@
         <v>2.14</v>
       </c>
       <c r="H16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I16" t="n">
         <v>3.7</v>
       </c>
-      <c r="I16" t="n">
-        <v>3.75</v>
-      </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -3503,10 +3503,10 @@
         <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
         <v>1.57</v>
@@ -3515,22 +3515,22 @@
         <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U16" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
         <v>1.87</v>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z16" t="n">
         <v>28</v>
@@ -3539,10 +3539,10 @@
         <v>65</v>
       </c>
       <c r="AB16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>15</v>
@@ -3557,7 +3557,7 @@
         <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI16" t="n">
         <v>40</v>
@@ -3566,22 +3566,22 @@
         <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO16" t="n">
         <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
         <v>17</v>
@@ -3590,31 +3590,31 @@
         <v>26</v>
       </c>
       <c r="AS16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX16" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>14</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
         <v>25</v>
@@ -3623,20 +3623,20 @@
         <v>18.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE16" t="n">
         <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G17" t="n">
         <v>2.56</v>
       </c>
-      <c r="G17" t="n">
-        <v>2.58</v>
-      </c>
       <c r="H17" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="J17" t="n">
         <v>3.75</v>
@@ -3694,16 +3694,16 @@
         <v>5.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
         <v>2.76</v>
@@ -3712,13 +3712,13 @@
         <v>1.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X17" t="n">
         <v>19.5</v>
@@ -3736,7 +3736,7 @@
         <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
         <v>13</v>
@@ -3745,13 +3745,13 @@
         <v>27</v>
       </c>
       <c r="AF17" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI17" t="n">
         <v>34</v>
@@ -3772,10 +3772,10 @@
         <v>15.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3784,7 +3784,7 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT17" t="n">
         <v>13.5</v>
@@ -3799,38 +3799,38 @@
         <v>26</v>
       </c>
       <c r="AX17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY17" t="n">
         <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC17" t="n">
         <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -3861,85 +3861,85 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="G18" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
         <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M18" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P18" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W18" t="n">
         <v>1.94</v>
       </c>
       <c r="X18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
         <v>34</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
@@ -3948,37 +3948,37 @@
         <v>27</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK18" t="n">
         <v>26</v>
       </c>
-      <c r="AK18" t="n">
-        <v>65</v>
-      </c>
       <c r="AL18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM18" t="n">
-        <v>180</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS18" t="n">
         <v>11</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>14</v>
       </c>
       <c r="AT18" t="n">
         <v>6.6</v>
@@ -3987,13 +3987,13 @@
         <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
@@ -4002,29 +4002,29 @@
         <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC18" t="n">
         <v>22</v>
       </c>
       <c r="BD18" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BE18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BF18" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -4067,10 +4067,10 @@
         <v>2.08</v>
       </c>
       <c r="J19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.95</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>1.33</v>
@@ -4079,58 +4079,58 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S19" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T19" t="n">
         <v>1.63</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V19" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W19" t="n">
         <v>1.35</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
         <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB19" t="n">
         <v>18</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
         <v>10.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF19" t="n">
         <v>29</v>
@@ -4148,28 +4148,28 @@
         <v>70</v>
       </c>
       <c r="AK19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL19" t="n">
         <v>40</v>
       </c>
       <c r="AM19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO19" t="n">
         <v>11</v>
       </c>
       <c r="AP19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ19" t="n">
         <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
         <v>23</v>
@@ -4178,7 +4178,7 @@
         <v>17</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
@@ -4187,10 +4187,10 @@
         <v>18.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
         <v>14.5</v>
@@ -4199,7 +4199,7 @@
         <v>25</v>
       </c>
       <c r="BB19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BC19" t="n">
         <v>34</v>
@@ -4208,17 +4208,17 @@
         <v>38</v>
       </c>
       <c r="BE19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.32</v>
       </c>
       <c r="G20" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H20" t="n">
         <v>3.9</v>
@@ -4282,13 +4282,13 @@
         <v>1.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R20" t="n">
         <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T20" t="n">
         <v>2.14</v>
@@ -4300,7 +4300,7 @@
         <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X20" t="n">
         <v>8.6</v>
@@ -4324,16 +4324,16 @@
         <v>18</v>
       </c>
       <c r="AE20" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
         <v>460</v>
@@ -4354,19 +4354,19 @@
         <v>36</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ20" t="n">
         <v>9.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AT20" t="n">
         <v>6.6</v>
@@ -4378,7 +4378,7 @@
         <v>15.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AX20" t="n">
         <v>11.5</v>
@@ -4390,29 +4390,29 @@
         <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BB20" t="n">
         <v>28</v>
       </c>
       <c r="BC20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD20" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BE20" t="n">
         <v>70</v>
       </c>
       <c r="BF20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG20" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G21" t="n">
         <v>2.18</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
@@ -4470,7 +4470,7 @@
         <v>2.48</v>
       </c>
       <c r="O21" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P21" t="n">
         <v>1.46</v>
@@ -4482,31 +4482,31 @@
         <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="T21" t="n">
         <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y21" t="n">
         <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB21" t="n">
         <v>6.2</v>
@@ -4515,25 +4515,25 @@
         <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH21" t="n">
         <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK21" t="n">
         <v>32</v>
@@ -4548,7 +4548,7 @@
         <v>32</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP21" t="n">
         <v>6.8</v>
@@ -4557,56 +4557,56 @@
         <v>10.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS21" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
         <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
       </c>
       <c r="AY21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA21" t="n">
         <v>42</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD21" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BE21" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="BF21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BG21" t="n">
         <v>44</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="G22" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="H22" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="I22" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="J22" t="n">
         <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
         <v>1.55</v>
@@ -4661,16 +4661,16 @@
         <v>1.11</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O22" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P22" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R22" t="n">
         <v>1.21</v>
@@ -4685,16 +4685,16 @@
         <v>1.76</v>
       </c>
       <c r="V22" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="n">
         <v>22</v>
@@ -4703,10 +4703,10 @@
         <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
         <v>34</v>
@@ -4721,7 +4721,7 @@
         <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
@@ -4742,65 +4742,65 @@
         <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP22" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ22" t="n">
         <v>6</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AT22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU22" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU22" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AV22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AY22" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BA22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB22" t="n">
         <v>8.6</v>
       </c>
-      <c r="BB22" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BC22" t="n">
-        <v>5.2</v>
+        <v>8.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.98</v>
+        <v>8.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -4831,58 +4831,58 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M23" t="n">
         <v>1.05</v>
       </c>
-      <c r="G23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N23" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.21</v>
+        <v>1.78</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>1.21</v>
+        <v>2.82</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4894,16 +4894,16 @@
         <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB23" t="n">
         <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4915,7 +4915,7 @@
         <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -4936,65 +4936,65 @@
         <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H24" t="n">
         <v>3.45</v>
@@ -5037,16 +5037,16 @@
         <v>3.5</v>
       </c>
       <c r="J24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.6</v>
       </c>
-      <c r="K24" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L24" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
         <v>3.8</v>
@@ -5055,28 +5055,28 @@
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
         <v>3.65</v>
       </c>
       <c r="T24" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
         <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X24" t="n">
         <v>13.5</v>
@@ -5085,7 +5085,7 @@
         <v>13</v>
       </c>
       <c r="Z24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA24" t="n">
         <v>65</v>
@@ -5097,7 +5097,7 @@
         <v>7.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
         <v>40</v>
@@ -5109,31 +5109,31 @@
         <v>11</v>
       </c>
       <c r="AH24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="AJ24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="n">
         <v>95</v>
       </c>
       <c r="AN24" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AP24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
         <v>11.5</v>
@@ -5145,37 +5145,37 @@
         <v>50</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
       </c>
       <c r="AY24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA24" t="n">
         <v>44</v>
       </c>
       <c r="BB24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC24" t="n">
         <v>22</v>
       </c>
       <c r="BD24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE24" t="n">
         <v>75</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5219,64 +5219,64 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="G25" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="H25" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P25" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="V25" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="W25" t="n">
-        <v>2.14</v>
+        <v>2.52</v>
       </c>
       <c r="X25" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y25" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z25" t="n">
         <v>250</v>
@@ -5285,104 +5285,104 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AG25" t="n">
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK25" t="n">
         <v>21</v>
       </c>
-      <c r="AK25" t="n">
-        <v>44</v>
-      </c>
       <c r="AL25" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>48</v>
+        <v>13.5</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="AS25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV25" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AW25" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="BC25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BE25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G26" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I26" t="n">
         <v>7</v>
       </c>
-      <c r="I26" t="n">
-        <v>7.4</v>
-      </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.68</v>
@@ -5452,28 +5452,28 @@
         <v>1.14</v>
       </c>
       <c r="S26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V26" t="n">
         <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="X26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="AA26" t="n">
         <v>700</v>
@@ -5482,16 +5482,16 @@
         <v>5.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE26" t="n">
         <v>700</v>
       </c>
       <c r="AF26" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
         <v>12.5</v>
@@ -5503,10 +5503,10 @@
         <v>700</v>
       </c>
       <c r="AJ26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK26" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL26" t="n">
         <v>210</v>
@@ -5515,7 +5515,7 @@
         <v>700</v>
       </c>
       <c r="AN26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -5527,7 +5527,7 @@
         <v>12.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AS26" t="n">
         <v>110</v>
@@ -5539,13 +5539,13 @@
         <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW26" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY26" t="n">
         <v>11</v>
@@ -5554,16 +5554,16 @@
         <v>34</v>
       </c>
       <c r="BA26" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="BB26" t="n">
         <v>16.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD26" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="BE26" t="n">
         <v>110</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5610,58 +5610,58 @@
         <v>2.68</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H27" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I27" t="n">
         <v>3.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M27" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N27" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P27" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R27" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S27" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V27" t="n">
         <v>1.44</v>
       </c>
       <c r="W27" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y27" t="n">
         <v>9.199999999999999</v>
@@ -5670,10 +5670,10 @@
         <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC27" t="n">
         <v>7.4</v>
@@ -5682,7 +5682,7 @@
         <v>15</v>
       </c>
       <c r="AE27" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF27" t="n">
         <v>18</v>
@@ -5691,10 +5691,10 @@
         <v>14</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
         <v>55</v>
@@ -5703,19 +5703,19 @@
         <v>120</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ27" t="n">
         <v>7.6</v>
@@ -5724,7 +5724,7 @@
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5736,7 +5736,7 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX27" t="n">
         <v>14.5</v>
@@ -5754,23 +5754,23 @@
         <v>8.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF27" t="n">
         <v>8.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>1.78</v>
       </c>
       <c r="G28" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H28" t="n">
         <v>5.5</v>
@@ -5813,7 +5813,7 @@
         <v>5.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K28" t="n">
         <v>3.8</v>
@@ -5828,10 +5828,10 @@
         <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
         <v>2.04</v>
@@ -5846,7 +5846,7 @@
         <v>1.95</v>
       </c>
       <c r="U28" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V28" t="n">
         <v>1.21</v>
@@ -5855,16 +5855,16 @@
         <v>2.24</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y28" t="n">
         <v>18</v>
       </c>
       <c r="Z28" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA28" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AB28" t="n">
         <v>8.199999999999999</v>
@@ -5873,13 +5873,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG28" t="n">
         <v>10</v>
@@ -5888,34 +5888,34 @@
         <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL28" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN28" t="n">
         <v>12.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP28" t="n">
         <v>12</v>
       </c>
       <c r="AQ28" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS28" t="n">
         <v>42</v>
@@ -5924,13 +5924,13 @@
         <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV28" t="n">
         <v>19.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX28" t="n">
         <v>9.199999999999999</v>
@@ -5942,29 +5942,29 @@
         <v>18.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BB28" t="n">
         <v>16.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BE28" t="n">
         <v>65</v>
       </c>
       <c r="BF28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG28" t="n">
         <v>38</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I29" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>3.85</v>
@@ -6013,7 +6013,7 @@
         <v>4.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6022,64 +6022,64 @@
         <v>3.35</v>
       </c>
       <c r="O29" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R29" t="n">
         <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U29" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V29" t="n">
         <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y29" t="n">
         <v>21</v>
       </c>
       <c r="Z29" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC29" t="n">
         <v>9.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG29" t="n">
         <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
@@ -6103,7 +6103,7 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>17.5</v>
@@ -6148,7 +6148,7 @@
         <v>38</v>
       </c>
       <c r="BE29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF29" t="n">
         <v>9.4</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6189,170 +6189,170 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="G30" t="n">
-        <v>3.45</v>
+        <v>1.51</v>
       </c>
       <c r="H30" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="I30" t="n">
-        <v>320</v>
+        <v>11</v>
       </c>
       <c r="J30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N30" t="n">
         <v>3.55</v>
       </c>
-      <c r="K30" t="n">
+      <c r="O30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z30" t="n">
         <v>110</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE30" t="n">
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6389,10 +6389,10 @@
         <v>1.62</v>
       </c>
       <c r="H31" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I31" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
         <v>4.2</v>
@@ -6407,28 +6407,28 @@
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P31" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R31" t="n">
         <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T31" t="n">
         <v>2.06</v>
       </c>
       <c r="U31" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V31" t="n">
         <v>1.16</v>
@@ -6443,25 +6443,25 @@
         <v>21</v>
       </c>
       <c r="Z31" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA31" t="n">
         <v>230</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC31" t="n">
         <v>9.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE31" t="n">
         <v>110</v>
       </c>
       <c r="AF31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG31" t="n">
         <v>9.6</v>
@@ -6473,34 +6473,34 @@
         <v>110</v>
       </c>
       <c r="AJ31" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
         <v>17.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM31" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN31" t="n">
         <v>10.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP31" t="n">
         <v>13</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT31" t="n">
         <v>6.8</v>
@@ -6515,19 +6515,19 @@
         <v>19</v>
       </c>
       <c r="AX31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY31" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
         <v>19</v>
       </c>
       <c r="BB31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC31" t="n">
         <v>16</v>
@@ -6539,14 +6539,14 @@
         <v>20</v>
       </c>
       <c r="BF31" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G32" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H32" t="n">
         <v>6.8</v>
@@ -6595,100 +6595,100 @@
         <v>4.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M32" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O32" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="P32" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U32" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V32" t="n">
         <v>1.15</v>
       </c>
       <c r="W32" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z32" t="n">
         <v>60</v>
       </c>
       <c r="AA32" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AB32" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE32" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI32" t="n">
         <v>130</v>
       </c>
-      <c r="AF32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>140</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL32" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM32" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AN32" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AP32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR32" t="n">
         <v>42</v>
@@ -6697,13 +6697,13 @@
         <v>48</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU32" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW32" t="n">
         <v>40</v>
@@ -6712,10 +6712,10 @@
         <v>7.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA32" t="n">
         <v>42</v>
@@ -6724,23 +6724,23 @@
         <v>14</v>
       </c>
       <c r="BC32" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE32" t="n">
         <v>48</v>
       </c>
       <c r="BF32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG32" t="n">
         <v>46</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6777,10 +6777,10 @@
         <v>1.6</v>
       </c>
       <c r="H33" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J33" t="n">
         <v>3.95</v>
@@ -6792,7 +6792,7 @@
         <v>1.56</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N33" t="n">
         <v>2.92</v>
@@ -6804,7 +6804,7 @@
         <v>1.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R33" t="n">
         <v>1.22</v>
@@ -6813,10 +6813,10 @@
         <v>5.1</v>
       </c>
       <c r="T33" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V33" t="n">
         <v>1.13</v>
@@ -6828,16 +6828,16 @@
         <v>10</v>
       </c>
       <c r="Y33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z33" t="n">
         <v>75</v>
       </c>
       <c r="AA33" t="n">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AC33" t="n">
         <v>9.4</v>
@@ -6849,7 +6849,7 @@
         <v>200</v>
       </c>
       <c r="AF33" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG33" t="n">
         <v>11</v>
@@ -6870,19 +6870,19 @@
         <v>65</v>
       </c>
       <c r="AM33" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AN33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO33" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AP33" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR33" t="n">
         <v>55</v>
@@ -6891,10 +6891,10 @@
         <v>110</v>
       </c>
       <c r="AT33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV33" t="n">
         <v>30</v>
@@ -6924,17 +6924,17 @@
         <v>50</v>
       </c>
       <c r="BE33" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BF33" t="n">
         <v>12</v>
       </c>
       <c r="BG33" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
         <v>2.04</v>
       </c>
       <c r="H34" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I34" t="n">
         <v>5.1</v>
@@ -6989,28 +6989,28 @@
         <v>1.13</v>
       </c>
       <c r="N34" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O34" t="n">
         <v>1.55</v>
       </c>
       <c r="P34" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q34" t="n">
         <v>2.68</v>
       </c>
       <c r="R34" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
         <v>5.6</v>
       </c>
       <c r="T34" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U34" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V34" t="n">
         <v>1.24</v>
@@ -7019,10 +7019,10 @@
         <v>1.96</v>
       </c>
       <c r="X34" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z34" t="n">
         <v>1000</v>
@@ -7037,7 +7037,7 @@
         <v>8</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE34" t="n">
         <v>1000</v>
@@ -7052,7 +7052,7 @@
         <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ34" t="n">
         <v>1000</v>
@@ -7067,46 +7067,46 @@
         <v>260</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ34" t="n">
         <v>11</v>
       </c>
       <c r="AR34" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AX34" t="n">
         <v>9</v>
       </c>
       <c r="AY34" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BB34" t="n">
         <v>20</v>
@@ -7115,20 +7115,20 @@
         <v>23</v>
       </c>
       <c r="BD34" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.4</v>
+        <v>48</v>
       </c>
       <c r="BF34" t="n">
         <v>20</v>
       </c>
       <c r="BG34" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>
@@ -7162,61 +7162,61 @@
         <v>2.06</v>
       </c>
       <c r="G35" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H35" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
         <v>3.25</v>
       </c>
       <c r="L35" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M35" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N35" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="P35" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S35" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="U35" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W35" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="X35" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y35" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z35" t="n">
         <v>38</v>
@@ -7225,7 +7225,7 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC35" t="n">
         <v>7.6</v>
@@ -7252,10 +7252,10 @@
         <v>30</v>
       </c>
       <c r="AK35" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
@@ -7276,19 +7276,19 @@
         <v>24</v>
       </c>
       <c r="AS35" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AU35" t="n">
         <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX35" t="n">
         <v>9.6</v>
@@ -7297,32 +7297,32 @@
         <v>10</v>
       </c>
       <c r="AZ35" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB35" t="n">
         <v>6.8</v>
       </c>
-      <c r="BA35" t="n">
+      <c r="BC35" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD35" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE35" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF35" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 04:33:47</t>
+          <t>2026-03-11 06:41:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>07:00:07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.95</v>
+        <v>4.9</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>34</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>1.22</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>1.31</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>3.95</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>34</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.92</v>
+        <v>110</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>110</v>
       </c>
       <c r="T2" t="n">
-        <v>1.82</v>
+        <v>17.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.98</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>1.35</v>
       </c>
       <c r="Y2" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
         <v>17</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS2" t="n">
         <v>32</v>
       </c>
-      <c r="AA2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AT2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>120</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BG2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>75</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>40</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:29:38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Istanbulspor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed Sportif Faaliyetler</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>600</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K3" t="n">
+        <v>170</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V3" t="n">
+        <v>50</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT3" t="n">
         <v>20</v>
       </c>
-      <c r="G3" t="n">
-        <v>25</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N3" t="n">
-        <v>7</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>980</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AU3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AV3" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="BE3" t="n">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:30:16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Istanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Amed Sportif Faaliyetler</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="I4" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>1.64</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>2.44</v>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>1.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.66</v>
+        <v>7.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.03</v>
       </c>
       <c r="S4" t="n">
-        <v>2.64</v>
+        <v>28</v>
       </c>
       <c r="T4" t="n">
-        <v>1.66</v>
+        <v>6.4</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV4" t="n">
         <v>22</v>
       </c>
-      <c r="Y4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AW4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>95</v>
+      </c>
+      <c r="BA4" t="n">
         <v>16</v>
       </c>
-      <c r="AI4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW4" t="n">
+      <c r="BB4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>270</v>
+      </c>
+      <c r="BF4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AX4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>20</v>
-      </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:32:10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adana 1954 FK</t>
+          <t>Erzincanspor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ankaraspor</t>
+          <t>Beykoz Anadolu Spor</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.08</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.26</v>
+        <v>1.07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>750</v>
       </c>
       <c r="L5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>2.54</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8</v>
+        <v>17.5</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD5" t="n">
         <v>22</v>
       </c>
-      <c r="AH5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>290</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BE5" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.7</v>
+        <v>1.82</v>
       </c>
       <c r="BG5" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>07:30:00</t>
+          <t>07:33:04</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erzincanspor</t>
+          <t>Adana 1954 FK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Beykoz Anadolu Spor</t>
+          <t>Ankaraspor</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="G6" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="K6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W6" t="n">
         <v>4.3</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.3</v>
-      </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
         <v>900</v>
       </c>
-      <c r="AB6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>960</v>
       </c>
       <c r="AI6" t="n">
-        <v>260</v>
+        <v>990</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>990</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>12.5</v>
+        <v>1.55</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>1.55</v>
       </c>
       <c r="AV6" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.5</v>
+        <v>1.55</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>110</v>
+        <v>1.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="X7" t="n">
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF7" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>190</v>
       </c>
       <c r="AJ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>21</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AR7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>20</v>
       </c>
-      <c r="AL7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA7" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.800000000000001</v>
+        <v>80</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
         <v>1.89</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="Z8" t="n">
         <v>980</v>
@@ -1987,25 +1987,25 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AE8" t="n">
         <v>700</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
         <v>18</v>
       </c>
       <c r="AH8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
         <v>700</v>
@@ -2017,74 +2017,74 @@
         <v>65</v>
       </c>
       <c r="AL8" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
         <v>700</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="AR8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU8" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AV8" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC8" t="n">
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>85</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="I9" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.45</v>
@@ -2139,146 +2139,146 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
         <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="W9" t="n">
         <v>1.2</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
         <v>8.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI9" t="n">
         <v>38</v>
       </c>
-      <c r="AF9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
         <v>160</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AL9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN9" t="n">
         <v>700</v>
       </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO9" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT9" t="n">
         <v>16</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV9" t="n">
         <v>9</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5.9</v>
       </c>
       <c r="AW9" t="n">
         <v>13</v>
       </c>
       <c r="AX9" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AY9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF9" t="n">
         <v>13</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>40</v>
-      </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
         <v>3.8</v>
@@ -2333,13 +2333,13 @@
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
         <v>2</v>
@@ -2351,58 +2351,58 @@
         <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="X10" t="n">
         <v>14</v>
       </c>
       <c r="Y10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>980</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF10" t="n">
         <v>14</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>14.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
         <v>40</v>
@@ -2411,22 +2411,22 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS10" t="n">
         <v>11</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>55</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
@@ -2441,16 +2441,16 @@
         <v>34</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB10" t="n">
         <v>22</v>
@@ -2462,17 +2462,17 @@
         <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.4</v>
+        <v>70</v>
       </c>
       <c r="BF10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.75</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H11" t="n">
         <v>4.6</v>
@@ -2515,10 +2515,10 @@
         <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L11" t="n">
         <v>1.32</v>
@@ -2533,25 +2533,25 @@
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
         <v>2.26</v>
@@ -2560,10 +2560,10 @@
         <v>55</v>
       </c>
       <c r="Y11" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2602,49 +2602,49 @@
         <v>65</v>
       </c>
       <c r="AM11" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.6</v>
+        <v>2.94</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>9</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB11" t="n">
         <v>10.5</v>
@@ -2656,17 +2656,17 @@
         <v>13</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="G12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I12" t="n">
         <v>1.85</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.92</v>
       </c>
       <c r="J12" t="n">
         <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.42</v>
@@ -2721,13 +2721,13 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
         <v>1.98</v>
@@ -2736,19 +2736,19 @@
         <v>1.34</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="U12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="W12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
         <v>15</v>
@@ -2757,13 +2757,13 @@
         <v>8.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC12" t="n">
         <v>9.199999999999999</v>
@@ -2775,10 +2775,10 @@
         <v>21</v>
       </c>
       <c r="AF12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AG12" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
         <v>22</v>
@@ -2790,19 +2790,19 @@
         <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP12" t="n">
         <v>12.5</v>
@@ -2817,7 +2817,7 @@
         <v>17</v>
       </c>
       <c r="AT12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU12" t="n">
         <v>7.6</v>
@@ -2829,16 +2829,16 @@
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="AY12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ12" t="n">
         <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BB12" t="n">
         <v>9.4</v>
@@ -2847,20 +2847,20 @@
         <v>9</v>
       </c>
       <c r="BD12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BE12" t="n">
         <v>9.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12" t="n">
         <v>11</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -2897,19 +2897,19 @@
         <v>7.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I13" t="n">
         <v>1.54</v>
       </c>
       <c r="J13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.7</v>
       </c>
-      <c r="K13" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -2921,7 +2921,7 @@
         <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
         <v>1.86</v>
@@ -2930,16 +2930,16 @@
         <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V13" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="W13" t="n">
         <v>1.15</v>
@@ -2951,7 +2951,7 @@
         <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AA13" t="n">
         <v>13.5</v>
@@ -2960,7 +2960,7 @@
         <v>22</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
         <v>9.800000000000001</v>
@@ -2981,7 +2981,7 @@
         <v>36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AK13" t="n">
         <v>110</v>
@@ -2993,10 +2993,10 @@
         <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AO13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AP13" t="n">
         <v>16</v>
@@ -3038,7 +3038,7 @@
         <v>210</v>
       </c>
       <c r="BC13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BD13" t="n">
         <v>90</v>
@@ -3047,14 +3047,14 @@
         <v>110</v>
       </c>
       <c r="BF13" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="G14" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="H14" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="I14" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="J14" t="n">
         <v>3.25</v>
@@ -3112,31 +3112,31 @@
         <v>2.76</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P14" t="n">
         <v>1.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R14" t="n">
         <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="W14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
         <v>9.199999999999999</v>
@@ -3145,16 +3145,16 @@
         <v>6.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AB14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
         <v>11.5</v>
@@ -3163,13 +3163,13 @@
         <v>28</v>
       </c>
       <c r="AF14" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AG14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>150</v>
@@ -3178,10 +3178,10 @@
         <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
@@ -3190,10 +3190,10 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ14" t="n">
         <v>5.8</v>
@@ -3202,53 +3202,53 @@
         <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU14" t="n">
         <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AZ14" t="n">
         <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC14" t="n">
         <v>10.5</v>
       </c>
-      <c r="BC14" t="n">
-        <v>12</v>
-      </c>
       <c r="BD14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -3282,22 +3282,22 @@
         <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H15" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I15" t="n">
         <v>3.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="K15" t="n">
         <v>2.78</v>
       </c>
       <c r="L15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="M15" t="n">
         <v>1.19</v>
@@ -3309,67 +3309,67 @@
         <v>1.74</v>
       </c>
       <c r="P15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
         <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>1.45</v>
       </c>
       <c r="W15" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X15" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.800000000000001</v>
+        <v>980</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AA15" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.6</v>
+        <v>980</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="AD15" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="AE15" t="n">
         <v>500</v>
       </c>
       <c r="AF15" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="AG15" t="n">
-        <v>15.5</v>
+        <v>980</v>
       </c>
       <c r="AH15" t="n">
-        <v>65</v>
+        <v>980</v>
       </c>
       <c r="AI15" t="n">
         <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>210</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
         <v>980</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.4</v>
+        <v>3.05</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="AR15" t="n">
-        <v>17</v>
+        <v>2.24</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.800000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.6</v>
+        <v>2.26</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AY15" t="n">
-        <v>12.5</v>
+        <v>3.9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>2.42</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>2.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>15</v>
+        <v>2.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>10.5</v>
+        <v>2.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>10</v>
+        <v>2.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>10</v>
+        <v>2.08</v>
       </c>
       <c r="BG15" t="n">
-        <v>10</v>
+        <v>2.08</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="H16" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K16" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.34</v>
@@ -3497,43 +3497,43 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
         <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q16" t="n">
         <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="X16" t="n">
         <v>20</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
         <v>65</v>
@@ -3542,31 +3542,31 @@
         <v>13</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
         <v>36</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
         <v>10.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3578,31 +3578,31 @@
         <v>11.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16" t="n">
         <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX16" t="n">
         <v>14.5</v>
@@ -3611,16 +3611,16 @@
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD16" t="n">
         <v>26</v>
@@ -3629,14 +3629,14 @@
         <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="H17" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="I17" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="J17" t="n">
         <v>3.75</v>
@@ -3685,7 +3685,7 @@
         <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
@@ -3697,13 +3697,13 @@
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S17" t="n">
         <v>2.76</v>
@@ -3715,10 +3715,10 @@
         <v>2.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X17" t="n">
         <v>19.5</v>
@@ -3727,10 +3727,10 @@
         <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AB17" t="n">
         <v>14</v>
@@ -3742,10 +3742,10 @@
         <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
@@ -3757,7 +3757,7 @@
         <v>34</v>
       </c>
       <c r="AJ17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="n">
         <v>23</v>
@@ -3769,37 +3769,37 @@
         <v>55</v>
       </c>
       <c r="AN17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AT17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY17" t="n">
         <v>11</v>
@@ -3814,23 +3814,23 @@
         <v>32</v>
       </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G18" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
         <v>3.4</v>
@@ -3879,22 +3879,22 @@
         <v>3.55</v>
       </c>
       <c r="L18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P18" t="n">
         <v>1.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
@@ -3909,61 +3909,61 @@
         <v>1.89</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X18" t="n">
         <v>10.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>200</v>
       </c>
       <c r="AF18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI18" t="n">
         <v>90</v>
       </c>
       <c r="AJ18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
         <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AO18" t="n">
         <v>110</v>
@@ -3975,37 +3975,37 @@
         <v>11.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS18" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU18" t="n">
         <v>7.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BC18" t="n">
         <v>22</v>
@@ -4014,17 +4014,17 @@
         <v>38</v>
       </c>
       <c r="BE18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>34</v>
+        <v>14.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4061,25 +4061,25 @@
         <v>3.85</v>
       </c>
       <c r="H19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.9</v>
       </c>
-      <c r="K19" t="n">
-        <v>3.95</v>
-      </c>
       <c r="L19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
@@ -4088,7 +4088,7 @@
         <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R19" t="n">
         <v>1.56</v>
@@ -4097,28 +4097,28 @@
         <v>2.74</v>
       </c>
       <c r="T19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="W19" t="n">
         <v>1.35</v>
       </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z19" t="n">
         <v>14.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB19" t="n">
         <v>18</v>
@@ -4130,7 +4130,7 @@
         <v>10.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
         <v>29</v>
@@ -4139,7 +4139,7 @@
         <v>15.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
@@ -4157,10 +4157,10 @@
         <v>55</v>
       </c>
       <c r="AN19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AP19" t="n">
         <v>19</v>
@@ -4172,7 +4172,7 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT19" t="n">
         <v>17</v>
@@ -4193,7 +4193,7 @@
         <v>15</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>25</v>
@@ -4205,7 +4205,7 @@
         <v>34</v>
       </c>
       <c r="BD19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE19" t="n">
         <v>50</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4255,25 +4255,25 @@
         <v>2.38</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I20" t="n">
         <v>4.1</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
         <v>3.15</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
         <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O20" t="n">
         <v>1.55</v>
@@ -4390,16 +4390,16 @@
         <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB20" t="n">
         <v>28</v>
       </c>
       <c r="BC20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE20" t="n">
         <v>70</v>
@@ -4408,11 +4408,11 @@
         <v>23</v>
       </c>
       <c r="BG20" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G21" t="n">
         <v>2.14</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.18</v>
-      </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
@@ -4473,13 +4473,13 @@
         <v>1.64</v>
       </c>
       <c r="P21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q21" t="n">
         <v>3.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
         <v>6.6</v>
@@ -4491,10 +4491,10 @@
         <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W21" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X21" t="n">
         <v>7.2</v>
@@ -4512,13 +4512,13 @@
         <v>6.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD21" t="n">
         <v>22</v>
       </c>
       <c r="AE21" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="AF21" t="n">
         <v>10.5</v>
@@ -4539,16 +4539,16 @@
         <v>32</v>
       </c>
       <c r="AL21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="n">
-        <v>500</v>
+        <v>280</v>
       </c>
       <c r="AN21" t="n">
         <v>32</v>
       </c>
       <c r="AO21" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP21" t="n">
         <v>6.8</v>
@@ -4560,7 +4560,7 @@
         <v>30</v>
       </c>
       <c r="AS21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT21" t="n">
         <v>5.9</v>
@@ -4572,41 +4572,41 @@
         <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AX21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
         <v>29</v>
       </c>
       <c r="BD21" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BE21" t="n">
         <v>70</v>
       </c>
       <c r="BF21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BG21" t="n">
         <v>44</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4643,34 +4643,34 @@
         <v>5.9</v>
       </c>
       <c r="H22" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I22" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
         <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M22" t="n">
         <v>1.11</v>
       </c>
       <c r="N22" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O22" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P22" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
         <v>1.21</v>
@@ -4679,19 +4679,19 @@
         <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
         <v>1.76</v>
       </c>
       <c r="V22" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W22" t="n">
         <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y22" t="n">
         <v>7</v>
@@ -4706,7 +4706,7 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
         <v>34</v>
@@ -4745,10 +4745,10 @@
         <v>55</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AR22" t="n">
         <v>5.8</v>
@@ -4760,10 +4760,10 @@
         <v>6.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
         <v>14.5</v>
@@ -4778,29 +4778,29 @@
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4831,67 +4831,67 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.96</v>
+        <v>3.55</v>
       </c>
       <c r="G23" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="T23" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="W23" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA23" t="n">
         <v>900</v>
@@ -4903,10 +4903,10 @@
         <v>42</v>
       </c>
       <c r="AD23" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>55</v>
       </c>
       <c r="AP23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>5.3</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>7</v>
-      </c>
       <c r="AR23" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT23" t="n">
         <v>7.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF23" t="n">
         <v>3.9</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I24" t="n">
         <v>3.45</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.5</v>
       </c>
       <c r="J24" t="n">
         <v>3.5</v>
@@ -5049,16 +5049,16 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
         <v>1.35</v>
@@ -5067,7 +5067,7 @@
         <v>3.65</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U24" t="n">
         <v>2.12</v>
@@ -5076,31 +5076,31 @@
         <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X24" t="n">
         <v>13.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z24" t="n">
         <v>23</v>
       </c>
       <c r="AA24" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC24" t="n">
         <v>7.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AF24" t="n">
         <v>14.5</v>
@@ -5112,13 +5112,13 @@
         <v>17.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="AJ24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL24" t="n">
         <v>40</v>
@@ -5127,10 +5127,10 @@
         <v>95</v>
       </c>
       <c r="AN24" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AP24" t="n">
         <v>12</v>
@@ -5145,25 +5145,25 @@
         <v>50</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
       </c>
       <c r="AV24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX24" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>13</v>
       </c>
       <c r="AY24" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA24" t="n">
         <v>44</v>
@@ -5178,7 +5178,7 @@
         <v>36</v>
       </c>
       <c r="BE24" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF24" t="n">
         <v>17.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="G25" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="I25" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P25" t="n">
         <v>1.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W25" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="X25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Z25" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX25" t="n">
         <v>6.4</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>7.2</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BB25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC25" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BE25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF25" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G26" t="n">
         <v>1.76</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.79</v>
-      </c>
       <c r="H26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J26" t="n">
         <v>3.4</v>
@@ -5437,16 +5437,16 @@
         <v>1.15</v>
       </c>
       <c r="N26" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O26" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="P26" t="n">
         <v>1.43</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R26" t="n">
         <v>1.14</v>
@@ -5455,7 +5455,7 @@
         <v>7.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
         <v>1.51</v>
@@ -5464,7 +5464,7 @@
         <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="X26" t="n">
         <v>7.4</v>
@@ -5491,22 +5491,22 @@
         <v>700</v>
       </c>
       <c r="AF26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="n">
         <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AI26" t="n">
         <v>700</v>
       </c>
       <c r="AJ26" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL26" t="n">
         <v>210</v>
@@ -5515,34 +5515,34 @@
         <v>700</v>
       </c>
       <c r="AN26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR26" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AS26" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU26" t="n">
         <v>7.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AW26" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AX26" t="n">
         <v>7.4</v>
@@ -5563,20 +5563,20 @@
         <v>26</v>
       </c>
       <c r="BD26" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BE26" t="n">
         <v>110</v>
       </c>
       <c r="BF26" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BG26" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5616,10 +5616,10 @@
         <v>2.96</v>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K27" t="n">
         <v>3.2</v>
@@ -5631,7 +5631,7 @@
         <v>1.13</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O27" t="n">
         <v>1.56</v>
@@ -5640,13 +5640,13 @@
         <v>1.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R27" t="n">
         <v>1.17</v>
       </c>
       <c r="S27" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T27" t="n">
         <v>2.1</v>
@@ -5655,7 +5655,7 @@
         <v>1.74</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
         <v>1.52</v>
@@ -5709,7 +5709,7 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO27" t="n">
         <v>75</v>
@@ -5724,7 +5724,7 @@
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5736,7 +5736,7 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="AX27" t="n">
         <v>14.5</v>
@@ -5751,26 +5751,26 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BB27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF27" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>8.6</v>
       </c>
       <c r="BG27" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
         <v>5.5</v>
       </c>
       <c r="I28" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J28" t="n">
         <v>3.75</v>
@@ -5822,31 +5822,31 @@
         <v>1.43</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
         <v>1.34</v>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U28" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>1.21</v>
@@ -5855,7 +5855,7 @@
         <v>2.24</v>
       </c>
       <c r="X28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
         <v>18</v>
@@ -5864,28 +5864,28 @@
         <v>42</v>
       </c>
       <c r="AA28" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AB28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>80</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG28" t="n">
         <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
         <v>85</v>
@@ -5894,7 +5894,7 @@
         <v>18</v>
       </c>
       <c r="AK28" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL28" t="n">
         <v>38</v>
@@ -5903,25 +5903,25 @@
         <v>130</v>
       </c>
       <c r="AN28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP28" t="n">
         <v>12.5</v>
       </c>
-      <c r="AO28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ28" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR28" t="n">
         <v>38</v>
       </c>
       <c r="AS28" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU28" t="n">
         <v>7.8</v>
@@ -5930,41 +5930,41 @@
         <v>19.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AX28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY28" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.4</v>
       </c>
       <c r="AZ28" t="n">
         <v>18.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BB28" t="n">
         <v>16.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD28" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BE28" t="n">
         <v>65</v>
       </c>
       <c r="BF28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G29" t="n">
         <v>1.65</v>
@@ -6007,7 +6007,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K29" t="n">
         <v>4.4</v>
@@ -6025,22 +6025,22 @@
         <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R29" t="n">
         <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T29" t="n">
         <v>2.16</v>
       </c>
       <c r="U29" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V29" t="n">
         <v>1.15</v>
@@ -6121,7 +6121,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV29" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="AW29" t="n">
         <v>10</v>
@@ -6133,7 +6133,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA29" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6189,61 +6189,61 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="G30" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="H30" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="I30" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K30" t="n">
         <v>5.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U30" t="n">
         <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W30" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="X30" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
         <v>29</v>
@@ -6255,7 +6255,7 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
         <v>12</v>
@@ -6267,7 +6267,7 @@
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
         <v>11</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS30" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AT30" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.8</v>
+        <v>2.94</v>
       </c>
       <c r="AV30" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AX30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BA30" t="n">
         <v>4.2</v>
       </c>
-      <c r="AY30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BB30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC30" t="n">
-        <v>5.6</v>
+        <v>3.15</v>
       </c>
       <c r="BD30" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="BG30" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
         <v>4.4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
@@ -6434,10 +6434,10 @@
         <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X31" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y31" t="n">
         <v>21</v>
@@ -6446,10 +6446,10 @@
         <v>60</v>
       </c>
       <c r="AA31" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC31" t="n">
         <v>9.4</v>
@@ -6464,7 +6464,7 @@
         <v>9</v>
       </c>
       <c r="AG31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH31" t="n">
         <v>25</v>
@@ -6473,13 +6473,13 @@
         <v>110</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="AK31" t="n">
         <v>17.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM31" t="n">
         <v>160</v>
@@ -6494,16 +6494,16 @@
         <v>13</v>
       </c>
       <c r="AQ31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS31" t="n">
         <v>17.5</v>
       </c>
-      <c r="AR31" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>19</v>
-      </c>
       <c r="AT31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU31" t="n">
         <v>8.800000000000001</v>
@@ -6512,7 +6512,7 @@
         <v>23</v>
       </c>
       <c r="AW31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX31" t="n">
         <v>8.4</v>
@@ -6524,7 +6524,7 @@
         <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BB31" t="n">
         <v>13.5</v>
@@ -6536,7 +6536,7 @@
         <v>36</v>
       </c>
       <c r="BE31" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BF31" t="n">
         <v>9.4</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G32" t="n">
         <v>1.64</v>
       </c>
       <c r="H32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I32" t="n">
         <v>7.4</v>
@@ -6607,7 +6607,7 @@
         <v>1.43</v>
       </c>
       <c r="P32" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q32" t="n">
         <v>2.28</v>
@@ -6622,7 +6622,7 @@
         <v>2.26</v>
       </c>
       <c r="U32" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V32" t="n">
         <v>1.15</v>
@@ -6634,13 +6634,13 @@
         <v>12</v>
       </c>
       <c r="Y32" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z32" t="n">
         <v>60</v>
       </c>
       <c r="AA32" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AB32" t="n">
         <v>6.4</v>
@@ -6664,7 +6664,7 @@
         <v>29</v>
       </c>
       <c r="AI32" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AJ32" t="n">
         <v>15.5</v>
@@ -6673,7 +6673,7 @@
         <v>20</v>
       </c>
       <c r="AL32" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM32" t="n">
         <v>210</v>
@@ -6691,13 +6691,13 @@
         <v>16.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS32" t="n">
         <v>48</v>
       </c>
       <c r="AT32" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU32" t="n">
         <v>8.4</v>
@@ -6709,7 +6709,7 @@
         <v>40</v>
       </c>
       <c r="AX32" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY32" t="n">
         <v>9.4</v>
@@ -6727,7 +6727,7 @@
         <v>18.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE32" t="n">
         <v>48</v>
@@ -6736,11 +6736,11 @@
         <v>11.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
         <v>8.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K33" t="n">
         <v>4.1</v>
@@ -6795,22 +6795,22 @@
         <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O33" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P33" t="n">
         <v>1.62</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R33" t="n">
         <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T33" t="n">
         <v>2.44</v>
@@ -6840,7 +6840,7 @@
         <v>5.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD33" t="n">
         <v>36</v>
@@ -6849,7 +6849,7 @@
         <v>200</v>
       </c>
       <c r="AF33" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG33" t="n">
         <v>11</v>
@@ -6858,7 +6858,7 @@
         <v>36</v>
       </c>
       <c r="AI33" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AJ33" t="n">
         <v>14.5</v>
@@ -6870,13 +6870,13 @@
         <v>65</v>
       </c>
       <c r="AM33" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
         <v>9</v>
@@ -6888,13 +6888,13 @@
         <v>55</v>
       </c>
       <c r="AS33" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AT33" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU33" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV33" t="n">
         <v>30</v>
@@ -6903,7 +6903,7 @@
         <v>46</v>
       </c>
       <c r="AX33" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY33" t="n">
         <v>10</v>
@@ -6915,10 +6915,10 @@
         <v>48</v>
       </c>
       <c r="BB33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD33" t="n">
         <v>50</v>
@@ -6927,14 +6927,14 @@
         <v>100</v>
       </c>
       <c r="BF33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG33" t="n">
         <v>55</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>2.04</v>
       </c>
       <c r="H34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I34" t="n">
         <v>5.1</v>
@@ -6989,28 +6989,28 @@
         <v>1.13</v>
       </c>
       <c r="N34" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
         <v>1.55</v>
       </c>
       <c r="P34" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S34" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="T34" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U34" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V34" t="n">
         <v>1.24</v>
@@ -7019,10 +7019,10 @@
         <v>1.96</v>
       </c>
       <c r="X34" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y34" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z34" t="n">
         <v>1000</v>
@@ -7031,10 +7031,10 @@
         <v>180</v>
       </c>
       <c r="AB34" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD34" t="n">
         <v>30</v>
@@ -7049,16 +7049,16 @@
         <v>11.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI34" t="n">
         <v>130</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL34" t="n">
         <v>1000</v>
@@ -7067,34 +7067,34 @@
         <v>260</v>
       </c>
       <c r="AN34" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ34" t="n">
         <v>11</v>
       </c>
       <c r="AR34" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AS34" t="n">
         <v>40</v>
       </c>
       <c r="AT34" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AW34" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AX34" t="n">
         <v>9</v>
@@ -7103,10 +7103,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB34" t="n">
         <v>20</v>
@@ -7115,20 +7115,20 @@
         <v>23</v>
       </c>
       <c r="BD34" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BE34" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF34" t="n">
         <v>20</v>
       </c>
       <c r="BG34" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>
@@ -7183,19 +7183,19 @@
         <v>1.16</v>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O35" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P35" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q35" t="n">
         <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S35" t="n">
         <v>6.8</v>
@@ -7255,7 +7255,7 @@
         <v>36</v>
       </c>
       <c r="AL35" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
@@ -7303,7 +7303,7 @@
         <v>8.6</v>
       </c>
       <c r="BB35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC35" t="n">
         <v>28</v>
@@ -7318,11 +7318,11 @@
         <v>7.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-11 06:41:37</t>
+          <t>2026-03-11 08:49:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-11.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:07:25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.72</v>
+        <v>2.36</v>
       </c>
       <c r="G2" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
         <v>5.7</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AD2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO2" t="n">
         <v>44</v>
       </c>
-      <c r="Y2" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AP2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW2" t="n">
         <v>22</v>
       </c>
-      <c r="AE2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AX2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR2" t="n">
+      <c r="BD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>36</v>
       </c>
-      <c r="AS2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:32:41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>330</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>460</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>4.9</v>
       </c>
-      <c r="G3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X3" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF3" t="n">
+      <c r="AR3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>42</v>
       </c>
-      <c r="AG3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>19</v>
-      </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="BC3" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="BD3" t="n">
-        <v>10</v>
+        <v>220</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>420</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>180</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="H4" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="I4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.57</v>
       </c>
-      <c r="J4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.02</v>
-      </c>
       <c r="V4" t="n">
-        <v>2.76</v>
+        <v>2.36</v>
       </c>
       <c r="W4" t="n">
         <v>1.16</v>
       </c>
       <c r="X4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>490</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
         <v>18</v>
       </c>
-      <c r="Y4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AP4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
         <v>22</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AX4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>32</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="BA4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB4" t="n">
         <v>210</v>
       </c>
-      <c r="AK4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN4" t="n">
+      <c r="BC4" t="n">
         <v>130</v>
       </c>
-      <c r="AO4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>190</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>90</v>
-      </c>
       <c r="BD4" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="BE4" t="n">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="BF4" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.4</v>
+        <v>17</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1339,31 +1339,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="I5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J5" t="n">
         <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
         <v>1.52</v>
@@ -1372,10 +1372,10 @@
         <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
         <v>5.4</v>
@@ -1390,7 +1390,7 @@
         <v>2.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X5" t="n">
         <v>9.800000000000001</v>
@@ -1417,22 +1417,22 @@
         <v>26</v>
       </c>
       <c r="AF5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AG5" t="n">
         <v>23</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AL5" t="n">
         <v>700</v>
@@ -1450,7 +1450,7 @@
         <v>8.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
         <v>8.800000000000001</v>
@@ -1459,7 +1459,7 @@
         <v>19.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
         <v>7</v>
@@ -1477,32 +1477,32 @@
         <v>19</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
         <v>46</v>
       </c>
       <c r="BB5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>11</v>
       </c>
       <c r="BE5" t="n">
         <v>14.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="BG5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1545,10 +1545,10 @@
         <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="L6" t="n">
         <v>1.72</v>
@@ -1557,28 +1557,28 @@
         <v>1.19</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.12</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
         <v>1.44</v>
@@ -1587,116 +1587,116 @@
         <v>1.44</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>980</v>
+        <v>8</v>
       </c>
       <c r="Z6" t="n">
-        <v>980</v>
+        <v>18</v>
       </c>
       <c r="AA6" t="n">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
-        <v>980</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>6.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>980</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AH6" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AK6" t="n">
         <v>980</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.96</v>
+        <v>36</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.96</v>
+        <v>40</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.88</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.92</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.96</v>
+        <v>14.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.96</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.96</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.97</v>
+        <v>14.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.98</v>
+        <v>28</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.94</v>
+        <v>14</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.94</v>
+        <v>13.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -1748,16 +1748,16 @@
         <v>1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
         <v>2.38</v>
@@ -1769,31 +1769,31 @@
         <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
         <v>1.89</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="X7" t="n">
         <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
@@ -1805,10 +1805,10 @@
         <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
@@ -1817,80 +1817,80 @@
         <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
         <v>95</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AT7" t="n">
         <v>7</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA7" t="n">
         <v>48</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BC7" t="n">
         <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>14.5</v>
+        <v>65</v>
       </c>
       <c r="BF7" t="n">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
         <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.34</v>
@@ -1951,16 +1951,16 @@
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
         <v>1.64</v>
@@ -1969,13 +1969,13 @@
         <v>2.54</v>
       </c>
       <c r="V8" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="W8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -1984,31 +1984,31 @@
         <v>14</v>
       </c>
       <c r="AA8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
         <v>10.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG8" t="n">
         <v>15.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ8" t="n">
         <v>70</v>
@@ -2023,13 +2023,13 @@
         <v>60</v>
       </c>
       <c r="AN8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>11.5</v>
@@ -2038,28 +2038,28 @@
         <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>15</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>14</v>
       </c>
       <c r="BA8" t="n">
         <v>25</v>
@@ -2071,20 +2071,20 @@
         <v>36</v>
       </c>
       <c r="BD8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE8" t="n">
         <v>55</v>
       </c>
       <c r="BF8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>1.32</v>
@@ -2139,10 +2139,10 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
         <v>2.44</v>
@@ -2151,13 +2151,13 @@
         <v>1.68</v>
       </c>
       <c r="R9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.58</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.57</v>
       </c>
       <c r="U9" t="n">
         <v>2.68</v>
@@ -2172,31 +2172,31 @@
         <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z9" t="n">
         <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB9" t="n">
         <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
         <v>30</v>
       </c>
       <c r="AF9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
         <v>14</v>
@@ -2208,10 +2208,10 @@
         <v>32</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM9" t="n">
         <v>55</v>
@@ -2220,16 +2220,16 @@
         <v>13.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP9" t="n">
         <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS9" t="n">
         <v>50</v>
@@ -2244,19 +2244,19 @@
         <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB9" t="n">
         <v>30</v>
@@ -2274,11 +2274,11 @@
         <v>12.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -2309,67 +2309,67 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
         <v>65</v>
@@ -2378,16 +2378,16 @@
         <v>13.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF10" t="n">
         <v>15</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>15.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2396,28 +2396,28 @@
         <v>14.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK10" t="n">
         <v>18.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP10" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -2432,10 +2432,10 @@
         <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
         <v>36</v>
@@ -2444,35 +2444,35 @@
         <v>14.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -2512,10 +2512,10 @@
         <v>3.8</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
         <v>3.15</v>
@@ -2527,16 +2527,16 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O11" t="n">
         <v>1.55</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
         <v>1.2</v>
@@ -2545,16 +2545,16 @@
         <v>5.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V11" t="n">
         <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X11" t="n">
         <v>8.800000000000001</v>
@@ -2563,7 +2563,7 @@
         <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AA11" t="n">
         <v>90</v>
@@ -2584,7 +2584,7 @@
         <v>13.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>24</v>
@@ -2593,7 +2593,7 @@
         <v>85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
         <v>34</v>
@@ -2605,7 +2605,7 @@
         <v>200</v>
       </c>
       <c r="AN11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
         <v>90</v>
@@ -2617,7 +2617,7 @@
         <v>9.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS11" t="n">
         <v>42</v>
@@ -2632,7 +2632,7 @@
         <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX11" t="n">
         <v>12</v>
@@ -2647,7 +2647,7 @@
         <v>60</v>
       </c>
       <c r="BB11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC11" t="n">
         <v>28</v>
@@ -2662,11 +2662,11 @@
         <v>23</v>
       </c>
       <c r="BG11" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
         <v>3.05</v>
@@ -2724,19 +2724,19 @@
         <v>2.66</v>
       </c>
       <c r="O12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T12" t="n">
         <v>2.26</v>
@@ -2745,10 +2745,10 @@
         <v>1.76</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W12" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="X12" t="n">
         <v>8.199999999999999</v>
@@ -2763,7 +2763,7 @@
         <v>130</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC12" t="n">
         <v>7.2</v>
@@ -2775,7 +2775,7 @@
         <v>85</v>
       </c>
       <c r="AF12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
@@ -2787,7 +2787,7 @@
         <v>110</v>
       </c>
       <c r="AJ12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK12" t="n">
         <v>29</v>
@@ -2796,7 +2796,7 @@
         <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN12" t="n">
         <v>27</v>
@@ -2817,13 +2817,13 @@
         <v>40</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW12" t="n">
         <v>75</v>
@@ -2835,7 +2835,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA12" t="n">
         <v>95</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -2891,94 +2891,94 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="G13" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="I13" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="U13" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="V13" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>19.5</v>
       </c>
       <c r="AB13" t="n">
         <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
         <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AH13" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AI13" t="n">
-        <v>460</v>
+        <v>150</v>
       </c>
       <c r="AJ13" t="n">
         <v>1000</v>
@@ -2996,7 +2996,7 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AP13" t="n">
         <v>8.4</v>
@@ -3005,19 +3005,19 @@
         <v>5.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AS13" t="n">
         <v>14.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AW13" t="n">
         <v>11.5</v>
@@ -3026,7 +3026,7 @@
         <v>13</v>
       </c>
       <c r="AY13" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -3035,26 +3035,26 @@
         <v>32</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>48</v>
+        <v>10.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="H14" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="I14" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.35</v>
@@ -3109,7 +3109,7 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
         <v>1.24</v>
@@ -3118,7 +3118,7 @@
         <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R14" t="n">
         <v>1.45</v>
@@ -3127,16 +3127,16 @@
         <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3154,10 +3154,10 @@
         <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AE14" t="n">
         <v>170</v>
@@ -3169,7 +3169,7 @@
         <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3202,7 +3202,7 @@
         <v>6.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
         <v>8.199999999999999</v>
@@ -3211,10 +3211,10 @@
         <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3226,29 +3226,29 @@
         <v>7.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC14" t="n">
         <v>6.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE14" t="n">
         <v>6</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.34</v>
       </c>
       <c r="G15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
         <v>3.35</v>
@@ -3291,7 +3291,7 @@
         <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
         <v>3.6</v>
@@ -3303,25 +3303,25 @@
         <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
         <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U15" t="n">
         <v>2.16</v>
@@ -3330,31 +3330,31 @@
         <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y15" t="n">
         <v>13</v>
       </c>
-      <c r="Y15" t="n">
-        <v>12.5</v>
-      </c>
       <c r="Z15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF15" t="n">
         <v>14.5</v>
@@ -3363,10 +3363,10 @@
         <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="AJ15" t="n">
         <v>30</v>
@@ -3375,22 +3375,22 @@
         <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM15" t="n">
         <v>95</v>
       </c>
       <c r="AN15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO15" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>12</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
         <v>21</v>
@@ -3399,13 +3399,13 @@
         <v>50</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW15" t="n">
         <v>34</v>
@@ -3414,16 +3414,16 @@
         <v>13.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BB15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC15" t="n">
         <v>23</v>
@@ -3438,11 +3438,11 @@
         <v>18</v>
       </c>
       <c r="BG15" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="G16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J16" t="n">
         <v>4.1</v>
@@ -3497,7 +3497,7 @@
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>1.43</v>
@@ -3506,16 +3506,16 @@
         <v>1.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R16" t="n">
         <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
         <v>1.65</v>
@@ -3524,7 +3524,7 @@
         <v>1.17</v>
       </c>
       <c r="W16" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X16" t="n">
         <v>12</v>
@@ -3533,7 +3533,7 @@
         <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA16" t="n">
         <v>260</v>
@@ -3542,16 +3542,16 @@
         <v>6.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE16" t="n">
         <v>140</v>
       </c>
       <c r="AF16" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG16" t="n">
         <v>10.5</v>
@@ -3560,10 +3560,10 @@
         <v>32</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK16" t="n">
         <v>21</v>
@@ -3572,19 +3572,19 @@
         <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO16" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AP16" t="n">
         <v>11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR16" t="n">
         <v>42</v>
@@ -3593,34 +3593,34 @@
         <v>11.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD16" t="n">
         <v>36</v>
@@ -3629,14 +3629,14 @@
         <v>60</v>
       </c>
       <c r="BF16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG16" t="n">
         <v>11.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -3676,22 +3676,22 @@
         <v>6.8</v>
       </c>
       <c r="I17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N17" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O17" t="n">
         <v>1.71</v>
@@ -3721,19 +3721,19 @@
         <v>2.28</v>
       </c>
       <c r="X17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y17" t="n">
         <v>14.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="AB17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AC17" t="n">
         <v>8.6</v>
@@ -3742,34 +3742,34 @@
         <v>34</v>
       </c>
       <c r="AE17" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="AF17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AI17" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL17" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AM17" t="n">
         <v>700</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
@@ -3778,59 +3778,59 @@
         <v>6.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR17" t="n">
         <v>48</v>
       </c>
       <c r="AS17" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AW17" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY17" t="n">
         <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BA17" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BB17" t="n">
         <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD17" t="n">
         <v>75</v>
       </c>
       <c r="BE17" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BF17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG17" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G18" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H18" t="n">
         <v>3.05</v>
@@ -3885,7 +3885,7 @@
         <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.58</v>
@@ -3912,7 +3912,7 @@
         <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X18" t="n">
         <v>8.4</v>
@@ -3966,7 +3966,7 @@
         <v>600</v>
       </c>
       <c r="AO18" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="AP18" t="n">
         <v>7</v>
@@ -3975,7 +3975,7 @@
         <v>7.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS18" t="n">
         <v>27</v>
@@ -4017,14 +4017,14 @@
         <v>10</v>
       </c>
       <c r="BF18" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.4</v>
+        <v>26</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -4055,58 +4055,58 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X19" t="n">
         <v>13</v>
@@ -4121,52 +4121,52 @@
         <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
         <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG19" t="n">
         <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM19" t="n">
-        <v>140</v>
+        <v>430</v>
       </c>
       <c r="AN19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP19" t="n">
         <v>12.5</v>
       </c>
-      <c r="AO19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AQ19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR19" t="n">
         <v>38</v>
@@ -4175,10 +4175,10 @@
         <v>42</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV19" t="n">
         <v>19.5</v>
@@ -4187,38 +4187,38 @@
         <v>75</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY19" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA19" t="n">
         <v>75</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC19" t="n">
         <v>18</v>
       </c>
       <c r="BD19" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE19" t="n">
         <v>100</v>
       </c>
       <c r="BF19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG19" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
         <v>17.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="AS20" t="n">
         <v>10</v>
@@ -4387,7 +4387,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
         <v>10</v>
@@ -4396,13 +4396,13 @@
         <v>12.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD20" t="n">
         <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BF20" t="n">
         <v>9.4</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>9.4</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K21" t="n">
         <v>5.4</v>
@@ -4479,13 +4479,13 @@
         <v>1.74</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U21" t="n">
         <v>1.94</v>
@@ -4560,10 +4560,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
         <v>9.199999999999999</v>
@@ -4587,7 +4587,7 @@
         <v>8.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="BC21" t="n">
         <v>7.4</v>
@@ -4602,11 +4602,11 @@
         <v>5.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G22" t="n">
         <v>1.62</v>
@@ -4646,7 +4646,7 @@
         <v>6.8</v>
       </c>
       <c r="I22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
         <v>4.2</v>
@@ -4673,7 +4673,7 @@
         <v>2.04</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
         <v>3.75</v>
@@ -4682,7 +4682,7 @@
         <v>2.06</v>
       </c>
       <c r="U22" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V22" t="n">
         <v>1.16</v>
@@ -4703,7 +4703,7 @@
         <v>220</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC22" t="n">
         <v>9.199999999999999</v>
@@ -4727,13 +4727,13 @@
         <v>110</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK22" t="n">
         <v>17.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM22" t="n">
         <v>160</v>
@@ -4748,13 +4748,13 @@
         <v>13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT22" t="n">
         <v>7</v>
@@ -4766,7 +4766,7 @@
         <v>24</v>
       </c>
       <c r="AW22" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AX22" t="n">
         <v>8.4</v>
@@ -4778,7 +4778,7 @@
         <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="BB22" t="n">
         <v>14</v>
@@ -4787,20 +4787,20 @@
         <v>16.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG22" t="n">
         <v>120</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G23" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H23" t="n">
         <v>7</v>
@@ -4858,13 +4858,13 @@
         <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P23" t="n">
         <v>1.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R23" t="n">
         <v>1.27</v>
@@ -4873,16 +4873,16 @@
         <v>4.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="U23" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V23" t="n">
         <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X23" t="n">
         <v>12</v>
@@ -4894,7 +4894,7 @@
         <v>60</v>
       </c>
       <c r="AA23" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB23" t="n">
         <v>6.6</v>
@@ -4903,10 +4903,10 @@
         <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF23" t="n">
         <v>8.199999999999999</v>
@@ -4930,7 +4930,7 @@
         <v>55</v>
       </c>
       <c r="AM23" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN23" t="n">
         <v>13</v>
@@ -4942,13 +4942,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS23" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AT23" t="n">
         <v>6</v>
@@ -4957,44 +4957,44 @@
         <v>8.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW23" t="n">
         <v>42</v>
       </c>
       <c r="AX23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY23" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA23" t="n">
         <v>42</v>
       </c>
       <c r="BB23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BE23" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -5031,13 +5031,13 @@
         <v>2.04</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I24" t="n">
         <v>5.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
         <v>3.3</v>
@@ -5049,25 +5049,25 @@
         <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O24" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S24" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U24" t="n">
         <v>1.72</v>
@@ -5079,7 +5079,7 @@
         <v>1.96</v>
       </c>
       <c r="X24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y24" t="n">
         <v>13</v>
@@ -5100,7 +5100,7 @@
         <v>22</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF24" t="n">
         <v>10.5</v>
@@ -5109,10 +5109,10 @@
         <v>11.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AI24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ24" t="n">
         <v>24</v>
@@ -5124,7 +5124,7 @@
         <v>65</v>
       </c>
       <c r="AM24" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN24" t="n">
         <v>25</v>
@@ -5133,7 +5133,7 @@
         <v>160</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ24" t="n">
         <v>11.5</v>
@@ -5142,7 +5142,7 @@
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AT24" t="n">
         <v>6</v>
@@ -5154,7 +5154,7 @@
         <v>19.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AX24" t="n">
         <v>9.4</v>
@@ -5163,7 +5163,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
         <v>42</v>
@@ -5184,11 +5184,11 @@
         <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -5219,37 +5219,37 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="G25" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
         <v>1.55</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P25" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q25" t="n">
         <v>2.5</v>
@@ -5258,115 +5258,115 @@
         <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="U25" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="V25" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W25" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="X25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="n">
-        <v>370</v>
+        <v>480</v>
       </c>
       <c r="AB25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD25" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AE25" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AF25" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AI25" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AN25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AP25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU25" t="n">
         <v>9</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="AV25" t="n">
         <v>32</v>
       </c>
-      <c r="AS25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>30</v>
-      </c>
       <c r="AW25" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AX25" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AY25" t="n">
         <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BA25" t="n">
         <v>48</v>
       </c>
       <c r="BB25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC25" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD25" t="n">
         <v>55</v>
@@ -5375,14 +5375,14 @@
         <v>55</v>
       </c>
       <c r="BF25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG25" t="n">
         <v>55</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
@@ -5422,10 +5422,10 @@
         <v>4.6</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>3.25</v>
@@ -5434,7 +5434,7 @@
         <v>1.69</v>
       </c>
       <c r="M26" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N26" t="n">
         <v>2.32</v>
@@ -5455,7 +5455,7 @@
         <v>6.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
         <v>1.6</v>
@@ -5485,10 +5485,10 @@
         <v>7.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF26" t="n">
         <v>11.5</v>
@@ -5509,19 +5509,19 @@
         <v>36</v>
       </c>
       <c r="AL26" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ26" t="n">
         <v>9.6</v>
@@ -5530,7 +5530,7 @@
         <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT26" t="n">
         <v>5.2</v>
@@ -5542,7 +5542,7 @@
         <v>19.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX26" t="n">
         <v>9.6</v>
@@ -5551,13 +5551,13 @@
         <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC26" t="n">
         <v>28</v>
@@ -5566,17 +5566,17 @@
         <v>60</v>
       </c>
       <c r="BE26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF26" t="n">
         <v>12</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-11 13:05:31</t>
+          <t>2026-03-11 15:15:29</t>
         </is>
       </c>
     </row>
